--- a/src/attributions/attributions_saliency_traj_206.xlsx
+++ b/src/attributions/attributions_saliency_traj_206.xlsx
@@ -1568,571 +1568,571 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.003176763653755188</v>
+        <v>0.1009618937969208</v>
       </c>
       <c r="B3" t="n">
-        <v>1.090634942054749</v>
+        <v>0.9619448781013489</v>
       </c>
       <c r="C3" t="n">
-        <v>0.08916226029396057</v>
+        <v>0.03720031678676605</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1711438596248627</v>
+        <v>0.1906541883945465</v>
       </c>
       <c r="E3" t="n">
-        <v>0.3314861953258514</v>
+        <v>0.3174963295459747</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8662043809890747</v>
+        <v>1.020945191383362</v>
       </c>
       <c r="G3" t="n">
-        <v>0.04185806959867477</v>
+        <v>0.1935279965400696</v>
       </c>
       <c r="H3" t="n">
-        <v>0.2151976227760315</v>
+        <v>0.1872215867042542</v>
       </c>
       <c r="I3" t="n">
-        <v>0.07907550781965256</v>
+        <v>0.1086628437042236</v>
       </c>
       <c r="J3" t="n">
-        <v>0.2293035387992859</v>
+        <v>0.01312116160988808</v>
       </c>
       <c r="K3" t="n">
-        <v>0.8554242849349976</v>
+        <v>1.022967576980591</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1011684685945511</v>
+        <v>0.03804990649223328</v>
       </c>
       <c r="M3" t="n">
-        <v>0.3708005547523499</v>
+        <v>0.1553482264280319</v>
       </c>
       <c r="N3" t="n">
-        <v>0.2226188331842422</v>
+        <v>0.1209084987640381</v>
       </c>
       <c r="O3" t="n">
-        <v>0.735045313835144</v>
+        <v>0.821387767791748</v>
       </c>
       <c r="P3" t="n">
-        <v>0.08027338236570358</v>
+        <v>0.09595222771167755</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.03256834298372269</v>
+        <v>0.1850077211856842</v>
       </c>
       <c r="R3" t="n">
-        <v>0.01469361782073975</v>
+        <v>0.06197892129421234</v>
       </c>
       <c r="S3" t="n">
-        <v>0.09735672920942307</v>
+        <v>0.1324288249015808</v>
       </c>
       <c r="T3" t="n">
-        <v>0.12343530356884</v>
+        <v>0.1941964030265808</v>
       </c>
       <c r="U3" t="n">
-        <v>0.07083943486213684</v>
+        <v>0.3486402630805969</v>
       </c>
       <c r="V3" t="n">
-        <v>0.02563388086855412</v>
+        <v>0.1534881889820099</v>
       </c>
       <c r="W3" t="n">
-        <v>0.05433753132820129</v>
+        <v>0.123751200735569</v>
       </c>
       <c r="X3" t="n">
-        <v>0.03667748719453812</v>
+        <v>0.1557458937168121</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.01271747797727585</v>
+        <v>0.4212295711040497</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.07301425188779831</v>
+        <v>0.1848563700914383</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.0504072830080986</v>
+        <v>0.1315041184425354</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.1288817971944809</v>
+        <v>0.2206304371356964</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.1116460710763931</v>
+        <v>0.2157236635684967</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.007551536895334721</v>
+        <v>0.1338132321834564</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.03828326985239983</v>
+        <v>0.5343719720840454</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.2263237982988358</v>
+        <v>0.07957915216684341</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.1339369118213654</v>
+        <v>0.2968880534172058</v>
       </c>
       <c r="AH3" t="n">
-        <v>0.04073311388492584</v>
+        <v>0.1975512504577637</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.009972257539629936</v>
+        <v>0.3604474365711212</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.03729330003261566</v>
+        <v>0.2741925716400146</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.01407001912593842</v>
+        <v>0.05741199105978012</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.1036582365632057</v>
+        <v>0.1262995898723602</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.009037138894200325</v>
+        <v>0.006751447916030884</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.02375011146068573</v>
+        <v>0.0784473642706871</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.09097342193126678</v>
+        <v>0.1494381129741669</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.1981810182332993</v>
+        <v>0.2482832223176956</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.005139895714819431</v>
+        <v>0.2746559381484985</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.05457079783082008</v>
+        <v>0.1937159299850464</v>
       </c>
       <c r="AS3" t="n">
-        <v>0.142734482884407</v>
+        <v>0.05354410409927368</v>
       </c>
       <c r="AT3" t="n">
-        <v>0.1284535378217697</v>
+        <v>0.06094437465071678</v>
       </c>
       <c r="AU3" t="n">
-        <v>0.5198414325714111</v>
+        <v>0.6584639549255371</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.00167560949921608</v>
+        <v>0.1545112133026123</v>
       </c>
       <c r="AW3" t="n">
-        <v>0.02689577266573906</v>
+        <v>0.1085624173283577</v>
       </c>
       <c r="AX3" t="n">
-        <v>0.2586131989955902</v>
+        <v>0.4041799008846283</v>
       </c>
       <c r="AY3" t="n">
-        <v>0.6706234216690063</v>
+        <v>0.6225893497467041</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0.07114848494529724</v>
+        <v>0.209059089422226</v>
       </c>
       <c r="BA3" t="n">
-        <v>0.1664115339517593</v>
+        <v>0.03637435287237167</v>
       </c>
       <c r="BB3" t="n">
-        <v>0.2374999076128006</v>
+        <v>0.1711551547050476</v>
       </c>
       <c r="BC3" t="n">
-        <v>0.03928536549210548</v>
+        <v>0.1781889945268631</v>
       </c>
       <c r="BD3" t="n">
-        <v>0.3141694664955139</v>
+        <v>0.4127059578895569</v>
       </c>
       <c r="BE3" t="n">
-        <v>0.1105800941586494</v>
+        <v>0.1312989443540573</v>
       </c>
       <c r="BF3" t="n">
-        <v>0.1987052261829376</v>
+        <v>0.3853715062141418</v>
       </c>
       <c r="BG3" t="n">
-        <v>0.07023946940898895</v>
+        <v>0.359509289264679</v>
       </c>
       <c r="BH3" t="n">
-        <v>0.1396628320217133</v>
+        <v>0.313403308391571</v>
       </c>
       <c r="BI3" t="n">
-        <v>0.06870205700397491</v>
+        <v>0.05479621887207031</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.07757763564586639</v>
+        <v>0.2185585200786591</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.1284697353839874</v>
+        <v>0.1174919083714485</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.01127934455871582</v>
+        <v>0.1525183767080307</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.05509329587221146</v>
+        <v>0.1013377383351326</v>
       </c>
       <c r="BN3" t="n">
-        <v>0.009582009166479111</v>
+        <v>0.08022407442331314</v>
       </c>
       <c r="BO3" t="n">
-        <v>0.0363907665014267</v>
+        <v>0.004808731377124786</v>
       </c>
       <c r="BP3" t="n">
-        <v>0.09561393409967422</v>
+        <v>0.08598634600639343</v>
       </c>
       <c r="BQ3" t="n">
-        <v>0.03600814193487167</v>
+        <v>0.2282414138317108</v>
       </c>
       <c r="BR3" t="n">
-        <v>0.004098502919077873</v>
+        <v>0.09995280206203461</v>
       </c>
       <c r="BS3" t="n">
-        <v>0.05134343355894089</v>
+        <v>0.08133861422538757</v>
       </c>
       <c r="BT3" t="n">
-        <v>0.01583832874894142</v>
+        <v>0.1155704259872437</v>
       </c>
       <c r="BU3" t="n">
-        <v>0.09705358743667603</v>
+        <v>0.06778687238693237</v>
       </c>
       <c r="BV3" t="n">
-        <v>0.2306451201438904</v>
+        <v>0.2782940268516541</v>
       </c>
       <c r="BW3" t="n">
-        <v>0.09792174398899078</v>
+        <v>0.2572897672653198</v>
       </c>
       <c r="BX3" t="n">
-        <v>0.04723362624645233</v>
+        <v>0.05366081744432449</v>
       </c>
       <c r="BY3" t="n">
-        <v>0.2537739276885986</v>
+        <v>0.1638933420181274</v>
       </c>
       <c r="BZ3" t="n">
-        <v>0.2578223645687103</v>
+        <v>0.4563577473163605</v>
       </c>
       <c r="CA3" t="n">
-        <v>0.07080020755529404</v>
+        <v>0.4858265221118927</v>
       </c>
       <c r="CB3" t="n">
-        <v>0.04846732318401337</v>
+        <v>0.05532900989055634</v>
       </c>
       <c r="CC3" t="n">
-        <v>0.008164118975400925</v>
+        <v>0.01287483237683773</v>
       </c>
       <c r="CD3" t="n">
-        <v>0.01700654067099094</v>
+        <v>0.02970247901976109</v>
       </c>
       <c r="CE3" t="n">
-        <v>0.1991893351078033</v>
+        <v>0.2917495965957642</v>
       </c>
       <c r="CF3" t="n">
-        <v>0.04217452555894852</v>
+        <v>0.04870393872261047</v>
       </c>
       <c r="CG3" t="n">
-        <v>0.02706475183367729</v>
+        <v>0.06565176695585251</v>
       </c>
       <c r="CH3" t="n">
-        <v>0.02332529798150063</v>
+        <v>0.08949930965900421</v>
       </c>
       <c r="CI3" t="n">
-        <v>0.1364151388406754</v>
+        <v>0.206930473446846</v>
       </c>
       <c r="CJ3" t="n">
-        <v>0.003691749647259712</v>
+        <v>0.007526207715272903</v>
       </c>
       <c r="CK3" t="n">
-        <v>0.02854388020932674</v>
+        <v>0.04961953684687614</v>
       </c>
       <c r="CL3" t="n">
-        <v>0.01738779246807098</v>
+        <v>0.02989841625094414</v>
       </c>
       <c r="CM3" t="n">
-        <v>0.1068881675601006</v>
+        <v>0.2751917243003845</v>
       </c>
       <c r="CN3" t="n">
-        <v>0.03234162926673889</v>
+        <v>0.5421987175941467</v>
       </c>
       <c r="CO3" t="n">
-        <v>0.008914459496736526</v>
+        <v>0.383217990398407</v>
       </c>
       <c r="CP3" t="n">
-        <v>0.04861224442720413</v>
+        <v>0.2511419951915741</v>
       </c>
       <c r="CQ3" t="n">
-        <v>0.04574398696422577</v>
+        <v>0.0009055137634277344</v>
       </c>
       <c r="CR3" t="n">
-        <v>0.07571211457252502</v>
+        <v>0.2674154937267303</v>
       </c>
       <c r="CS3" t="n">
-        <v>0.04824373871088028</v>
+        <v>0.01799659430980682</v>
       </c>
       <c r="CT3" t="n">
-        <v>0.1434581428766251</v>
+        <v>0.1864372342824936</v>
       </c>
       <c r="CU3" t="n">
-        <v>0.1162162572145462</v>
+        <v>0.2143482863903046</v>
       </c>
       <c r="CV3" t="n">
-        <v>0.004516782239079475</v>
+        <v>0.004631481133401394</v>
       </c>
       <c r="CW3" t="n">
-        <v>0.1730197966098785</v>
+        <v>0.2750575244426727</v>
       </c>
       <c r="CX3" t="n">
-        <v>0.05088021606206894</v>
+        <v>0.01093796640634537</v>
       </c>
       <c r="CY3" t="n">
-        <v>0.06238923966884613</v>
+        <v>0.02536306716501713</v>
       </c>
       <c r="CZ3" t="n">
-        <v>0.00475563108921051</v>
+        <v>0.07503685355186462</v>
       </c>
       <c r="DA3" t="n">
-        <v>0.1521009206771851</v>
+        <v>0.1842414140701294</v>
       </c>
       <c r="DB3" t="n">
-        <v>0.0222315676510334</v>
+        <v>0.01014160364866257</v>
       </c>
       <c r="DC3" t="n">
-        <v>0.03820198774337769</v>
+        <v>0.008766558952629566</v>
       </c>
       <c r="DD3" t="n">
-        <v>0.008313373662531376</v>
+        <v>0.001251569017767906</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.129475399851799</v>
+        <v>0.4364661276340485</v>
       </c>
       <c r="DF3" t="n">
-        <v>0.102547399699688</v>
+        <v>0.1814206093549728</v>
       </c>
       <c r="DG3" t="n">
-        <v>0.1011130437254906</v>
+        <v>0.3242855966091156</v>
       </c>
       <c r="DH3" t="n">
-        <v>0.1176287829875946</v>
+        <v>0.1193707808852196</v>
       </c>
       <c r="DI3" t="n">
-        <v>0.082644984126091</v>
+        <v>0.1722100675106049</v>
       </c>
       <c r="DJ3" t="n">
-        <v>0.1611846536397934</v>
+        <v>0.7039209008216858</v>
       </c>
       <c r="DK3" t="n">
-        <v>0.01220195554196835</v>
+        <v>0.1958638876676559</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.3321308493614197</v>
+        <v>0.218825101852417</v>
       </c>
       <c r="DM3" t="n">
-        <v>0.1756742596626282</v>
+        <v>0.280312716960907</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.006820355542004108</v>
+        <v>0.01781033724546432</v>
       </c>
       <c r="DO3" t="n">
-        <v>0.03202518820762634</v>
+        <v>0.1616053581237793</v>
       </c>
       <c r="DP3" t="n">
-        <v>0.07990981638431549</v>
+        <v>0.07543037831783295</v>
       </c>
       <c r="DQ3" t="n">
-        <v>0.0491829514503479</v>
+        <v>0.169287770986557</v>
       </c>
       <c r="DR3" t="n">
-        <v>0.1132903695106506</v>
+        <v>0.05349945276975632</v>
       </c>
       <c r="DS3" t="n">
-        <v>0.06891582161188126</v>
+        <v>0.06285571306943893</v>
       </c>
       <c r="DT3" t="n">
-        <v>0.06057535856962204</v>
+        <v>0.04368365556001663</v>
       </c>
       <c r="DU3" t="n">
-        <v>0.1021963730454445</v>
+        <v>0.04543203115463257</v>
       </c>
       <c r="DV3" t="n">
-        <v>0.06217992678284645</v>
+        <v>0.0412646196782589</v>
       </c>
       <c r="DW3" t="n">
-        <v>0.02281901612877846</v>
+        <v>0.1314668655395508</v>
       </c>
       <c r="DX3" t="n">
-        <v>0.121631033718586</v>
+        <v>0.2265576273202896</v>
       </c>
       <c r="DY3" t="n">
-        <v>0.03983542695641518</v>
+        <v>0.003688722848892212</v>
       </c>
       <c r="DZ3" t="n">
-        <v>0.02847215719521046</v>
+        <v>0.04998970031738281</v>
       </c>
       <c r="EA3" t="n">
-        <v>0.05007693916559219</v>
+        <v>0.1949121057987213</v>
       </c>
       <c r="EB3" t="n">
-        <v>0.0664634108543396</v>
+        <v>0.2998351454734802</v>
       </c>
       <c r="EC3" t="n">
-        <v>0.01956033334136009</v>
+        <v>0.003912759944796562</v>
       </c>
       <c r="ED3" t="n">
-        <v>0.08041739463806152</v>
+        <v>0.3609897196292877</v>
       </c>
       <c r="EE3" t="n">
-        <v>0.04520286619663239</v>
+        <v>0.3365048766136169</v>
       </c>
       <c r="EF3" t="n">
-        <v>0.001429326832294464</v>
+        <v>0.1160257905721664</v>
       </c>
       <c r="EG3" t="n">
-        <v>0.1720469892024994</v>
+        <v>0.1042429059743881</v>
       </c>
       <c r="EH3" t="n">
-        <v>0.03653135895729065</v>
+        <v>0.1407304704189301</v>
       </c>
       <c r="EI3" t="n">
-        <v>0.06931308656930923</v>
+        <v>0.2631579637527466</v>
       </c>
       <c r="EJ3" t="n">
-        <v>0.01541219837963581</v>
+        <v>0.09345094859600067</v>
       </c>
       <c r="EK3" t="n">
-        <v>0.1909297704696655</v>
+        <v>0.2007109969854355</v>
       </c>
       <c r="EL3" t="n">
-        <v>0.02705355733633041</v>
+        <v>0.08283232152462006</v>
       </c>
       <c r="EM3" t="n">
-        <v>0.1084042489528656</v>
+        <v>0.09148281067609787</v>
       </c>
       <c r="EN3" t="n">
-        <v>0.02794075943529606</v>
+        <v>0.07577002793550491</v>
       </c>
       <c r="EO3" t="n">
-        <v>0.05483536794781685</v>
+        <v>0.04146110638976097</v>
       </c>
       <c r="EP3" t="n">
-        <v>0.09904917329549789</v>
+        <v>0.213242769241333</v>
       </c>
       <c r="EQ3" t="n">
-        <v>0.06472702324390411</v>
+        <v>0.2723135352134705</v>
       </c>
       <c r="ER3" t="n">
-        <v>0.05638530850410461</v>
+        <v>0.1744583249092102</v>
       </c>
       <c r="ES3" t="n">
-        <v>0.08878687024116516</v>
+        <v>0.3504588007926941</v>
       </c>
       <c r="ET3" t="n">
-        <v>0.173735648393631</v>
+        <v>0.2476053237915039</v>
       </c>
       <c r="EU3" t="n">
-        <v>0.03787913918495178</v>
+        <v>0.02812289074063301</v>
       </c>
       <c r="EV3" t="n">
-        <v>0.04837135225534439</v>
+        <v>0.1045912504196167</v>
       </c>
       <c r="EW3" t="n">
-        <v>0.09549235552549362</v>
+        <v>0.08614890277385712</v>
       </c>
       <c r="EX3" t="n">
-        <v>0.02345912344753742</v>
+        <v>0.01510997489094734</v>
       </c>
       <c r="EY3" t="n">
-        <v>0.1771242320537567</v>
+        <v>0.260969340801239</v>
       </c>
       <c r="EZ3" t="n">
-        <v>0.005841606296598911</v>
+        <v>0.01008510030806065</v>
       </c>
       <c r="FA3" t="n">
-        <v>0.01431673858314753</v>
+        <v>0.01357104070484638</v>
       </c>
       <c r="FB3" t="n">
-        <v>0.03204662352800369</v>
+        <v>0.1516528427600861</v>
       </c>
       <c r="FC3" t="n">
-        <v>0.1372276842594147</v>
+        <v>0.19808030128479</v>
       </c>
       <c r="FD3" t="n">
-        <v>0.001209482550621033</v>
+        <v>0.01643713563680649</v>
       </c>
       <c r="FE3" t="n">
-        <v>0.01606994122266769</v>
+        <v>0.02823822200298309</v>
       </c>
       <c r="FF3" t="n">
-        <v>0.009847449138760567</v>
+        <v>0.0444987453520298</v>
       </c>
       <c r="FG3" t="n">
-        <v>0.02442295663058758</v>
+        <v>0.2036422193050385</v>
       </c>
       <c r="FH3" t="n">
-        <v>0.08566276729106903</v>
+        <v>0.02019244432449341</v>
       </c>
       <c r="FI3" t="n">
-        <v>0.01332208514213562</v>
+        <v>0.1710987985134125</v>
       </c>
       <c r="FJ3" t="n">
-        <v>0.1729075461626053</v>
+        <v>0.008184734731912613</v>
       </c>
       <c r="FK3" t="n">
-        <v>0.07712309807538986</v>
+        <v>0.1737096905708313</v>
       </c>
       <c r="FL3" t="n">
-        <v>0.1594229936599731</v>
+        <v>0.4004904627799988</v>
       </c>
       <c r="FM3" t="n">
-        <v>0.07111727446317673</v>
+        <v>0.1504963338375092</v>
       </c>
       <c r="FN3" t="n">
-        <v>0.07995792478322983</v>
+        <v>0.0982174351811409</v>
       </c>
       <c r="FO3" t="n">
-        <v>0.159436970949173</v>
+        <v>0.4238471984863281</v>
       </c>
       <c r="FP3" t="n">
-        <v>0.06839775294065475</v>
+        <v>0.48250812292099</v>
       </c>
       <c r="FQ3" t="n">
-        <v>0.3499903976917267</v>
+        <v>0.1609686762094498</v>
       </c>
       <c r="FR3" t="n">
-        <v>0.03112018294632435</v>
+        <v>0.0452551543712616</v>
       </c>
       <c r="FS3" t="n">
-        <v>0.200702041387558</v>
+        <v>0.01301127672195435</v>
       </c>
       <c r="FT3" t="n">
-        <v>0.1267289668321609</v>
+        <v>0.1018935590982437</v>
       </c>
       <c r="FU3" t="n">
-        <v>0.08309736102819443</v>
+        <v>0.00615309365093708</v>
       </c>
       <c r="FV3" t="n">
-        <v>0.1338207125663757</v>
+        <v>0.2195558696985245</v>
       </c>
       <c r="FW3" t="n">
-        <v>0.1316115111112595</v>
+        <v>0.161151334643364</v>
       </c>
       <c r="FX3" t="n">
-        <v>0.04730986058712006</v>
+        <v>0.1049992591142654</v>
       </c>
       <c r="FY3" t="n">
-        <v>0.1392429620027542</v>
+        <v>0.2259500622749329</v>
       </c>
       <c r="FZ3" t="n">
-        <v>0.05144687369465828</v>
+        <v>0.07876726984977722</v>
       </c>
       <c r="GA3" t="n">
-        <v>0.02406468242406845</v>
+        <v>0.0450688973069191</v>
       </c>
       <c r="GB3" t="n">
-        <v>0.02111739106476307</v>
+        <v>0.07175861299037933</v>
       </c>
       <c r="GC3" t="n">
-        <v>0.3859622776508331</v>
+        <v>0.4871550798416138</v>
       </c>
       <c r="GD3" t="n">
-        <v>0.1573798060417175</v>
+        <v>0.2907436192035675</v>
       </c>
       <c r="GE3" t="n">
-        <v>0.01981906965374947</v>
+        <v>0.09223983436822891</v>
       </c>
       <c r="GF3" t="n">
-        <v>0.02627955935895443</v>
+        <v>0.1344727277755737</v>
       </c>
       <c r="GG3" t="n">
-        <v>0.02548835426568985</v>
+        <v>0.3415894508361816</v>
       </c>
     </row>
     <row r="4">
@@ -2706,1140 +2706,1140 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>0.0002082900755340233</v>
+        <v>0.006936602760106325</v>
       </c>
       <c r="B5" t="n">
-        <v>0.002794719766825438</v>
+        <v>0.02985402941703796</v>
       </c>
       <c r="C5" t="n">
-        <v>0.000223240815103054</v>
+        <v>0.009970320388674736</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0004778216243721545</v>
+        <v>0.002490818966180086</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0004229714104440063</v>
+        <v>0.0004014018923044205</v>
       </c>
       <c r="F5" t="n">
-        <v>0.001151087577454746</v>
+        <v>0.03135279566049576</v>
       </c>
       <c r="G5" t="n">
-        <v>1.228600740432739e-05</v>
+        <v>0.003966202028095722</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0003384615120012313</v>
+        <v>0.007849641144275665</v>
       </c>
       <c r="I5" t="n">
-        <v>7.979146903380752e-05</v>
+        <v>0.006657417863607407</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0002558781707193702</v>
+        <v>0.001301958691328764</v>
       </c>
       <c r="K5" t="n">
-        <v>0.002668379107490182</v>
+        <v>0.037164356559515</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0001622683630557731</v>
+        <v>0.01202073507010937</v>
       </c>
       <c r="M5" t="n">
-        <v>0.001004836405627429</v>
+        <v>0.00680663762614131</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0006562566850334406</v>
+        <v>0.01259134709835052</v>
       </c>
       <c r="O5" t="n">
-        <v>0.001440655440092087</v>
+        <v>0.03284868225455284</v>
       </c>
       <c r="P5" t="n">
-        <v>0.0005312583525665104</v>
+        <v>0.000832316349260509</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.0004384684143587947</v>
+        <v>0.001003787619993091</v>
       </c>
       <c r="R5" t="n">
-        <v>0.0002485283475834876</v>
+        <v>0.006408156361430883</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0001547366991871968</v>
+        <v>5.294892616802827e-05</v>
       </c>
       <c r="T5" t="n">
-        <v>0.0003556305600795895</v>
+        <v>0.004663103725761175</v>
       </c>
       <c r="U5" t="n">
-        <v>0.000135377689730376</v>
+        <v>0.005817613564431667</v>
       </c>
       <c r="V5" t="n">
-        <v>0.0001895754103315994</v>
+        <v>0.01062413305044174</v>
       </c>
       <c r="W5" t="n">
-        <v>2.401218443992548e-05</v>
+        <v>0.01057752687484026</v>
       </c>
       <c r="X5" t="n">
-        <v>8.58640851220116e-06</v>
+        <v>0.005500502418726683</v>
       </c>
       <c r="Y5" t="n">
-        <v>9.706476703286171e-06</v>
+        <v>0.0009321116376668215</v>
       </c>
       <c r="Z5" t="n">
-        <v>5.678020534105599e-05</v>
+        <v>0.003297251649200916</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.000188769176020287</v>
+        <v>0.003614862915128469</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.0003285130951553583</v>
+        <v>0.0003361573326401412</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.000377191900042817</v>
+        <v>0.004717622417956591</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.0005754823796451092</v>
+        <v>0.004632412921637297</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.0001936790649779141</v>
+        <v>0.01016255468130112</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.0004351494426373392</v>
+        <v>0.01245820056647062</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.041586074279621e-05</v>
+        <v>0.007279956247657537</v>
       </c>
       <c r="AH5" t="n">
-        <v>0.000377646298147738</v>
+        <v>0.00136637850664556</v>
       </c>
       <c r="AI5" t="n">
-        <v>5.595944458036683e-05</v>
+        <v>0.02049561589956284</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.0003310299944132566</v>
+        <v>0.000432858185376972</v>
       </c>
       <c r="AK5" t="n">
-        <v>3.353185093146749e-06</v>
+        <v>0.0008171795634552836</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.0006787324673496187</v>
+        <v>0.008461541496217251</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.0001967249263543636</v>
+        <v>0.004904118366539478</v>
       </c>
       <c r="AN5" t="n">
-        <v>1.795894058886915e-05</v>
+        <v>0.005818789359182119</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.0004287046613171697</v>
+        <v>0.00308521999977529</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.0002453305933158845</v>
+        <v>0.003712145378813148</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.116241764975712e-05</v>
+        <v>0.002222528215497732</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.000121025565022137</v>
+        <v>0.00640565250068903</v>
       </c>
       <c r="AS5" t="n">
-        <v>6.039882646291517e-05</v>
+        <v>0.006636890582740307</v>
       </c>
       <c r="AT5" t="n">
-        <v>0.000380976009182632</v>
+        <v>0.001251679146662354</v>
       </c>
       <c r="AU5" t="n">
-        <v>0.001907986821606755</v>
+        <v>0.03779125213623047</v>
       </c>
       <c r="AV5" t="n">
-        <v>0.0003228698042221367</v>
+        <v>0.00778939388692379</v>
       </c>
       <c r="AW5" t="n">
-        <v>0.0001577681250637397</v>
+        <v>0.0009537795558571815</v>
       </c>
       <c r="AX5" t="n">
-        <v>0.0005399949150159955</v>
+        <v>0.01266940962523222</v>
       </c>
       <c r="AY5" t="n">
-        <v>9.502329339738935e-05</v>
+        <v>0.02071190066635609</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0.0005688645178452134</v>
+        <v>0.003787395544350147</v>
       </c>
       <c r="BA5" t="n">
-        <v>0.0001949285651789978</v>
+        <v>0.0004301037988625467</v>
       </c>
       <c r="BB5" t="n">
-        <v>9.147592936642468e-05</v>
+        <v>0.004457382950931787</v>
       </c>
       <c r="BC5" t="n">
-        <v>4.582190740620717e-05</v>
+        <v>0.002725806785747409</v>
       </c>
       <c r="BD5" t="n">
-        <v>0.0006618303013965487</v>
+        <v>0.00588690210133791</v>
       </c>
       <c r="BE5" t="n">
-        <v>0.0002089837653329596</v>
+        <v>0.007127440068870783</v>
       </c>
       <c r="BF5" t="n">
-        <v>0.0001737878628773615</v>
+        <v>9.945454075932503e-05</v>
       </c>
       <c r="BG5" t="n">
-        <v>0.0009049692889675498</v>
+        <v>0.0002521456917747855</v>
       </c>
       <c r="BH5" t="n">
-        <v>0.0008131615468300879</v>
+        <v>0.0004647249006666243</v>
       </c>
       <c r="BI5" t="n">
-        <v>0.0003774423676077276</v>
+        <v>0.003205779241397977</v>
       </c>
       <c r="BJ5" t="n">
-        <v>1.930769030877855e-06</v>
+        <v>0.006346499547362328</v>
       </c>
       <c r="BK5" t="n">
-        <v>7.538714271504432e-06</v>
+        <v>0.0006152157438918948</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.0002490611805114895</v>
+        <v>0.002587987808510661</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.0004146486171521246</v>
+        <v>0.005476295948028564</v>
       </c>
       <c r="BN5" t="n">
-        <v>2.175165718654171e-05</v>
+        <v>0.0004518822534009814</v>
       </c>
       <c r="BO5" t="n">
-        <v>0.0001065888354787603</v>
+        <v>0.004312362987548113</v>
       </c>
       <c r="BP5" t="n">
-        <v>7.506600377382711e-05</v>
+        <v>0.004074074327945709</v>
       </c>
       <c r="BQ5" t="n">
-        <v>9.304834384238347e-05</v>
+        <v>0.005539725068956614</v>
       </c>
       <c r="BR5" t="n">
-        <v>5.675471038557589e-05</v>
+        <v>0.01281827222555876</v>
       </c>
       <c r="BS5" t="n">
-        <v>0.0001002387871267274</v>
+        <v>0.001541629084385931</v>
       </c>
       <c r="BT5" t="n">
-        <v>3.244302934035659e-05</v>
+        <v>0.005474191624671221</v>
       </c>
       <c r="BU5" t="n">
-        <v>0.0003304221318103373</v>
+        <v>0.002769440645352006</v>
       </c>
       <c r="BV5" t="n">
-        <v>0.001016247435472906</v>
+        <v>0.02263796143233776</v>
       </c>
       <c r="BW5" t="n">
-        <v>7.123395334929228e-06</v>
+        <v>0.005516089964658022</v>
       </c>
       <c r="BX5" t="n">
-        <v>3.02014741464518e-05</v>
+        <v>0.01227897778153419</v>
       </c>
       <c r="BY5" t="n">
-        <v>0.0001846712839324027</v>
+        <v>0.006387664005160332</v>
       </c>
       <c r="BZ5" t="n">
-        <v>4.083658495801501e-05</v>
+        <v>0.01378374733030796</v>
       </c>
       <c r="CA5" t="n">
-        <v>0.000457172718597576</v>
+        <v>0.002931371564045548</v>
       </c>
       <c r="CB5" t="n">
-        <v>1.360670921712881e-05</v>
+        <v>0.0006855415413156152</v>
       </c>
       <c r="CC5" t="n">
-        <v>0.0001426426024409011</v>
+        <v>0.0050211101770401</v>
       </c>
       <c r="CD5" t="n">
-        <v>0.0001518621720606461</v>
+        <v>0.001336006447672844</v>
       </c>
       <c r="CE5" t="n">
-        <v>0.000471574574476108</v>
+        <v>0.01060759648680687</v>
       </c>
       <c r="CF5" t="n">
-        <v>2.047638190560974e-05</v>
+        <v>0.001424476271495223</v>
       </c>
       <c r="CG5" t="n">
-        <v>0.0002178851427743211</v>
+        <v>0.003147085197269917</v>
       </c>
       <c r="CH5" t="n">
-        <v>9.155159932561219e-05</v>
+        <v>0.000197145389392972</v>
       </c>
       <c r="CI5" t="n">
-        <v>0.0001844017242547125</v>
+        <v>0.007218839600682259</v>
       </c>
       <c r="CJ5" t="n">
-        <v>0.0002589740906842053</v>
+        <v>0.003084293799474835</v>
       </c>
       <c r="CK5" t="n">
-        <v>3.581638156902045e-05</v>
+        <v>0.001674487488344312</v>
       </c>
       <c r="CL5" t="n">
-        <v>2.183823380619287e-05</v>
+        <v>0.001919099478982389</v>
       </c>
       <c r="CM5" t="n">
-        <v>0.0002917656383942813</v>
+        <v>0.006901956163346767</v>
       </c>
       <c r="CN5" t="n">
-        <v>0.000431280757766217</v>
+        <v>0.01382935047149658</v>
       </c>
       <c r="CO5" t="n">
-        <v>0.0001687795884208754</v>
+        <v>0.009532541036605835</v>
       </c>
       <c r="CP5" t="n">
-        <v>0.000192501989658922</v>
+        <v>0.01104527153074741</v>
       </c>
       <c r="CQ5" t="n">
-        <v>2.135045906470623e-05</v>
+        <v>0.007899285294115543</v>
       </c>
       <c r="CR5" t="n">
-        <v>0.000117781077278778</v>
+        <v>0.0009288262808695436</v>
       </c>
       <c r="CS5" t="n">
-        <v>0.0005491551128216088</v>
+        <v>0.006001263856887817</v>
       </c>
       <c r="CT5" t="n">
-        <v>0.0006813568179495633</v>
+        <v>0.003004948608577251</v>
       </c>
       <c r="CU5" t="n">
-        <v>0.0002675790165085346</v>
+        <v>0.0001359271700493991</v>
       </c>
       <c r="CV5" t="n">
-        <v>0.0001422437781002373</v>
+        <v>0.0006860796129330993</v>
       </c>
       <c r="CW5" t="n">
-        <v>0.000437555048847571</v>
+        <v>0.008982865139842033</v>
       </c>
       <c r="CX5" t="n">
-        <v>3.581615601433441e-05</v>
+        <v>0.002128345659002662</v>
       </c>
       <c r="CY5" t="n">
-        <v>0.0002137717674486339</v>
+        <v>0.001807510969229043</v>
       </c>
       <c r="CZ5" t="n">
-        <v>2.033443342952523e-05</v>
+        <v>0.000829724594950676</v>
       </c>
       <c r="DA5" t="n">
-        <v>0.0002615482080727816</v>
+        <v>0.007703772746026516</v>
       </c>
       <c r="DB5" t="n">
-        <v>0.0001705103786662221</v>
+        <v>0.00168305542320013</v>
       </c>
       <c r="DC5" t="n">
-        <v>2.052093441307079e-05</v>
+        <v>0.001015527290292084</v>
       </c>
       <c r="DD5" t="n">
-        <v>1.237692777067423e-05</v>
+        <v>0.001383054303005338</v>
       </c>
       <c r="DE5" t="n">
-        <v>2.7934365789406e-06</v>
+        <v>0.005225932225584984</v>
       </c>
       <c r="DF5" t="n">
-        <v>0.0002551862853579223</v>
+        <v>0.002773816231638193</v>
       </c>
       <c r="DG5" t="n">
-        <v>0.0005999075947329402</v>
+        <v>0.005673632025718689</v>
       </c>
       <c r="DH5" t="n">
-        <v>7.099731010384858e-05</v>
+        <v>0.0008863508701324463</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.0001161374966613948</v>
+        <v>0.004365004599094391</v>
       </c>
       <c r="DJ5" t="n">
-        <v>0.0005603097379207611</v>
+        <v>0.009782792069017887</v>
       </c>
       <c r="DK5" t="n">
-        <v>0.0002789502323139459</v>
+        <v>0.002058623358607292</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.0003758782404474914</v>
+        <v>0.007963108830153942</v>
       </c>
       <c r="DM5" t="n">
-        <v>0.000217650958802551</v>
+        <v>0.00363773200660944</v>
       </c>
       <c r="DN5" t="n">
-        <v>6.709492299705744e-05</v>
+        <v>0.001139298197813332</v>
       </c>
       <c r="DO5" t="n">
-        <v>0.0003411537909414619</v>
+        <v>0.005448815878480673</v>
       </c>
       <c r="DP5" t="n">
-        <v>0.0001870730775408447</v>
+        <v>0.00107742240652442</v>
       </c>
       <c r="DQ5" t="n">
-        <v>0.0005434288759715855</v>
+        <v>0.003699838649481535</v>
       </c>
       <c r="DR5" t="n">
-        <v>2.790459620882757e-05</v>
+        <v>0.00254708924330771</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.0004795655841007829</v>
+        <v>0.003133459948003292</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.0003166988608427346</v>
+        <v>0.001232257345691323</v>
       </c>
       <c r="DU5" t="n">
-        <v>0.0003468990325927734</v>
+        <v>0.005879060830920935</v>
       </c>
       <c r="DV5" t="n">
-        <v>7.582941907458007e-05</v>
+        <v>0.003852042369544506</v>
       </c>
       <c r="DW5" t="n">
-        <v>0.0002152997476514429</v>
+        <v>0.00349118304438889</v>
       </c>
       <c r="DX5" t="n">
-        <v>0.0001184516513603739</v>
+        <v>0.002713222755119205</v>
       </c>
       <c r="DY5" t="n">
-        <v>4.961319064022973e-05</v>
+        <v>0.005438373889774084</v>
       </c>
       <c r="DZ5" t="n">
-        <v>0.0005070784827694297</v>
+        <v>0.004176985938102007</v>
       </c>
       <c r="EA5" t="n">
-        <v>0.0001701569999568164</v>
+        <v>0.00311898929066956</v>
       </c>
       <c r="EB5" t="n">
-        <v>0.0003600090858526528</v>
+        <v>0.007998204790055752</v>
       </c>
       <c r="EC5" t="n">
-        <v>0.0003093818086199462</v>
+        <v>0.0002775082248263061</v>
       </c>
       <c r="ED5" t="n">
-        <v>0.0007713304366916418</v>
+        <v>0.0009603166254237294</v>
       </c>
       <c r="EE5" t="n">
-        <v>1.135760976467282e-05</v>
+        <v>0.008004649542272091</v>
       </c>
       <c r="EF5" t="n">
-        <v>2.116583345923573e-05</v>
+        <v>9.644118836149573e-05</v>
       </c>
       <c r="EG5" t="n">
-        <v>0.0004253157530911267</v>
+        <v>0.0008112798677757382</v>
       </c>
       <c r="EH5" t="n">
-        <v>8.297751264763065e-06</v>
+        <v>0.001971459714695811</v>
       </c>
       <c r="EI5" t="n">
-        <v>0.0001124023692682385</v>
+        <v>0.008171559311449528</v>
       </c>
       <c r="EJ5" t="n">
-        <v>1.921185321407393e-05</v>
+        <v>0.004774895962327719</v>
       </c>
       <c r="EK5" t="n">
-        <v>0.0001186036242870614</v>
+        <v>0.004001837223768234</v>
       </c>
       <c r="EL5" t="n">
-        <v>0.0002726304228417575</v>
+        <v>0.0001880109484773129</v>
       </c>
       <c r="EM5" t="n">
-        <v>9.296203643316403e-05</v>
+        <v>0.0008537420071661472</v>
       </c>
       <c r="EN5" t="n">
-        <v>6.421800935640931e-05</v>
+        <v>0.001646799966692924</v>
       </c>
       <c r="EO5" t="n">
-        <v>8.646168134873733e-05</v>
+        <v>0.00080744584556669</v>
       </c>
       <c r="EP5" t="n">
-        <v>0.0003978912136517465</v>
+        <v>0.005400343332439661</v>
       </c>
       <c r="EQ5" t="n">
-        <v>0.0001483021187596023</v>
+        <v>0.003276320872828364</v>
       </c>
       <c r="ER5" t="n">
-        <v>9.493153629591689e-05</v>
+        <v>0.002542547415941954</v>
       </c>
       <c r="ES5" t="n">
-        <v>0.0005110061028972268</v>
+        <v>0.006644722539931536</v>
       </c>
       <c r="ET5" t="n">
-        <v>0.0003873752721119672</v>
+        <v>0.003003431716933846</v>
       </c>
       <c r="EU5" t="n">
-        <v>0.0001442956418031827</v>
+        <v>0.001182956388220191</v>
       </c>
       <c r="EV5" t="n">
-        <v>0.0001633807114558294</v>
+        <v>0.003108620643615723</v>
       </c>
       <c r="EW5" t="n">
-        <v>0.0002011788164963946</v>
+        <v>0.001088783843442798</v>
       </c>
       <c r="EX5" t="n">
-        <v>0.0001181679908768274</v>
+        <v>0.0006915609119459987</v>
       </c>
       <c r="EY5" t="n">
-        <v>0.0004430028493516147</v>
+        <v>0.01079641841351986</v>
       </c>
       <c r="EZ5" t="n">
-        <v>1.61291791300755e-05</v>
+        <v>0.001994568621739745</v>
       </c>
       <c r="FA5" t="n">
-        <v>0.0001403096539434046</v>
+        <v>0.001894793473184109</v>
       </c>
       <c r="FB5" t="n">
-        <v>8.291242556879297e-05</v>
+        <v>0.0009993626736104488</v>
       </c>
       <c r="FC5" t="n">
-        <v>0.0002083766303258017</v>
+        <v>0.007172694429755211</v>
       </c>
       <c r="FD5" t="n">
-        <v>0.0001803250343073159</v>
+        <v>0.003742440138012171</v>
       </c>
       <c r="FE5" t="n">
-        <v>0.0001377081352984533</v>
+        <v>0.001177566824480891</v>
       </c>
       <c r="FF5" t="n">
-        <v>3.230298170819879e-05</v>
+        <v>0.0007327677449211478</v>
       </c>
       <c r="FG5" t="n">
-        <v>9.628508269088343e-05</v>
+        <v>0.0003470857627689838</v>
       </c>
       <c r="FH5" t="n">
-        <v>0.0001775567216100171</v>
+        <v>0.009000212885439396</v>
       </c>
       <c r="FI5" t="n">
-        <v>9.126862278208137e-05</v>
+        <v>0.004896517377346754</v>
       </c>
       <c r="FJ5" t="n">
-        <v>0.0006365187000483274</v>
+        <v>0.002982528414577246</v>
       </c>
       <c r="FK5" t="n">
-        <v>0.0004576024657581002</v>
+        <v>0.00186195969581604</v>
       </c>
       <c r="FL5" t="n">
-        <v>0.0001794300478650257</v>
+        <v>0.01073563471436501</v>
       </c>
       <c r="FM5" t="n">
-        <v>0.0002918432001024485</v>
+        <v>0.005293605849146843</v>
       </c>
       <c r="FN5" t="n">
-        <v>0.0002810831356327981</v>
+        <v>0.01353620924055576</v>
       </c>
       <c r="FO5" t="n">
-        <v>0.0001681107532931492</v>
+        <v>0.009713101200759411</v>
       </c>
       <c r="FP5" t="n">
-        <v>2.841698005795479e-05</v>
+        <v>0.003312961431220174</v>
       </c>
       <c r="FQ5" t="n">
-        <v>0.001279828371480107</v>
+        <v>0.01077196933329105</v>
       </c>
       <c r="FR5" t="n">
-        <v>8.569904457544908e-05</v>
+        <v>0.005590252578258514</v>
       </c>
       <c r="FS5" t="n">
-        <v>0.0005007335566915572</v>
+        <v>0.00876634381711483</v>
       </c>
       <c r="FT5" t="n">
-        <v>0.0006501305033452809</v>
+        <v>0.003148142015561461</v>
       </c>
       <c r="FU5" t="n">
-        <v>0.0001123758192989044</v>
+        <v>0.00867646187543869</v>
       </c>
       <c r="FV5" t="n">
-        <v>0.0006877157720737159</v>
+        <v>0.001287742867134511</v>
       </c>
       <c r="FW5" t="n">
-        <v>0.0001561276440043002</v>
+        <v>0.01380895543843508</v>
       </c>
       <c r="FX5" t="n">
-        <v>0.0001644100120756775</v>
+        <v>0.007268932648003101</v>
       </c>
       <c r="FY5" t="n">
-        <v>0.0002073681826004758</v>
+        <v>0.004403283353894949</v>
       </c>
       <c r="FZ5" t="n">
-        <v>0.0004611971380654722</v>
+        <v>9.113270789384842e-05</v>
       </c>
       <c r="GA5" t="n">
-        <v>0.000391948182368651</v>
+        <v>0.007175370119512081</v>
       </c>
       <c r="GB5" t="n">
-        <v>2.379321085754782e-05</v>
+        <v>0.00193545816000551</v>
       </c>
       <c r="GC5" t="n">
-        <v>0.0002993284142576158</v>
+        <v>0.01155961211770773</v>
       </c>
       <c r="GD5" t="n">
-        <v>2.67523828370031e-05</v>
+        <v>0.009114905260503292</v>
       </c>
       <c r="GE5" t="n">
-        <v>0.0002805834519676864</v>
+        <v>0.002713073510676622</v>
       </c>
       <c r="GF5" t="n">
-        <v>6.569064862560481e-05</v>
+        <v>0.001286907587200403</v>
       </c>
       <c r="GG5" t="n">
-        <v>0.0001161560576292686</v>
+        <v>0.006585614755749702</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>0.000504637137055397</v>
+        <v>0.3109433352947235</v>
       </c>
       <c r="B6" t="n">
-        <v>0.05463951826095581</v>
+        <v>0.3904542028903961</v>
       </c>
       <c r="C6" t="n">
-        <v>0.003254338400438428</v>
+        <v>0.1200706511735916</v>
       </c>
       <c r="D6" t="n">
-        <v>0.02286634966731071</v>
+        <v>0.0938478484749794</v>
       </c>
       <c r="E6" t="n">
-        <v>0.005229020956903696</v>
+        <v>0.0147589948028326</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0454237125813961</v>
+        <v>0.3140907287597656</v>
       </c>
       <c r="G6" t="n">
-        <v>0.002133742440491915</v>
+        <v>0.05872178077697754</v>
       </c>
       <c r="H6" t="n">
-        <v>0.01511990651488304</v>
+        <v>0.1269216388463974</v>
       </c>
       <c r="I6" t="n">
-        <v>0.00101829192135483</v>
+        <v>0.08921033143997192</v>
       </c>
       <c r="J6" t="n">
-        <v>0.006521172821521759</v>
+        <v>0.2977679371833801</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0529009997844696</v>
+        <v>0.4816280901432037</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0001501943916082382</v>
+        <v>0.1496054232120514</v>
       </c>
       <c r="M6" t="n">
-        <v>0.02419457584619522</v>
+        <v>0.01861260458827019</v>
       </c>
       <c r="N6" t="n">
-        <v>0.001522162696346641</v>
+        <v>0.2070508897304535</v>
       </c>
       <c r="O6" t="n">
-        <v>0.039264976978302</v>
+        <v>0.3031727075576782</v>
       </c>
       <c r="P6" t="n">
-        <v>0.003403782611712813</v>
+        <v>0.05304598808288574</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.006819161120802164</v>
+        <v>0.02772182412445545</v>
       </c>
       <c r="R6" t="n">
-        <v>0.0007442879723384976</v>
+        <v>0.1461812257766724</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0040231728926301</v>
+        <v>0.01580441370606422</v>
       </c>
       <c r="T6" t="n">
-        <v>0.00443277508020401</v>
+        <v>0.03871703892946243</v>
       </c>
       <c r="U6" t="n">
-        <v>0.001943801529705524</v>
+        <v>0.1016645878553391</v>
       </c>
       <c r="V6" t="n">
-        <v>0.002646591747179627</v>
+        <v>0.1468660682439804</v>
       </c>
       <c r="W6" t="n">
-        <v>0.004454960580915213</v>
+        <v>0.1171129271388054</v>
       </c>
       <c r="X6" t="n">
-        <v>0.0009410034981556237</v>
+        <v>0.0815105214715004</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.001381309470161796</v>
+        <v>0.00515887513756752</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.002300333464518189</v>
+        <v>0.1216937601566315</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.005465687718242407</v>
+        <v>0.08447673916816711</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.000795160885900259</v>
+        <v>0.0397721491754055</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.002931397873908281</v>
+        <v>0.09026788175106049</v>
       </c>
       <c r="AD6" t="n">
-        <v>0.004599334206432104</v>
+        <v>0.03499977290630341</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.003993544727563858</v>
+        <v>0.1075912788510323</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.0007182041881605983</v>
+        <v>0.1903063654899597</v>
       </c>
       <c r="AG6" t="n">
-        <v>0.003846905659884214</v>
+        <v>0.03771587833762169</v>
       </c>
       <c r="AH6" t="n">
-        <v>0.002469500293955207</v>
+        <v>0.01514449715614319</v>
       </c>
       <c r="AI6" t="n">
-        <v>0.004403523169457912</v>
+        <v>0.1397756636142731</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.001008389517664909</v>
+        <v>0.04516434669494629</v>
       </c>
       <c r="AK6" t="n">
-        <v>0.001253860420547426</v>
+        <v>0.07680830359458923</v>
       </c>
       <c r="AL6" t="n">
-        <v>0.01090519782155752</v>
+        <v>0.1045944690704346</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.003614441026002169</v>
+        <v>0.1139045804738998</v>
       </c>
       <c r="AN6" t="n">
-        <v>0.0007655708468519151</v>
+        <v>0.1109361052513123</v>
       </c>
       <c r="AO6" t="n">
-        <v>0.006046996917575598</v>
+        <v>0.04747840762138367</v>
       </c>
       <c r="AP6" t="n">
-        <v>0.006326804868876934</v>
+        <v>0.03031401894986629</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0.0007479030173271894</v>
+        <v>0.06358177959918976</v>
       </c>
       <c r="AR6" t="n">
-        <v>0.004073158837854862</v>
+        <v>0.05779953300952911</v>
       </c>
       <c r="AS6" t="n">
-        <v>0.003227323526516557</v>
+        <v>0.1206374019384384</v>
       </c>
       <c r="AT6" t="n">
-        <v>0.007752323523163795</v>
+        <v>0.1711305230855942</v>
       </c>
       <c r="AU6" t="n">
-        <v>0.03662922233343124</v>
+        <v>0.3767654895782471</v>
       </c>
       <c r="AV6" t="n">
-        <v>0.004870238248258829</v>
+        <v>0.08149152994155884</v>
       </c>
       <c r="AW6" t="n">
-        <v>0.002193887019529939</v>
+        <v>0.03650206699967384</v>
       </c>
       <c r="AX6" t="n">
-        <v>0.006400733720511198</v>
+        <v>0.1211031377315521</v>
       </c>
       <c r="AY6" t="n">
-        <v>0.01954136788845062</v>
+        <v>0.09931601583957672</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0.006001229397952557</v>
+        <v>0.02457233145833015</v>
       </c>
       <c r="BA6" t="n">
-        <v>0.001113321399316192</v>
+        <v>0.01525003649294376</v>
       </c>
       <c r="BB6" t="n">
-        <v>0.004595036152750254</v>
+        <v>0.08309070020914078</v>
       </c>
       <c r="BC6" t="n">
-        <v>0.004269056022167206</v>
+        <v>0.01028556376695633</v>
       </c>
       <c r="BD6" t="n">
-        <v>0.008592568337917328</v>
+        <v>0.006017241626977921</v>
       </c>
       <c r="BE6" t="n">
-        <v>0.008174017071723938</v>
+        <v>0.09376493096351624</v>
       </c>
       <c r="BF6" t="n">
-        <v>0.003133086953312159</v>
+        <v>0.03562569618225098</v>
       </c>
       <c r="BG6" t="n">
-        <v>0.01322357356548309</v>
+        <v>0.03155959397554398</v>
       </c>
       <c r="BH6" t="n">
-        <v>0.0157051756978035</v>
+        <v>0.0897231325507164</v>
       </c>
       <c r="BI6" t="n">
-        <v>0.01080186478793621</v>
+        <v>0.05444983392953873</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.001270482782274485</v>
+        <v>0.04333667457103729</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.0001616548979654908</v>
+        <v>0.04749392345547676</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.001530060777440667</v>
+        <v>0.01365851610898972</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.0005676830187439919</v>
+        <v>0.06316989660263062</v>
       </c>
       <c r="BN6" t="n">
-        <v>0.0002663512714207172</v>
+        <v>0.01552093774080276</v>
       </c>
       <c r="BO6" t="n">
-        <v>0.003456297097727656</v>
+        <v>0.09828600287437439</v>
       </c>
       <c r="BP6" t="n">
-        <v>0.005888261832296848</v>
+        <v>0.02259377390146255</v>
       </c>
       <c r="BQ6" t="n">
-        <v>0.0006059084553271532</v>
+        <v>0.008886398747563362</v>
       </c>
       <c r="BR6" t="n">
-        <v>0.002721224911510944</v>
+        <v>0.1996787190437317</v>
       </c>
       <c r="BS6" t="n">
-        <v>0.001503307837992907</v>
+        <v>0.02681130915880203</v>
       </c>
       <c r="BT6" t="n">
-        <v>0.00176338548772037</v>
+        <v>0.05920708179473877</v>
       </c>
       <c r="BU6" t="n">
-        <v>0.006878144107758999</v>
+        <v>0.06730702519416809</v>
       </c>
       <c r="BV6" t="n">
-        <v>0.01906957663595676</v>
+        <v>0.2414781898260117</v>
       </c>
       <c r="BW6" t="n">
-        <v>0.001562613528221846</v>
+        <v>0.09117072075605392</v>
       </c>
       <c r="BX6" t="n">
-        <v>0.005277046002447605</v>
+        <v>0.1148968413472176</v>
       </c>
       <c r="BY6" t="n">
-        <v>3.157544415444136e-05</v>
+        <v>0.08234638720750809</v>
       </c>
       <c r="BZ6" t="n">
-        <v>0.00847988948225975</v>
+        <v>0.1577645987272263</v>
       </c>
       <c r="CA6" t="n">
-        <v>0.005050357431173325</v>
+        <v>0.0308174230158329</v>
       </c>
       <c r="CB6" t="n">
-        <v>0.003206705674529076</v>
+        <v>0.05365974456071854</v>
       </c>
       <c r="CC6" t="n">
-        <v>0.00557684525847435</v>
+        <v>0.1013145819306374</v>
       </c>
       <c r="CD6" t="n">
-        <v>0.001359336543828249</v>
+        <v>0.08089618384838104</v>
       </c>
       <c r="CE6" t="n">
-        <v>0.009028634056448936</v>
+        <v>0.1325742602348328</v>
       </c>
       <c r="CF6" t="n">
-        <v>0.002226232085376978</v>
+        <v>0.002246830146759748</v>
       </c>
       <c r="CG6" t="n">
-        <v>0.004653139505535364</v>
+        <v>0.03508106619119644</v>
       </c>
       <c r="CH6" t="n">
-        <v>0.001364003401249647</v>
+        <v>0.01824836246669292</v>
       </c>
       <c r="CI6" t="n">
-        <v>0.007781039923429489</v>
+        <v>0.08932101726531982</v>
       </c>
       <c r="CJ6" t="n">
-        <v>0.003454797435551882</v>
+        <v>0.07096516340970993</v>
       </c>
       <c r="CK6" t="n">
-        <v>0.001254185568541288</v>
+        <v>0.028162756934762</v>
       </c>
       <c r="CL6" t="n">
-        <v>0.002785455202683806</v>
+        <v>0.02408243343234062</v>
       </c>
       <c r="CM6" t="n">
-        <v>0.004699212033301592</v>
+        <v>0.004190541803836823</v>
       </c>
       <c r="CN6" t="n">
-        <v>3.089313395321369e-06</v>
+        <v>0.17583929002285</v>
       </c>
       <c r="CO6" t="n">
-        <v>0.0007511689327657223</v>
+        <v>0.06954492628574371</v>
       </c>
       <c r="CP6" t="n">
-        <v>0.007740950211882591</v>
+        <v>0.1229446232318878</v>
       </c>
       <c r="CQ6" t="n">
-        <v>0.0007889644475653768</v>
+        <v>0.01548556052148342</v>
       </c>
       <c r="CR6" t="n">
-        <v>0.001265142462216318</v>
+        <v>0.05444962531328201</v>
       </c>
       <c r="CS6" t="n">
-        <v>0.007861209101974964</v>
+        <v>0.05369388684630394</v>
       </c>
       <c r="CT6" t="n">
-        <v>0.01032986864447594</v>
+        <v>0.02150040306150913</v>
       </c>
       <c r="CU6" t="n">
-        <v>0.00330548663623631</v>
+        <v>0.05044877529144287</v>
       </c>
       <c r="CV6" t="n">
-        <v>0.0008981382707133889</v>
+        <v>0.06173192709684372</v>
       </c>
       <c r="CW6" t="n">
-        <v>0.008164831437170506</v>
+        <v>0.1127086207270622</v>
       </c>
       <c r="CX6" t="n">
-        <v>0.001409486052580178</v>
+        <v>0.004073357209563255</v>
       </c>
       <c r="CY6" t="n">
-        <v>0.005634348373860121</v>
+        <v>0.02149695530533791</v>
       </c>
       <c r="CZ6" t="n">
-        <v>0.0001704160531517118</v>
+        <v>0.00843949057161808</v>
       </c>
       <c r="DA6" t="n">
-        <v>0.008814130909740925</v>
+        <v>0.08905293792486191</v>
       </c>
       <c r="DB6" t="n">
-        <v>0.002924376167356968</v>
+        <v>0.0594136044383049</v>
       </c>
       <c r="DC6" t="n">
-        <v>0.002881154417991638</v>
+        <v>0.04696394130587578</v>
       </c>
       <c r="DD6" t="n">
-        <v>0.000946394691709429</v>
+        <v>0.02078212797641754</v>
       </c>
       <c r="DE6" t="n">
-        <v>0.00115019513759762</v>
+        <v>0.008207909762859344</v>
       </c>
       <c r="DF6" t="n">
-        <v>0.005999227054417133</v>
+        <v>0.04428090155124664</v>
       </c>
       <c r="DG6" t="n">
-        <v>0.002368464134633541</v>
+        <v>0.09809437394142151</v>
       </c>
       <c r="DH6" t="n">
-        <v>0.008384726010262966</v>
+        <v>0.01384932175278664</v>
       </c>
       <c r="DI6" t="n">
-        <v>0.01249940879642963</v>
+        <v>0.190258115530014</v>
       </c>
       <c r="DJ6" t="n">
-        <v>0.004305227659642696</v>
+        <v>0.06702122092247009</v>
       </c>
       <c r="DK6" t="n">
-        <v>0.005166088230907917</v>
+        <v>0.007516869343817234</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.005711513105779886</v>
+        <v>0.07567558437585831</v>
       </c>
       <c r="DM6" t="n">
-        <v>0.005512556992471218</v>
+        <v>0.09403329342603683</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.0007092040032148361</v>
+        <v>0.002236777916550636</v>
       </c>
       <c r="DO6" t="n">
-        <v>0.001107484335079789</v>
+        <v>0.08155281841754913</v>
       </c>
       <c r="DP6" t="n">
-        <v>0.0003964192001149058</v>
+        <v>0.053628820925951</v>
       </c>
       <c r="DQ6" t="n">
-        <v>0.008424215018749237</v>
+        <v>0.002611950039863586</v>
       </c>
       <c r="DR6" t="n">
-        <v>0.002452872926369309</v>
+        <v>0.04341385886073112</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.005078520625829697</v>
+        <v>0.1049815937876701</v>
       </c>
       <c r="DT6" t="n">
-        <v>0.002052052179351449</v>
+        <v>0.05917873233556747</v>
       </c>
       <c r="DU6" t="n">
-        <v>4.645483568310738e-05</v>
+        <v>0.1381116211414337</v>
       </c>
       <c r="DV6" t="n">
-        <v>0.003124230075627565</v>
+        <v>0.07303475588560104</v>
       </c>
       <c r="DW6" t="n">
-        <v>0.001360095106065273</v>
+        <v>0.05801190435886383</v>
       </c>
       <c r="DX6" t="n">
-        <v>0.001584687503054738</v>
+        <v>0.006068188697099686</v>
       </c>
       <c r="DY6" t="n">
-        <v>0.0007544099353253841</v>
+        <v>0.02039874345064163</v>
       </c>
       <c r="DZ6" t="n">
-        <v>0.004155601840466261</v>
+        <v>0.0792119950056076</v>
       </c>
       <c r="EA6" t="n">
-        <v>0.001909473678097129</v>
+        <v>0.1253336519002914</v>
       </c>
       <c r="EB6" t="n">
-        <v>0.0005539314006455243</v>
+        <v>0.1598201096057892</v>
       </c>
       <c r="EC6" t="n">
-        <v>0.003035166533663869</v>
+        <v>0.04411150515079498</v>
       </c>
       <c r="ED6" t="n">
-        <v>0.002624014392495155</v>
+        <v>0.03057195246219635</v>
       </c>
       <c r="EE6" t="n">
-        <v>0.002449675230309367</v>
+        <v>0.08677472919225693</v>
       </c>
       <c r="EF6" t="n">
-        <v>0.001126374350860715</v>
+        <v>0.07526882737874985</v>
       </c>
       <c r="EG6" t="n">
-        <v>0.00847751647233963</v>
+        <v>0.009088903665542603</v>
       </c>
       <c r="EH6" t="n">
-        <v>0.002433502813801169</v>
+        <v>0.04515765979886055</v>
       </c>
       <c r="EI6" t="n">
-        <v>0.001017187139950693</v>
+        <v>0.1552810966968536</v>
       </c>
       <c r="EJ6" t="n">
-        <v>0.002982671372592449</v>
+        <v>0.04969522356987</v>
       </c>
       <c r="EK6" t="n">
-        <v>0.006917377933859825</v>
+        <v>0.06102712824940681</v>
       </c>
       <c r="EL6" t="n">
-        <v>0.003737853607162833</v>
+        <v>0.03188572078943253</v>
       </c>
       <c r="EM6" t="n">
-        <v>0.00138885376509279</v>
+        <v>0.01046411413699389</v>
       </c>
       <c r="EN6" t="n">
-        <v>0.001480138627812266</v>
+        <v>0.04250486567616463</v>
       </c>
       <c r="EO6" t="n">
-        <v>0.001523162936791778</v>
+        <v>0.0574815571308136</v>
       </c>
       <c r="EP6" t="n">
-        <v>0.00850385706871748</v>
+        <v>0.05817146599292755</v>
       </c>
       <c r="EQ6" t="n">
-        <v>0.0001874929293990135</v>
+        <v>0.02701305598020554</v>
       </c>
       <c r="ER6" t="n">
-        <v>0.002455153036862612</v>
+        <v>0.0332767441868782</v>
       </c>
       <c r="ES6" t="n">
-        <v>0.0009827928151935339</v>
+        <v>0.03849326819181442</v>
       </c>
       <c r="ET6" t="n">
-        <v>0.01113893091678619</v>
+        <v>0.06129260361194611</v>
       </c>
       <c r="EU6" t="n">
-        <v>0.003037836868315935</v>
+        <v>0.01150978449732065</v>
       </c>
       <c r="EV6" t="n">
-        <v>0.006538667250424623</v>
+        <v>0.01829981803894043</v>
       </c>
       <c r="EW6" t="n">
-        <v>0.0003498436417430639</v>
+        <v>0.1346480399370193</v>
       </c>
       <c r="EX6" t="n">
-        <v>0.0001426069648005068</v>
+        <v>0.0829327255487442</v>
       </c>
       <c r="EY6" t="n">
-        <v>0.007918640971183777</v>
+        <v>0.1380173414945602</v>
       </c>
       <c r="EZ6" t="n">
-        <v>1.936487387865782e-05</v>
+        <v>0.009415374137461185</v>
       </c>
       <c r="FA6" t="n">
-        <v>0.004825215321034193</v>
+        <v>0.0251773726195097</v>
       </c>
       <c r="FB6" t="n">
-        <v>0.001064315438270569</v>
+        <v>0.02802847325801849</v>
       </c>
       <c r="FC6" t="n">
-        <v>0.007366949692368507</v>
+        <v>0.087265245616436</v>
       </c>
       <c r="FD6" t="n">
-        <v>0.004142727237194777</v>
+        <v>0.06829694658517838</v>
       </c>
       <c r="FE6" t="n">
-        <v>0.001261277124285698</v>
+        <v>0.0506402999162674</v>
       </c>
       <c r="FF6" t="n">
-        <v>0.002450086642056704</v>
+        <v>0.0009916564449667931</v>
       </c>
       <c r="FG6" t="n">
-        <v>0.0003561445337254554</v>
+        <v>0.02880964800715446</v>
       </c>
       <c r="FH6" t="n">
-        <v>0.001402708236128092</v>
+        <v>0.1651645004749298</v>
       </c>
       <c r="FI6" t="n">
-        <v>0.0006735087372362614</v>
+        <v>0.04328159615397453</v>
       </c>
       <c r="FJ6" t="n">
-        <v>0.008248580619692802</v>
+        <v>0.02876259386539459</v>
       </c>
       <c r="FK6" t="n">
-        <v>2.754075103439391e-05</v>
+        <v>0.06268595904111862</v>
       </c>
       <c r="FL6" t="n">
-        <v>0.001920811831951141</v>
+        <v>0.1347643136978149</v>
       </c>
       <c r="FM6" t="n">
-        <v>0.002484833123162389</v>
+        <v>0.07733617722988129</v>
       </c>
       <c r="FN6" t="n">
-        <v>0.002350443741306663</v>
+        <v>0.2525124251842499</v>
       </c>
       <c r="FO6" t="n">
-        <v>1.75024033524096e-05</v>
+        <v>0.001369550940580666</v>
       </c>
       <c r="FP6" t="n">
-        <v>0.0005258697783574462</v>
+        <v>0.0856633186340332</v>
       </c>
       <c r="FQ6" t="n">
-        <v>0.02012147940695286</v>
+        <v>0.116446927189827</v>
       </c>
       <c r="FR6" t="n">
-        <v>0.002847364405170083</v>
+        <v>0.1460136622190475</v>
       </c>
       <c r="FS6" t="n">
-        <v>0.007267260458320379</v>
+        <v>0.1247143819928169</v>
       </c>
       <c r="FT6" t="n">
-        <v>0.007235960103571415</v>
+        <v>0.08190791308879852</v>
       </c>
       <c r="FU6" t="n">
-        <v>0.003051577601581812</v>
+        <v>0.1194957420229912</v>
       </c>
       <c r="FV6" t="n">
-        <v>0.006806392688304186</v>
+        <v>0.1429886668920517</v>
       </c>
       <c r="FW6" t="n">
-        <v>0.001150179072283208</v>
+        <v>0.002800178481265903</v>
       </c>
       <c r="FX6" t="n">
-        <v>0.0003194560413248837</v>
+        <v>0.06647779792547226</v>
       </c>
       <c r="FY6" t="n">
-        <v>0.003300257725641131</v>
+        <v>0.08378825336694717</v>
       </c>
       <c r="FZ6" t="n">
-        <v>0.005373300053179264</v>
+        <v>0.05488120764493942</v>
       </c>
       <c r="GA6" t="n">
-        <v>0.0003582672798074782</v>
+        <v>0.06608037650585175</v>
       </c>
       <c r="GB6" t="n">
-        <v>0.0002865976421162486</v>
+        <v>0.08267362415790558</v>
       </c>
       <c r="GC6" t="n">
-        <v>0.01098682917654514</v>
+        <v>0.1259734034538269</v>
       </c>
       <c r="GD6" t="n">
-        <v>0.003122144844383001</v>
+        <v>0.05647977814078331</v>
       </c>
       <c r="GE6" t="n">
-        <v>0.0130847804248333</v>
+        <v>0.01664176769554615</v>
       </c>
       <c r="GF6" t="n">
-        <v>0.0002439978998154402</v>
+        <v>0.04278358444571495</v>
       </c>
       <c r="GG6" t="n">
-        <v>0.0008329841075465083</v>
+        <v>0.18397456407547</v>
       </c>
     </row>
     <row r="7">
@@ -4413,571 +4413,571 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>0.002652636729180813</v>
+        <v>0.002894115867093205</v>
       </c>
       <c r="B8" t="n">
-        <v>0.06739312410354614</v>
+        <v>0.004729354288429022</v>
       </c>
       <c r="C8" t="n">
-        <v>0.002688653534278274</v>
+        <v>6.368890171870589e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>0.007088016718626022</v>
+        <v>0.0008895921637304127</v>
       </c>
       <c r="E8" t="n">
-        <v>0.005232394672930241</v>
+        <v>0.000325626868288964</v>
       </c>
       <c r="F8" t="n">
-        <v>0.05271487683057785</v>
+        <v>0.001902847900055349</v>
       </c>
       <c r="G8" t="n">
-        <v>0.004325412213802338</v>
+        <v>0.0006192687433212996</v>
       </c>
       <c r="H8" t="n">
-        <v>0.004264402203261852</v>
+        <v>0.0008672548574395478</v>
       </c>
       <c r="I8" t="n">
-        <v>0.03083644062280655</v>
+        <v>0.0007877805619500577</v>
       </c>
       <c r="J8" t="n">
-        <v>0.005968520417809486</v>
+        <v>0.0024984001647681</v>
       </c>
       <c r="K8" t="n">
-        <v>0.06624037027359009</v>
+        <v>0.005294262431561947</v>
       </c>
       <c r="L8" t="n">
-        <v>0.002136701485142112</v>
+        <v>1.617966336198151e-05</v>
       </c>
       <c r="M8" t="n">
-        <v>0.016200827434659</v>
+        <v>0.001635558088310063</v>
       </c>
       <c r="N8" t="n">
-        <v>0.01677824929356575</v>
+        <v>0.0007757367566227913</v>
       </c>
       <c r="O8" t="n">
-        <v>0.04055270180106163</v>
+        <v>0.001948296325281262</v>
       </c>
       <c r="P8" t="n">
-        <v>0.005873911548405886</v>
+        <v>0.0002384792896918952</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.002726743929088116</v>
+        <v>2.435327041894197e-05</v>
       </c>
       <c r="R8" t="n">
-        <v>0.01548258028924465</v>
+        <v>0.001878072507679462</v>
       </c>
       <c r="S8" t="n">
-        <v>0.002491762628778815</v>
+        <v>0.0001745920890243724</v>
       </c>
       <c r="T8" t="n">
-        <v>0.0004997481591999531</v>
+        <v>0.0003005448670592159</v>
       </c>
       <c r="U8" t="n">
-        <v>0.01433118246495724</v>
+        <v>0.0005610702792182565</v>
       </c>
       <c r="V8" t="n">
-        <v>0.002126271603628993</v>
+        <v>0.0008025130955502391</v>
       </c>
       <c r="W8" t="n">
-        <v>0.005026232451200485</v>
+        <v>0.0008112482028082013</v>
       </c>
       <c r="X8" t="n">
-        <v>0.01042973715811968</v>
+        <v>0.0004834866267628968</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.0009438994457013905</v>
+        <v>0.0004467540711630136</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.004064604640007019</v>
+        <v>0.001327594160102308</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.001800136873498559</v>
+        <v>0.0003412966325413436</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.00701360497623682</v>
+        <v>0.001039544818922877</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.006060032173991203</v>
+        <v>0.0003356277011334896</v>
       </c>
       <c r="AD8" t="n">
-        <v>0.01251434255391359</v>
+        <v>0.0003619466733653098</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.003484718035906553</v>
+        <v>0.001537641626782715</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.006362833082675934</v>
+        <v>0.002328825648874044</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.003467663889750838</v>
+        <v>0.0004584901907946914</v>
       </c>
       <c r="AH8" t="n">
-        <v>0.0009897372219711542</v>
+        <v>0.0003551530826371163</v>
       </c>
       <c r="AI8" t="n">
-        <v>0.001904178410768509</v>
+        <v>0.0007060550851747394</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.004080479964613914</v>
+        <v>0.0003361853596288711</v>
       </c>
       <c r="AK8" t="n">
-        <v>0.005925879813730717</v>
+        <v>0.0008699453319422901</v>
       </c>
       <c r="AL8" t="n">
-        <v>0.003348925150930882</v>
+        <v>0.001091806800104678</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.01801459491252899</v>
+        <v>0.0006413352093659341</v>
       </c>
       <c r="AN8" t="n">
-        <v>0.0002026337606366724</v>
+        <v>0.0009301966056227684</v>
       </c>
       <c r="AO8" t="n">
-        <v>0.006447803229093552</v>
+        <v>0.0003707291907630861</v>
       </c>
       <c r="AP8" t="n">
-        <v>0.008329961448907852</v>
+        <v>0.0003266067942604423</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0.005180397536605597</v>
+        <v>0.000934744137339294</v>
       </c>
       <c r="AR8" t="n">
-        <v>0.002237850334495306</v>
+        <v>0.0006083081825636327</v>
       </c>
       <c r="AS8" t="n">
-        <v>0.003833157476037741</v>
+        <v>0.0005009946180507541</v>
       </c>
       <c r="AT8" t="n">
-        <v>0.003712733974680305</v>
+        <v>0.001759232953190804</v>
       </c>
       <c r="AU8" t="n">
-        <v>0.05160756781697273</v>
+        <v>0.003024850273504853</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.02356791868805885</v>
+        <v>0.0003154654114041477</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.005508217960596085</v>
+        <v>2.530336132622324e-06</v>
       </c>
       <c r="AX8" t="n">
-        <v>0.01696364767849445</v>
+        <v>0.001540221157483757</v>
       </c>
       <c r="AY8" t="n">
-        <v>0.0132571654394269</v>
+        <v>0.0004561640089377761</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0.00551231112331152</v>
+        <v>7.776989150443114e-06</v>
       </c>
       <c r="BA8" t="n">
-        <v>0.004239324014633894</v>
+        <v>0.0004510965954978019</v>
       </c>
       <c r="BB8" t="n">
-        <v>0.01765488088130951</v>
+        <v>0.0005328842089511454</v>
       </c>
       <c r="BC8" t="n">
-        <v>0.001531837042421103</v>
+        <v>9.871020301943645e-05</v>
       </c>
       <c r="BD8" t="n">
-        <v>0.01928171887993813</v>
+        <v>0.001331779174506664</v>
       </c>
       <c r="BE8" t="n">
-        <v>0.009936450980603695</v>
+        <v>0.0003357973182573915</v>
       </c>
       <c r="BF8" t="n">
-        <v>0.001588077750056982</v>
+        <v>0.001084426185116172</v>
       </c>
       <c r="BG8" t="n">
-        <v>0.007085882127285004</v>
+        <v>0.000615570810623467</v>
       </c>
       <c r="BH8" t="n">
-        <v>0.03368582203984261</v>
+        <v>0.001244274899363518</v>
       </c>
       <c r="BI8" t="n">
-        <v>0.0006506610661745071</v>
+        <v>0.0002267095551360399</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.004785002674907446</v>
+        <v>0.0001901884970720857</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.01058648619800806</v>
+        <v>0.0007548757130280137</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.01029995828866959</v>
+        <v>0.0001428850810043514</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.003147267270833254</v>
+        <v>0.0002438832598272711</v>
       </c>
       <c r="BN8" t="n">
-        <v>0.005620991811156273</v>
+        <v>9.939698065863922e-05</v>
       </c>
       <c r="BO8" t="n">
-        <v>0.005047039594501257</v>
+        <v>0.0002030152099905536</v>
       </c>
       <c r="BP8" t="n">
-        <v>0.005549162626266479</v>
+        <v>0.0004193125059828162</v>
       </c>
       <c r="BQ8" t="n">
-        <v>0.001709785778075457</v>
+        <v>0.0004932644078508019</v>
       </c>
       <c r="BR8" t="n">
-        <v>0.007906483486294746</v>
+        <v>0.001362651353701949</v>
       </c>
       <c r="BS8" t="n">
-        <v>0.007137001492083073</v>
+        <v>0.0007085804827511311</v>
       </c>
       <c r="BT8" t="n">
-        <v>0.002864734269678593</v>
+        <v>0.0007373418193310499</v>
       </c>
       <c r="BU8" t="n">
-        <v>0.003029973246157169</v>
+        <v>0.0007978571811690927</v>
       </c>
       <c r="BV8" t="n">
-        <v>0.02299295179545879</v>
+        <v>0.002175137167796493</v>
       </c>
       <c r="BW8" t="n">
-        <v>0.0178394503891468</v>
+        <v>0.0004219503316562623</v>
       </c>
       <c r="BX8" t="n">
-        <v>0.005662047769874334</v>
+        <v>0.0005466725560836494</v>
       </c>
       <c r="BY8" t="n">
-        <v>0.01118534337729216</v>
+        <v>9.970631799660623e-05</v>
       </c>
       <c r="BZ8" t="n">
-        <v>0.0003731378819793463</v>
+        <v>0.00122281932272017</v>
       </c>
       <c r="CA8" t="n">
-        <v>0.005000995472073555</v>
+        <v>0.0003447361523285508</v>
       </c>
       <c r="CB8" t="n">
-        <v>0.001924503361806273</v>
+        <v>0.0001474631135351956</v>
       </c>
       <c r="CC8" t="n">
-        <v>0.00610068254172802</v>
+        <v>0.0005245475331321359</v>
       </c>
       <c r="CD8" t="n">
-        <v>0.0001785983331501484</v>
+        <v>0.0006540153408423066</v>
       </c>
       <c r="CE8" t="n">
-        <v>0.01043236628174782</v>
+        <v>0.001367176068015397</v>
       </c>
       <c r="CF8" t="n">
-        <v>0.003790696384385228</v>
+        <v>0.0001989737065741792</v>
       </c>
       <c r="CG8" t="n">
-        <v>0.0009439175482839346</v>
+        <v>0.0002996456169057637</v>
       </c>
       <c r="CH8" t="n">
-        <v>0.0005470699397847056</v>
+        <v>0.0001409006072208285</v>
       </c>
       <c r="CI8" t="n">
-        <v>0.01209590211510658</v>
+        <v>0.0006533358246088028</v>
       </c>
       <c r="CJ8" t="n">
-        <v>0.002134151756763458</v>
+        <v>0.0004354012198746204</v>
       </c>
       <c r="CK8" t="n">
-        <v>0.003123276634141803</v>
+        <v>0.0002222936600446701</v>
       </c>
       <c r="CL8" t="n">
-        <v>0.0003260553348809481</v>
+        <v>0.0002514796215109527</v>
       </c>
       <c r="CM8" t="n">
-        <v>0.004473192617297173</v>
+        <v>0.0002313207369297743</v>
       </c>
       <c r="CN8" t="n">
-        <v>0.01255025807768106</v>
+        <v>0.002080413280054927</v>
       </c>
       <c r="CO8" t="n">
-        <v>0.001504850341007113</v>
+        <v>0.0004202261916361749</v>
       </c>
       <c r="CP8" t="n">
-        <v>0.01084636710584164</v>
+        <v>0.001215395284816623</v>
       </c>
       <c r="CQ8" t="n">
-        <v>0.002218380803242326</v>
+        <v>0.0001301137963309884</v>
       </c>
       <c r="CR8" t="n">
-        <v>0.002053875476121902</v>
+        <v>0.001421953900717199</v>
       </c>
       <c r="CS8" t="n">
-        <v>0.001147238188423216</v>
+        <v>0.0001586032740306109</v>
       </c>
       <c r="CT8" t="n">
-        <v>0.01597845368087292</v>
+        <v>0.0003828410990536213</v>
       </c>
       <c r="CU8" t="n">
-        <v>0.01058419700711966</v>
+        <v>0.0002000355161726475</v>
       </c>
       <c r="CV8" t="n">
-        <v>0.0004213873180560768</v>
+        <v>0.000512237602379173</v>
       </c>
       <c r="CW8" t="n">
-        <v>0.009806368499994278</v>
+        <v>0.001290771644562483</v>
       </c>
       <c r="CX8" t="n">
-        <v>0.00525091215968132</v>
+        <v>0.0002655818534549326</v>
       </c>
       <c r="CY8" t="n">
-        <v>0.0001895808964036405</v>
+        <v>0.0002687678788788617</v>
       </c>
       <c r="CZ8" t="n">
-        <v>0.0008616666309535503</v>
+        <v>0.000120173193863593</v>
       </c>
       <c r="DA8" t="n">
-        <v>0.01142170187085867</v>
+        <v>0.0006169433472678065</v>
       </c>
       <c r="DB8" t="n">
-        <v>0.0008667994989082217</v>
+        <v>0.0002115643001161516</v>
       </c>
       <c r="DC8" t="n">
-        <v>0.002206546254456043</v>
+        <v>0.0005320296040736139</v>
       </c>
       <c r="DD8" t="n">
-        <v>0.002411033725365996</v>
+        <v>0.0002380370569881052</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.002283165929839015</v>
+        <v>0.0004543624527286738</v>
       </c>
       <c r="DF8" t="n">
-        <v>0.008151921443641186</v>
+        <v>0.0006625362439081073</v>
       </c>
       <c r="DG8" t="n">
-        <v>0.006799660623073578</v>
+        <v>0.0005140674766153097</v>
       </c>
       <c r="DH8" t="n">
-        <v>0.002018313854932785</v>
+        <v>0.0003138642059639096</v>
       </c>
       <c r="DI8" t="n">
-        <v>0.02832826972007751</v>
+        <v>0.002670093439519405</v>
       </c>
       <c r="DJ8" t="n">
-        <v>0.01318630110472441</v>
+        <v>0.0003838990232907236</v>
       </c>
       <c r="DK8" t="n">
-        <v>3.075751010328531e-05</v>
+        <v>0.0001881488133221865</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.006451849825680256</v>
+        <v>6.444944301620126e-05</v>
       </c>
       <c r="DM8" t="n">
-        <v>0.0119355283677578</v>
+        <v>0.0005377706838771701</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.004642294719815254</v>
+        <v>0.0002214238047599792</v>
       </c>
       <c r="DO8" t="n">
-        <v>0.0006841002032160759</v>
+        <v>0.0008755353046581149</v>
       </c>
       <c r="DP8" t="n">
-        <v>0.0005270250840112567</v>
+        <v>0.0004330112424213439</v>
       </c>
       <c r="DQ8" t="n">
-        <v>2.233870327472687e-05</v>
+        <v>0.0001875224261311814</v>
       </c>
       <c r="DR8" t="n">
-        <v>0.0001223336439579725</v>
+        <v>0.0004297126142773777</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.00562827754765749</v>
+        <v>0.001131746452301741</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.00333117600530386</v>
+        <v>2.556228719186038e-05</v>
       </c>
       <c r="DU8" t="n">
-        <v>0.008521136827766895</v>
+        <v>0.00127157848328352</v>
       </c>
       <c r="DV8" t="n">
-        <v>0.006355581805109978</v>
+        <v>0.0003870294312946498</v>
       </c>
       <c r="DW8" t="n">
-        <v>0.0004646774614229798</v>
+        <v>0.0007104147225618362</v>
       </c>
       <c r="DX8" t="n">
-        <v>0.003119473345577717</v>
+        <v>0.0003362573334015906</v>
       </c>
       <c r="DY8" t="n">
-        <v>0.01046782359480858</v>
+        <v>0.0001773957192199305</v>
       </c>
       <c r="DZ8" t="n">
-        <v>0.0003586282255128026</v>
+        <v>0.0009584142826497555</v>
       </c>
       <c r="EA8" t="n">
-        <v>0.000726181548088789</v>
+        <v>0.0005567085463553667</v>
       </c>
       <c r="EB8" t="n">
-        <v>0.003090072423219681</v>
+        <v>0.0005469651077874005</v>
       </c>
       <c r="EC8" t="n">
-        <v>0.0006167686078697443</v>
+        <v>0.0004058516642544419</v>
       </c>
       <c r="ED8" t="n">
-        <v>0.0108023677021265</v>
+        <v>0.0005426153657026589</v>
       </c>
       <c r="EE8" t="n">
-        <v>0.002765540732070804</v>
+        <v>0.0006087283254601061</v>
       </c>
       <c r="EF8" t="n">
-        <v>0.00154106121044606</v>
+        <v>0.0005161052104085684</v>
       </c>
       <c r="EG8" t="n">
-        <v>0.01378062553703785</v>
+        <v>0.000320154707878828</v>
       </c>
       <c r="EH8" t="n">
-        <v>0.005746988579630852</v>
+        <v>0.0006317577790468931</v>
       </c>
       <c r="EI8" t="n">
-        <v>0.003883043071255088</v>
+        <v>0.0003982923808507621</v>
       </c>
       <c r="EJ8" t="n">
-        <v>0.006337877828627825</v>
+        <v>0.0002572466328274459</v>
       </c>
       <c r="EK8" t="n">
-        <v>0.006987164262682199</v>
+        <v>0.0002080903796013445</v>
       </c>
       <c r="EL8" t="n">
-        <v>0.0008101174607872963</v>
+        <v>0.0001554795453557745</v>
       </c>
       <c r="EM8" t="n">
-        <v>0.002559755463153124</v>
+        <v>0.000302304862998426</v>
       </c>
       <c r="EN8" t="n">
-        <v>0.0006365561857819557</v>
+        <v>6.601819768548012e-05</v>
       </c>
       <c r="EO8" t="n">
-        <v>0.005769950337707996</v>
+        <v>0.0006989429239183664</v>
       </c>
       <c r="EP8" t="n">
-        <v>0.01238404586911201</v>
+        <v>0.0006596260354854167</v>
       </c>
       <c r="EQ8" t="n">
-        <v>0.01379037089645863</v>
+        <v>0.0004590067255776376</v>
       </c>
       <c r="ER8" t="n">
-        <v>0.00426179775968194</v>
+        <v>0.0001910033461172134</v>
       </c>
       <c r="ES8" t="n">
-        <v>0.009523968212306499</v>
+        <v>0.0004577887884806842</v>
       </c>
       <c r="ET8" t="n">
-        <v>0.01103894971311092</v>
+        <v>0.00128916569519788</v>
       </c>
       <c r="EU8" t="n">
-        <v>0.004219100810587406</v>
+        <v>0.0001412163983331993</v>
       </c>
       <c r="EV8" t="n">
-        <v>0.003241570666432381</v>
+        <v>0.0003604721277952194</v>
       </c>
       <c r="EW8" t="n">
-        <v>0.0007816608995199203</v>
+        <v>0.001131182536482811</v>
       </c>
       <c r="EX8" t="n">
-        <v>0.0008427713182754815</v>
+        <v>0.0006697424687445164</v>
       </c>
       <c r="EY8" t="n">
-        <v>0.008908870629966259</v>
+        <v>0.001520217047072947</v>
       </c>
       <c r="EZ8" t="n">
-        <v>0.007243645377457142</v>
+        <v>0.0001604363205842674</v>
       </c>
       <c r="FA8" t="n">
-        <v>0.002424194477498531</v>
+        <v>0.0003432354133110493</v>
       </c>
       <c r="FB8" t="n">
-        <v>0.004042447078973055</v>
+        <v>0.0002529031771700829</v>
       </c>
       <c r="FC8" t="n">
-        <v>0.01094430685043335</v>
+        <v>0.0005577302654273808</v>
       </c>
       <c r="FD8" t="n">
-        <v>0.0009364272700622678</v>
+        <v>0.0003782642015721649</v>
       </c>
       <c r="FE8" t="n">
-        <v>0.003971600905060768</v>
+        <v>0.000437430280726403</v>
       </c>
       <c r="FF8" t="n">
-        <v>0.001671631587669253</v>
+        <v>3.464734618319198e-05</v>
       </c>
       <c r="FG8" t="n">
-        <v>0.00034622463863343</v>
+        <v>9.209140989696607e-05</v>
       </c>
       <c r="FH8" t="n">
-        <v>0.0009106225916184485</v>
+        <v>0.001351266633719206</v>
       </c>
       <c r="FI8" t="n">
-        <v>0.01490545179694891</v>
+        <v>0.0004328223003540188</v>
       </c>
       <c r="FJ8" t="n">
-        <v>0.002197072841227055</v>
+        <v>0.0001681662688497454</v>
       </c>
       <c r="FK8" t="n">
-        <v>0.003478629980236292</v>
+        <v>1.738769060466439e-05</v>
       </c>
       <c r="FL8" t="n">
-        <v>0.004613383207470179</v>
+        <v>0.001220890204422176</v>
       </c>
       <c r="FM8" t="n">
-        <v>0.006046129390597343</v>
+        <v>0.0005211932002566755</v>
       </c>
       <c r="FN8" t="n">
-        <v>0.007464773952960968</v>
+        <v>0.001100882072933018</v>
       </c>
       <c r="FO8" t="n">
-        <v>0.003146441886201501</v>
+        <v>0.0001679742708802223</v>
       </c>
       <c r="FP8" t="n">
-        <v>0.009221919812262058</v>
+        <v>0.001308410428464413</v>
       </c>
       <c r="FQ8" t="n">
-        <v>0.01648552156984806</v>
+        <v>0.001218833378516138</v>
       </c>
       <c r="FR8" t="n">
-        <v>0.01158611942082644</v>
+        <v>0.001555999158881605</v>
       </c>
       <c r="FS8" t="n">
-        <v>0.00984322652220726</v>
+        <v>0.001450055511668324</v>
       </c>
       <c r="FT8" t="n">
-        <v>0.004529838915914297</v>
+        <v>9.870942449197173e-05</v>
       </c>
       <c r="FU8" t="n">
-        <v>0.01018866337835789</v>
+        <v>0.001113242702558637</v>
       </c>
       <c r="FV8" t="n">
-        <v>0.004812535364180803</v>
+        <v>0.0005850832676514983</v>
       </c>
       <c r="FW8" t="n">
-        <v>0.002651179907843471</v>
+        <v>0.000947693653870374</v>
       </c>
       <c r="FX8" t="n">
-        <v>0.009207366034388542</v>
+        <v>0.0002632676041685045</v>
       </c>
       <c r="FY8" t="n">
-        <v>0.005168812349438667</v>
+        <v>0.0007594358758069575</v>
       </c>
       <c r="FZ8" t="n">
-        <v>0.01312101632356644</v>
+        <v>0.0002071862254524603</v>
       </c>
       <c r="GA8" t="n">
-        <v>0.003717937972396612</v>
+        <v>0.0004524902324192226</v>
       </c>
       <c r="GB8" t="n">
-        <v>0.007101589348167181</v>
+        <v>0.0004002894856967032</v>
       </c>
       <c r="GC8" t="n">
-        <v>0.006219105795025826</v>
+        <v>0.0001457239704905078</v>
       </c>
       <c r="GD8" t="n">
-        <v>0.002413665410131216</v>
+        <v>0.0004955133772455156</v>
       </c>
       <c r="GE8" t="n">
-        <v>0.0113673098385334</v>
+        <v>0.0003035855188500136</v>
       </c>
       <c r="GF8" t="n">
-        <v>0.0007992021273821592</v>
+        <v>0.0008187919738702476</v>
       </c>
       <c r="GG8" t="n">
-        <v>0.005028850864619017</v>
+        <v>0.001117806765250862</v>
       </c>
     </row>
     <row r="9">
@@ -5551,2278 +5551,2278 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>0.05010054260492325</v>
+        <v>0.002273491583764553</v>
       </c>
       <c r="B10" t="n">
-        <v>0.1802141815423965</v>
+        <v>0.02984588220715523</v>
       </c>
       <c r="C10" t="n">
-        <v>0.0243929959833622</v>
+        <v>0.006810718681663275</v>
       </c>
       <c r="D10" t="n">
-        <v>0.06073007360100746</v>
+        <v>0.004317764192819595</v>
       </c>
       <c r="E10" t="n">
-        <v>0.1149530485272408</v>
+        <v>0.003866888582706451</v>
       </c>
       <c r="F10" t="n">
-        <v>0.2585989832878113</v>
+        <v>0.03611762821674347</v>
       </c>
       <c r="G10" t="n">
-        <v>0.01384912431240082</v>
+        <v>0.00537501135841012</v>
       </c>
       <c r="H10" t="n">
-        <v>0.1173493936657906</v>
+        <v>0.03339570015668869</v>
       </c>
       <c r="I10" t="n">
-        <v>0.01579966209828854</v>
+        <v>0.005472310818731785</v>
       </c>
       <c r="J10" t="n">
-        <v>0.03471208363771439</v>
+        <v>0.0006026634946465492</v>
       </c>
       <c r="K10" t="n">
-        <v>0.1606845855712891</v>
+        <v>0.03224135190248489</v>
       </c>
       <c r="L10" t="n">
-        <v>0.01300339121371508</v>
+        <v>0.006325055845081806</v>
       </c>
       <c r="M10" t="n">
-        <v>0.0410824827849865</v>
+        <v>0.0072965775616467</v>
       </c>
       <c r="N10" t="n">
-        <v>0.01526932884007692</v>
+        <v>0.01499124430119991</v>
       </c>
       <c r="O10" t="n">
-        <v>0.1740654557943344</v>
+        <v>0.02755269408226013</v>
       </c>
       <c r="P10" t="n">
-        <v>0.00681735947728157</v>
+        <v>0.002433540998026729</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.1137329638004303</v>
+        <v>0.03707949444651604</v>
       </c>
       <c r="R10" t="n">
-        <v>0.01019987836480141</v>
+        <v>0.01088549010455608</v>
       </c>
       <c r="S10" t="n">
-        <v>0.003223574254661798</v>
+        <v>0.002107394859194756</v>
       </c>
       <c r="T10" t="n">
-        <v>0.01244623959064484</v>
+        <v>0.01009202934801579</v>
       </c>
       <c r="U10" t="n">
-        <v>0.03447432443499565</v>
+        <v>0.002456313464790583</v>
       </c>
       <c r="V10" t="n">
-        <v>0.04273094609379768</v>
+        <v>0.009356120601296425</v>
       </c>
       <c r="W10" t="n">
-        <v>0.05531677976250648</v>
+        <v>0.009116384200751781</v>
       </c>
       <c r="X10" t="n">
-        <v>0.02046337723731995</v>
+        <v>0.00279590766876936</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.0234161764383316</v>
+        <v>0.0004783007316291332</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.01724779047071934</v>
+        <v>0.006063231267035007</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.01196597330272198</v>
+        <v>0.002142792101949453</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.005229794885963202</v>
+        <v>0.00734466128051281</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.01516942121088505</v>
+        <v>0.003649091580882668</v>
       </c>
       <c r="AD10" t="n">
-        <v>0.01836475916206837</v>
+        <v>0.0003855130635201931</v>
       </c>
       <c r="AE10" t="n">
-        <v>0.009845980443060398</v>
+        <v>0.01920389011502266</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.02151064202189445</v>
+        <v>0.01513381022959948</v>
       </c>
       <c r="AG10" t="n">
-        <v>0.04262971132993698</v>
+        <v>0.001991261960938573</v>
       </c>
       <c r="AH10" t="n">
-        <v>0.05289676785469055</v>
+        <v>0.008555391803383827</v>
       </c>
       <c r="AI10" t="n">
-        <v>0.02340554445981979</v>
+        <v>0.006818171590566635</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0.004707520827651024</v>
+        <v>0.005770208779722452</v>
       </c>
       <c r="AK10" t="n">
-        <v>0.0002417159266769886</v>
+        <v>0.002885672030970454</v>
       </c>
       <c r="AL10" t="n">
-        <v>0.02509762346744537</v>
+        <v>0.007752422243356705</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.01665387861430645</v>
+        <v>0.006030667573213577</v>
       </c>
       <c r="AN10" t="n">
-        <v>0.01739405654370785</v>
+        <v>0.005985141266137362</v>
       </c>
       <c r="AO10" t="n">
-        <v>0.02359260991215706</v>
+        <v>0.01730041764676571</v>
       </c>
       <c r="AP10" t="n">
-        <v>0.05188065022230148</v>
+        <v>0.01906939037144184</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0.008051746524870396</v>
+        <v>0.008729944936931133</v>
       </c>
       <c r="AR10" t="n">
-        <v>0.03541825711727142</v>
+        <v>0.01111702062189579</v>
       </c>
       <c r="AS10" t="n">
-        <v>0.01051714271306992</v>
+        <v>0.006005969829857349</v>
       </c>
       <c r="AT10" t="n">
-        <v>0.0354861319065094</v>
+        <v>0.004235920961946249</v>
       </c>
       <c r="AU10" t="n">
-        <v>0.0714767798781395</v>
+        <v>0.0443759560585022</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.002062596380710602</v>
+        <v>0.00679801544174552</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.006039186846464872</v>
+        <v>0.002804394578561187</v>
       </c>
       <c r="AX10" t="n">
-        <v>0.1025348082184792</v>
+        <v>0.01391686871647835</v>
       </c>
       <c r="AY10" t="n">
-        <v>0.173352912068367</v>
+        <v>0.01249622832983732</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0.02209295704960823</v>
+        <v>0.001627281541004777</v>
       </c>
       <c r="BA10" t="n">
-        <v>0.04620678350329399</v>
+        <v>0.004061417654156685</v>
       </c>
       <c r="BB10" t="n">
-        <v>0.02951007336378098</v>
+        <v>0.01213298831135035</v>
       </c>
       <c r="BC10" t="n">
-        <v>0.002136267954483628</v>
+        <v>0.004189358092844486</v>
       </c>
       <c r="BD10" t="n">
-        <v>0.05710870400071144</v>
+        <v>0.03742020577192307</v>
       </c>
       <c r="BE10" t="n">
-        <v>0.0113301994279027</v>
+        <v>0.01158003509044647</v>
       </c>
       <c r="BF10" t="n">
-        <v>0.05353956669569016</v>
+        <v>0.003949129953980446</v>
       </c>
       <c r="BG10" t="n">
-        <v>0.05842079967260361</v>
+        <v>0.04445375874638557</v>
       </c>
       <c r="BH10" t="n">
-        <v>0.02985000796616077</v>
+        <v>0.007641582749783993</v>
       </c>
       <c r="BI10" t="n">
-        <v>0.01166858244687319</v>
+        <v>0.002037228550761938</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.007488276809453964</v>
+        <v>0.001054987777024508</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.002180315554141998</v>
+        <v>0.002342045539990067</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.01463192049413919</v>
+        <v>0.003263122867792845</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.04185269773006439</v>
+        <v>0.003847088199108839</v>
       </c>
       <c r="BN10" t="n">
-        <v>0.02744554542005062</v>
+        <v>0.009990593418478966</v>
       </c>
       <c r="BO10" t="n">
-        <v>0.0003274241462349892</v>
+        <v>0.004965721163898706</v>
       </c>
       <c r="BP10" t="n">
-        <v>0.01995084621012211</v>
+        <v>0.003756799967959523</v>
       </c>
       <c r="BQ10" t="n">
-        <v>0.00207554129883647</v>
+        <v>0.005303042009472847</v>
       </c>
       <c r="BR10" t="n">
-        <v>0.03080199658870697</v>
+        <v>0.0002808854915201664</v>
       </c>
       <c r="BS10" t="n">
-        <v>0.0401662290096283</v>
+        <v>0.01207169145345688</v>
       </c>
       <c r="BT10" t="n">
-        <v>0.02679943293333054</v>
+        <v>0.002645853906869888</v>
       </c>
       <c r="BU10" t="n">
-        <v>0.02398391626775265</v>
+        <v>0.003210074966773391</v>
       </c>
       <c r="BV10" t="n">
-        <v>0.05880873277783394</v>
+        <v>0.02999623119831085</v>
       </c>
       <c r="BW10" t="n">
-        <v>0.01243611052632332</v>
+        <v>0.0005372690502554178</v>
       </c>
       <c r="BX10" t="n">
-        <v>0.01191670820116997</v>
+        <v>0.01028263941407204</v>
       </c>
       <c r="BY10" t="n">
-        <v>0.04381785914301872</v>
+        <v>0.007539786398410797</v>
       </c>
       <c r="BZ10" t="n">
-        <v>0.05791015177965164</v>
+        <v>0.01549440901726484</v>
       </c>
       <c r="CA10" t="n">
-        <v>0.007305124774575233</v>
+        <v>0.009911099448800087</v>
       </c>
       <c r="CB10" t="n">
-        <v>0.03677251189947128</v>
+        <v>0.003280499018728733</v>
       </c>
       <c r="CC10" t="n">
-        <v>0.01695580221712589</v>
+        <v>0.002553232712671161</v>
       </c>
       <c r="CD10" t="n">
-        <v>0.0004844912327826023</v>
+        <v>0.002207031939178705</v>
       </c>
       <c r="CE10" t="n">
-        <v>0.02394809387624264</v>
+        <v>0.01296084187924862</v>
       </c>
       <c r="CF10" t="n">
-        <v>0.006454151123762131</v>
+        <v>0.006422552280128002</v>
       </c>
       <c r="CG10" t="n">
-        <v>0.01556295901536942</v>
+        <v>0.00449356809258461</v>
       </c>
       <c r="CH10" t="n">
-        <v>0.01443103700876236</v>
+        <v>0.005305559374392033</v>
       </c>
       <c r="CI10" t="n">
-        <v>0.04120505973696709</v>
+        <v>0.01025610417127609</v>
       </c>
       <c r="CJ10" t="n">
-        <v>0.002903812564909458</v>
+        <v>0.0007474401500076056</v>
       </c>
       <c r="CK10" t="n">
-        <v>0.01454339735209942</v>
+        <v>0.006555983796715736</v>
       </c>
       <c r="CL10" t="n">
-        <v>0.005499542690813541</v>
+        <v>0.003115908708423376</v>
       </c>
       <c r="CM10" t="n">
-        <v>0.010697141289711</v>
+        <v>0.001033084001392126</v>
       </c>
       <c r="CN10" t="n">
-        <v>0.02448084950447083</v>
+        <v>0.002911231247708201</v>
       </c>
       <c r="CO10" t="n">
-        <v>0.0009741820394992828</v>
+        <v>0.01136076077818871</v>
       </c>
       <c r="CP10" t="n">
-        <v>0.0196709930896759</v>
+        <v>0.0189142394810915</v>
       </c>
       <c r="CQ10" t="n">
-        <v>0.07498577982187271</v>
+        <v>0.0411713495850563</v>
       </c>
       <c r="CR10" t="n">
-        <v>0.02115566283464432</v>
+        <v>0.005192844197154045</v>
       </c>
       <c r="CS10" t="n">
-        <v>0.02392587251961231</v>
+        <v>0.001307155005633831</v>
       </c>
       <c r="CT10" t="n">
-        <v>0.02300279960036278</v>
+        <v>0.01447322685271502</v>
       </c>
       <c r="CU10" t="n">
-        <v>0.03985200822353363</v>
+        <v>0.002511952538043261</v>
       </c>
       <c r="CV10" t="n">
-        <v>0.00189406331628561</v>
+        <v>0.001393322600051761</v>
       </c>
       <c r="CW10" t="n">
-        <v>0.01830931566655636</v>
+        <v>0.01060137525200844</v>
       </c>
       <c r="CX10" t="n">
-        <v>0.007322821766138077</v>
+        <v>0.005433207377791405</v>
       </c>
       <c r="CY10" t="n">
-        <v>0.01860015466809273</v>
+        <v>0.002152735367417336</v>
       </c>
       <c r="CZ10" t="n">
-        <v>0.02261624671518803</v>
+        <v>0.004803180694580078</v>
       </c>
       <c r="DA10" t="n">
-        <v>0.05054856091737747</v>
+        <v>0.009703412652015686</v>
       </c>
       <c r="DB10" t="n">
-        <v>0.002935250755399466</v>
+        <v>0.0003963857889175415</v>
       </c>
       <c r="DC10" t="n">
-        <v>0.02861518226563931</v>
+        <v>0.004241845570504665</v>
       </c>
       <c r="DD10" t="n">
-        <v>0.008293286897242069</v>
+        <v>0.001715249964036047</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.01932800561189651</v>
+        <v>0.01071297563612461</v>
       </c>
       <c r="DF10" t="n">
-        <v>0.09607860445976257</v>
+        <v>0.02629592455923557</v>
       </c>
       <c r="DG10" t="n">
-        <v>0.006615751888602972</v>
+        <v>0.007635163608938456</v>
       </c>
       <c r="DH10" t="n">
-        <v>0.05261856690049171</v>
+        <v>0.01416412927210331</v>
       </c>
       <c r="DI10" t="n">
-        <v>0.1199826672673225</v>
+        <v>0.02048399299383163</v>
       </c>
       <c r="DJ10" t="n">
-        <v>0.05551708489656448</v>
+        <v>0.01142862811684608</v>
       </c>
       <c r="DK10" t="n">
-        <v>0.02908401563763618</v>
+        <v>0.005911578889936209</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.06651142984628677</v>
+        <v>0.002766585908830166</v>
       </c>
       <c r="DM10" t="n">
-        <v>0.07002340257167816</v>
+        <v>0.02360009215772152</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.01487570814788342</v>
+        <v>0.005202984903007746</v>
       </c>
       <c r="DO10" t="n">
-        <v>0.008005101233720779</v>
+        <v>0.001845447812229395</v>
       </c>
       <c r="DP10" t="n">
-        <v>0.01580097712576389</v>
+        <v>0.000744371791370213</v>
       </c>
       <c r="DQ10" t="n">
-        <v>0.03945307433605194</v>
+        <v>0.005678063258528709</v>
       </c>
       <c r="DR10" t="n">
-        <v>0.0101240761578083</v>
+        <v>0.003294672584161162</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.006219036877155304</v>
+        <v>0.004031170159578323</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.01408953778445721</v>
+        <v>0.0007673398358747363</v>
       </c>
       <c r="DU10" t="n">
-        <v>0.04724057763814926</v>
+        <v>0.0008995876414701343</v>
       </c>
       <c r="DV10" t="n">
-        <v>0.003213003743439913</v>
+        <v>0.002459642942994833</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.007574032992124557</v>
+        <v>0.008092328906059265</v>
       </c>
       <c r="DX10" t="n">
-        <v>0.01015944220125675</v>
+        <v>0.002840810688212514</v>
       </c>
       <c r="DY10" t="n">
-        <v>0.01684890501201153</v>
+        <v>0.006436399649828672</v>
       </c>
       <c r="DZ10" t="n">
-        <v>0.005439765751361847</v>
+        <v>0.02112436480820179</v>
       </c>
       <c r="EA10" t="n">
-        <v>0.05859214439988136</v>
+        <v>0.005751339718699455</v>
       </c>
       <c r="EB10" t="n">
-        <v>0.02175805903971195</v>
+        <v>0.003411931218579412</v>
       </c>
       <c r="EC10" t="n">
-        <v>0.003870476270094514</v>
+        <v>0.003432061057537794</v>
       </c>
       <c r="ED10" t="n">
-        <v>0.02814658731222153</v>
+        <v>0.008767749182879925</v>
       </c>
       <c r="EE10" t="n">
-        <v>0.04296909272670746</v>
+        <v>0.01448719948530197</v>
       </c>
       <c r="EF10" t="n">
-        <v>0.01832010969519615</v>
+        <v>0.001267440267838538</v>
       </c>
       <c r="EG10" t="n">
-        <v>0.01204453688114882</v>
+        <v>0.006184608675539494</v>
       </c>
       <c r="EH10" t="n">
-        <v>0.010656981728971</v>
+        <v>0.003483615582808852</v>
       </c>
       <c r="EI10" t="n">
-        <v>0.004656897857785225</v>
+        <v>0.00262763979844749</v>
       </c>
       <c r="EJ10" t="n">
-        <v>0.03267782181501389</v>
+        <v>0.008383974432945251</v>
       </c>
       <c r="EK10" t="n">
-        <v>0.04640111699700356</v>
+        <v>0.001263652578927577</v>
       </c>
       <c r="EL10" t="n">
-        <v>0.00499300379306078</v>
+        <v>0.006693513132631779</v>
       </c>
       <c r="EM10" t="n">
-        <v>0.01509466487914324</v>
+        <v>0.01009940076619387</v>
       </c>
       <c r="EN10" t="n">
-        <v>0.006421090103685856</v>
+        <v>0.003023954574018717</v>
       </c>
       <c r="EO10" t="n">
-        <v>0.002144591882824898</v>
+        <v>0.004739109426736832</v>
       </c>
       <c r="EP10" t="n">
-        <v>0.003964442759752274</v>
+        <v>0.006260894704610109</v>
       </c>
       <c r="EQ10" t="n">
-        <v>0.01956070028245449</v>
+        <v>0.0004445395898073912</v>
       </c>
       <c r="ER10" t="n">
-        <v>0.00496297050267458</v>
+        <v>0.004151334054768085</v>
       </c>
       <c r="ES10" t="n">
-        <v>0.0212294477969408</v>
+        <v>0.00545469019562006</v>
       </c>
       <c r="ET10" t="n">
-        <v>0.03224465250968933</v>
+        <v>0.01418054476380348</v>
       </c>
       <c r="EU10" t="n">
-        <v>0.004774044267833233</v>
+        <v>0.01102684251964092</v>
       </c>
       <c r="EV10" t="n">
-        <v>0.05599146708846092</v>
+        <v>0.01132189948111773</v>
       </c>
       <c r="EW10" t="n">
-        <v>0.009560756385326385</v>
+        <v>0.01017643604427576</v>
       </c>
       <c r="EX10" t="n">
-        <v>0.0004389763344079256</v>
+        <v>0.0006283337716013193</v>
       </c>
       <c r="EY10" t="n">
-        <v>0.0184154212474823</v>
+        <v>0.0135263791307807</v>
       </c>
       <c r="EZ10" t="n">
-        <v>0.01551225502043962</v>
+        <v>0.005782778840512037</v>
       </c>
       <c r="FA10" t="n">
-        <v>0.01663902401924133</v>
+        <v>0.002602552529424429</v>
       </c>
       <c r="FB10" t="n">
-        <v>0.02142597362399101</v>
+        <v>0.00318406498990953</v>
       </c>
       <c r="FC10" t="n">
-        <v>0.04697351530194283</v>
+        <v>0.008736690506339073</v>
       </c>
       <c r="FD10" t="n">
-        <v>0.006302198860794306</v>
+        <v>0.0001071940059773624</v>
       </c>
       <c r="FE10" t="n">
-        <v>0.0332891158759594</v>
+        <v>0.006251349113881588</v>
       </c>
       <c r="FF10" t="n">
-        <v>0.002216288819909096</v>
+        <v>0.0003607235848903656</v>
       </c>
       <c r="FG10" t="n">
-        <v>0.003483402542769909</v>
+        <v>0.00347865978255868</v>
       </c>
       <c r="FH10" t="n">
-        <v>0.02752851508557796</v>
+        <v>0.01437103468924761</v>
       </c>
       <c r="FI10" t="n">
-        <v>0.02851664647459984</v>
+        <v>0.004561955109238625</v>
       </c>
       <c r="FJ10" t="n">
-        <v>0.01143809966742992</v>
+        <v>0.01143081486225128</v>
       </c>
       <c r="FK10" t="n">
-        <v>0.007216335274279118</v>
+        <v>0.004143238067626953</v>
       </c>
       <c r="FL10" t="n">
-        <v>0.02893687039613724</v>
+        <v>0.01397045981138945</v>
       </c>
       <c r="FM10" t="n">
-        <v>0.004757300950586796</v>
+        <v>0.001346806762740016</v>
       </c>
       <c r="FN10" t="n">
-        <v>0.01551714725792408</v>
+        <v>0.0102304071187973</v>
       </c>
       <c r="FO10" t="n">
-        <v>0.01840310171246529</v>
+        <v>0.002913747448474169</v>
       </c>
       <c r="FP10" t="n">
-        <v>0.001000894466415048</v>
+        <v>0.006364187691360712</v>
       </c>
       <c r="FQ10" t="n">
-        <v>0.003495860379189253</v>
+        <v>0.03515173494815826</v>
       </c>
       <c r="FR10" t="n">
-        <v>0.01624386385083199</v>
+        <v>0.04894549772143364</v>
       </c>
       <c r="FS10" t="n">
-        <v>0.02142002992331982</v>
+        <v>0.004147825296968222</v>
       </c>
       <c r="FT10" t="n">
-        <v>0.0829230472445488</v>
+        <v>0.004770579747855663</v>
       </c>
       <c r="FU10" t="n">
-        <v>0.05432537198066711</v>
+        <v>0.02839760109782219</v>
       </c>
       <c r="FV10" t="n">
-        <v>0.02182264439761639</v>
+        <v>0.01749548874795437</v>
       </c>
       <c r="FW10" t="n">
-        <v>0.04141096025705338</v>
+        <v>0.007028563413769007</v>
       </c>
       <c r="FX10" t="n">
-        <v>0.01215804740786552</v>
+        <v>0.02698644995689392</v>
       </c>
       <c r="FY10" t="n">
-        <v>0.011559734120965</v>
+        <v>0.00962107814848423</v>
       </c>
       <c r="FZ10" t="n">
-        <v>0.0141269126906991</v>
+        <v>0.01065054628998041</v>
       </c>
       <c r="GA10" t="n">
-        <v>0.01083369459956884</v>
+        <v>0.001171842683106661</v>
       </c>
       <c r="GB10" t="n">
-        <v>0.006608592346310616</v>
+        <v>0.007796771824359894</v>
       </c>
       <c r="GC10" t="n">
-        <v>0.1336806416511536</v>
+        <v>0.0044287433847785</v>
       </c>
       <c r="GD10" t="n">
-        <v>0.02368594333529472</v>
+        <v>0.001093628583475947</v>
       </c>
       <c r="GE10" t="n">
-        <v>0.02276832424104214</v>
+        <v>0.001768445828929543</v>
       </c>
       <c r="GF10" t="n">
-        <v>0.03070877864956856</v>
+        <v>0.01651499234139919</v>
       </c>
       <c r="GG10" t="n">
-        <v>0.0006729802116751671</v>
+        <v>0.006696120370179415</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>4.085490218130872e-06</v>
+        <v>3.717918389156694e-06</v>
       </c>
       <c r="B11" t="n">
-        <v>0.0002776877954602242</v>
+        <v>0.0002112887741532177</v>
       </c>
       <c r="C11" t="n">
-        <v>1.515382155048428e-05</v>
+        <v>8.22876172605902e-05</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0001034436718327925</v>
+        <v>2.86610647890484e-05</v>
       </c>
       <c r="E11" t="n">
-        <v>7.147723863454303e-06</v>
+        <v>6.234031752683222e-05</v>
       </c>
       <c r="F11" t="n">
-        <v>0.0002235991560155526</v>
+        <v>0.0002049094327958301</v>
       </c>
       <c r="G11" t="n">
-        <v>1.632443490962032e-05</v>
+        <v>4.318194896768546e-06</v>
       </c>
       <c r="H11" t="n">
-        <v>7.955566979944706e-05</v>
+        <v>0.000106040621176362</v>
       </c>
       <c r="I11" t="n">
-        <v>2.046740337391384e-05</v>
+        <v>8.882987458491698e-06</v>
       </c>
       <c r="J11" t="n">
-        <v>5.252435948932543e-05</v>
+        <v>1.080067886505276e-05</v>
       </c>
       <c r="K11" t="n">
-        <v>0.0002412796602584422</v>
+        <v>0.0002706586383283138</v>
       </c>
       <c r="L11" t="n">
-        <v>2.92172489935183e-06</v>
+        <v>0.0001158329032477923</v>
       </c>
       <c r="M11" t="n">
-        <v>0.0001198082900373265</v>
+        <v>8.23006485006772e-05</v>
       </c>
       <c r="N11" t="n">
-        <v>2.168288119719364e-06</v>
+        <v>4.366842040326446e-05</v>
       </c>
       <c r="O11" t="n">
-        <v>0.0002191946259699762</v>
+        <v>0.0002037004887824878</v>
       </c>
       <c r="P11" t="n">
-        <v>8.140523277688771e-08</v>
+        <v>7.458174877683632e-06</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.460042353253812e-05</v>
+        <v>6.252957973629236e-05</v>
       </c>
       <c r="R11" t="n">
-        <v>1.384248753311113e-05</v>
+        <v>1.392470039718319e-05</v>
       </c>
       <c r="S11" t="n">
-        <v>8.648057701066136e-06</v>
+        <v>4.170535703451606e-06</v>
       </c>
       <c r="T11" t="n">
-        <v>2.276123632327653e-05</v>
+        <v>2.833031430782285e-05</v>
       </c>
       <c r="U11" t="n">
-        <v>1.976211024157237e-06</v>
+        <v>2.118478732882068e-06</v>
       </c>
       <c r="V11" t="n">
-        <v>3.180707426508889e-05</v>
+        <v>3.856108742184006e-05</v>
       </c>
       <c r="W11" t="n">
-        <v>3.181847569067031e-05</v>
+        <v>2.197001231252216e-05</v>
       </c>
       <c r="X11" t="n">
-        <v>7.747000381641556e-06</v>
+        <v>6.910449883434922e-05</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.442673874407774e-05</v>
+        <v>1.780745333235245e-05</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.594526449684054e-05</v>
+        <v>3.407246185815893e-05</v>
       </c>
       <c r="AA11" t="n">
-        <v>9.122263691097032e-06</v>
+        <v>6.23406640443136e-06</v>
       </c>
       <c r="AB11" t="n">
-        <v>3.115023719146848e-05</v>
+        <v>2.11060068977531e-06</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.272186586400494e-05</v>
+        <v>1.912421066663228e-05</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.477790101489518e-05</v>
+        <v>2.113060691044666e-05</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.788835288607515e-05</v>
+        <v>4.962185630574822e-05</v>
       </c>
       <c r="AF11" t="n">
-        <v>8.476009497826453e-06</v>
+        <v>4.936454206472263e-05</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.934794611064717e-05</v>
+        <v>4.734503454528749e-05</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.472834628657438e-05</v>
+        <v>1.147198236139957e-05</v>
       </c>
       <c r="AI11" t="n">
-        <v>2.242914888483938e-05</v>
+        <v>0.0001014906811178662</v>
       </c>
       <c r="AJ11" t="n">
-        <v>3.258632659708383e-06</v>
+        <v>2.694972499739379e-05</v>
       </c>
       <c r="AK11" t="n">
-        <v>2.167282946174964e-05</v>
+        <v>1.57558242790401e-05</v>
       </c>
       <c r="AL11" t="n">
-        <v>3.04770001093857e-05</v>
+        <v>5.604076432064176e-05</v>
       </c>
       <c r="AM11" t="n">
-        <v>1.149681793322088e-05</v>
+        <v>3.547274900483899e-06</v>
       </c>
       <c r="AN11" t="n">
-        <v>1.887982216430828e-05</v>
+        <v>4.051691212225705e-05</v>
       </c>
       <c r="AO11" t="n">
-        <v>6.567691343661863e-06</v>
+        <v>1.789878297131509e-05</v>
       </c>
       <c r="AP11" t="n">
-        <v>5.232553667156026e-05</v>
+        <v>1.780120328476187e-05</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.783834886737168e-05</v>
+        <v>1.8142409317079e-06</v>
       </c>
       <c r="AR11" t="n">
-        <v>1.546286512166262e-05</v>
+        <v>5.370674625737593e-05</v>
       </c>
       <c r="AS11" t="n">
-        <v>2.814330218825489e-05</v>
+        <v>2.282233253936283e-05</v>
       </c>
       <c r="AT11" t="n">
-        <v>3.21669976983685e-05</v>
+        <v>3.623118027462624e-05</v>
       </c>
       <c r="AU11" t="n">
-        <v>0.000185023425729014</v>
+        <v>0.0002701580815482885</v>
       </c>
       <c r="AV11" t="n">
-        <v>1.866495949798264e-05</v>
+        <v>1.869683183031157e-05</v>
       </c>
       <c r="AW11" t="n">
-        <v>2.225796561106108e-05</v>
+        <v>4.591689503286034e-05</v>
       </c>
       <c r="AX11" t="n">
-        <v>4.515144610195421e-05</v>
+        <v>7.008033571764827e-05</v>
       </c>
       <c r="AY11" t="n">
-        <v>0.000127878476632759</v>
+        <v>0.000141396900289692</v>
       </c>
       <c r="AZ11" t="n">
-        <v>6.49113098916132e-06</v>
+        <v>4.042973614559742e-06</v>
       </c>
       <c r="BA11" t="n">
-        <v>3.917541835107841e-05</v>
+        <v>2.000765198317822e-05</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.783062361937482e-05</v>
+        <v>3.080713941017166e-05</v>
       </c>
       <c r="BC11" t="n">
-        <v>1.110405719373375e-06</v>
+        <v>2.229968686151551e-06</v>
       </c>
       <c r="BD11" t="n">
-        <v>6.839857815066352e-05</v>
+        <v>7.32841290300712e-05</v>
       </c>
       <c r="BE11" t="n">
-        <v>6.33009331068024e-05</v>
+        <v>6.20766804786399e-05</v>
       </c>
       <c r="BF11" t="n">
-        <v>4.260240530129522e-05</v>
+        <v>2.604327846711385e-06</v>
       </c>
       <c r="BG11" t="n">
-        <v>8.256271394202486e-05</v>
+        <v>5.863498518010601e-05</v>
       </c>
       <c r="BH11" t="n">
-        <v>7.839866157155484e-05</v>
+        <v>1.399818756908644e-05</v>
       </c>
       <c r="BI11" t="n">
-        <v>9.577625860401895e-06</v>
+        <v>3.741769251064397e-05</v>
       </c>
       <c r="BJ11" t="n">
-        <v>3.617280162870884e-05</v>
+        <v>2.739846604526974e-05</v>
       </c>
       <c r="BK11" t="n">
-        <v>1.388107193633914e-06</v>
+        <v>2.272865458508022e-06</v>
       </c>
       <c r="BL11" t="n">
-        <v>9.075091838894878e-06</v>
+        <v>1.296168466069503e-05</v>
       </c>
       <c r="BM11" t="n">
-        <v>4.369363887235522e-05</v>
+        <v>2.768490594462492e-05</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.766161585692316e-05</v>
+        <v>1.160753618023591e-05</v>
       </c>
       <c r="BO11" t="n">
-        <v>3.292959445388988e-05</v>
+        <v>1.234806222782936e-05</v>
       </c>
       <c r="BP11" t="n">
-        <v>1.22600920349214e-06</v>
+        <v>6.110828508099075e-06</v>
       </c>
       <c r="BQ11" t="n">
-        <v>1.842116034822538e-05</v>
+        <v>1.341814822808374e-05</v>
       </c>
       <c r="BR11" t="n">
-        <v>1.771765892044641e-05</v>
+        <v>2.304886584170163e-05</v>
       </c>
       <c r="BS11" t="n">
-        <v>2.657666664163116e-05</v>
+        <v>2.477074758644449e-06</v>
       </c>
       <c r="BT11" t="n">
-        <v>6.961243798286887e-06</v>
+        <v>1.773647272784729e-05</v>
       </c>
       <c r="BU11" t="n">
-        <v>1.765466186043341e-05</v>
+        <v>5.321652224665741e-06</v>
       </c>
       <c r="BV11" t="n">
-        <v>9.700164082460105e-05</v>
+        <v>0.0001414033322362229</v>
       </c>
       <c r="BW11" t="n">
-        <v>1.453321965527721e-05</v>
+        <v>3.588858817238361e-06</v>
       </c>
       <c r="BX11" t="n">
-        <v>1.034804881783202e-07</v>
+        <v>4.796340726898052e-05</v>
       </c>
       <c r="BY11" t="n">
-        <v>1.205753414978972e-05</v>
+        <v>3.334335633553565e-05</v>
       </c>
       <c r="BZ11" t="n">
-        <v>5.845402847626247e-05</v>
+        <v>0.0001093321043299511</v>
       </c>
       <c r="CA11" t="n">
-        <v>1.107125626731431e-05</v>
+        <v>3.33731368300505e-05</v>
       </c>
       <c r="CB11" t="n">
-        <v>2.050270450126845e-05</v>
+        <v>2.448026316415053e-05</v>
       </c>
       <c r="CC11" t="n">
-        <v>1.939359935931861e-05</v>
+        <v>8.996079486678354e-06</v>
       </c>
       <c r="CD11" t="n">
-        <v>3.470838919383823e-06</v>
+        <v>2.725540070969146e-06</v>
       </c>
       <c r="CE11" t="n">
-        <v>4.64073964394629e-05</v>
+        <v>7.510129944421351e-05</v>
       </c>
       <c r="CF11" t="n">
-        <v>1.988536678254604e-05</v>
+        <v>1.571321990923025e-05</v>
       </c>
       <c r="CG11" t="n">
-        <v>2.056296943919733e-05</v>
+        <v>1.540800985821988e-05</v>
       </c>
       <c r="CH11" t="n">
-        <v>1.77230922417948e-05</v>
+        <v>3.612449290812947e-07</v>
       </c>
       <c r="CI11" t="n">
-        <v>3.173323784722015e-05</v>
+        <v>4.233851723256521e-05</v>
       </c>
       <c r="CJ11" t="n">
-        <v>1.565319871588144e-05</v>
+        <v>1.082432618204621e-06</v>
       </c>
       <c r="CK11" t="n">
-        <v>9.647140359447803e-06</v>
+        <v>1.857115603343118e-05</v>
       </c>
       <c r="CL11" t="n">
-        <v>1.015099405776709e-05</v>
+        <v>6.145146926428424e-06</v>
       </c>
       <c r="CM11" t="n">
-        <v>4.905774039798416e-05</v>
+        <v>1.31675351440208e-05</v>
       </c>
       <c r="CN11" t="n">
-        <v>4.23308665631339e-05</v>
+        <v>6.48896602797322e-05</v>
       </c>
       <c r="CO11" t="n">
-        <v>8.385236469621304e-07</v>
+        <v>4.460456693777815e-05</v>
       </c>
       <c r="CP11" t="n">
-        <v>3.608418046496809e-05</v>
+        <v>6.915468838997185e-05</v>
       </c>
       <c r="CQ11" t="n">
-        <v>1.42672297442914e-05</v>
+        <v>6.131967529654503e-05</v>
       </c>
       <c r="CR11" t="n">
-        <v>2.838270347638172e-06</v>
+        <v>3.36882658302784e-05</v>
       </c>
       <c r="CS11" t="n">
-        <v>3.273115726187825e-05</v>
+        <v>1.960541703738272e-05</v>
       </c>
       <c r="CT11" t="n">
-        <v>4.940127473673783e-05</v>
+        <v>1.880014497146476e-05</v>
       </c>
       <c r="CU11" t="n">
-        <v>5.768636583525222e-06</v>
+        <v>5.399428118835203e-06</v>
       </c>
       <c r="CV11" t="n">
-        <v>2.204374595748959e-06</v>
+        <v>1.09126840470708e-05</v>
       </c>
       <c r="CW11" t="n">
-        <v>3.758999810088426e-05</v>
+        <v>6.842798757134005e-05</v>
       </c>
       <c r="CX11" t="n">
-        <v>2.13891762541607e-05</v>
+        <v>2.541993308113888e-05</v>
       </c>
       <c r="CY11" t="n">
-        <v>2.928117828560062e-05</v>
+        <v>2.761444557108916e-05</v>
       </c>
       <c r="CZ11" t="n">
-        <v>1.693725243967492e-05</v>
+        <v>2.904517714341637e-06</v>
       </c>
       <c r="DA11" t="n">
-        <v>3.741901309695095e-05</v>
+        <v>4.972769602318294e-05</v>
       </c>
       <c r="DB11" t="n">
-        <v>1.258580869034631e-05</v>
+        <v>6.729419510520529e-06</v>
       </c>
       <c r="DC11" t="n">
-        <v>1.776465069269761e-05</v>
+        <v>1.135371530835982e-05</v>
       </c>
       <c r="DD11" t="n">
-        <v>6.769354058633326e-06</v>
+        <v>6.777344196962076e-07</v>
       </c>
       <c r="DE11" t="n">
-        <v>8.269173122243956e-06</v>
+        <v>9.015101568365935e-06</v>
       </c>
       <c r="DF11" t="n">
-        <v>3.701879541040398e-05</v>
+        <v>4.908916162094101e-05</v>
       </c>
       <c r="DG11" t="n">
-        <v>2.236786895082332e-05</v>
+        <v>1.850451371865347e-05</v>
       </c>
       <c r="DH11" t="n">
-        <v>6.038450374035165e-05</v>
+        <v>2.37132771871984e-05</v>
       </c>
       <c r="DI11" t="n">
-        <v>4.950396487402031e-06</v>
+        <v>1.37637325678952e-05</v>
       </c>
       <c r="DJ11" t="n">
-        <v>5.05169100506464e-06</v>
+        <v>7.855545845814049e-05</v>
       </c>
       <c r="DK11" t="n">
-        <v>2.947996836155653e-05</v>
+        <v>1.306541525991634e-05</v>
       </c>
       <c r="DL11" t="n">
-        <v>3.27597044815775e-05</v>
+        <v>0.0001025309757096693</v>
       </c>
       <c r="DM11" t="n">
-        <v>3.58598554157652e-05</v>
+        <v>2.493887950549833e-05</v>
       </c>
       <c r="DN11" t="n">
-        <v>5.86275382374879e-06</v>
+        <v>2.207733996328898e-05</v>
       </c>
       <c r="DO11" t="n">
-        <v>7.272496077348478e-06</v>
+        <v>2.783001582429279e-05</v>
       </c>
       <c r="DP11" t="n">
-        <v>1.380273261020193e-05</v>
+        <v>1.43169927468989e-05</v>
       </c>
       <c r="DQ11" t="n">
-        <v>3.055956767639145e-07</v>
+        <v>1.384274582960643e-05</v>
       </c>
       <c r="DR11" t="n">
-        <v>1.813694143493194e-05</v>
+        <v>4.40636449638987e-06</v>
       </c>
       <c r="DS11" t="n">
-        <v>1.049250658979872e-05</v>
+        <v>2.704399958020076e-05</v>
       </c>
       <c r="DT11" t="n">
-        <v>1.230073121405439e-05</v>
+        <v>1.916254404932261e-05</v>
       </c>
       <c r="DU11" t="n">
-        <v>1.289071224164218e-05</v>
+        <v>4.097901182831265e-05</v>
       </c>
       <c r="DV11" t="n">
-        <v>2.308279908902477e-05</v>
+        <v>1.178174989036052e-05</v>
       </c>
       <c r="DW11" t="n">
-        <v>1.462259388063103e-05</v>
+        <v>4.09752938139718e-05</v>
       </c>
       <c r="DX11" t="n">
-        <v>2.534199120418634e-05</v>
+        <v>5.272813723422587e-05</v>
       </c>
       <c r="DY11" t="n">
-        <v>1.528843131382018e-05</v>
+        <v>3.920332528650761e-05</v>
       </c>
       <c r="DZ11" t="n">
-        <v>9.992900231736712e-06</v>
+        <v>2.551514626247808e-07</v>
       </c>
       <c r="EA11" t="n">
-        <v>1.460281282561482e-06</v>
+        <v>4.579569940688089e-05</v>
       </c>
       <c r="EB11" t="n">
-        <v>6.004210717946989e-06</v>
+        <v>4.69841506856028e-05</v>
       </c>
       <c r="EC11" t="n">
-        <v>3.690406174428063e-06</v>
+        <v>1.512640028522583e-05</v>
       </c>
       <c r="ED11" t="n">
-        <v>1.098046959668864e-05</v>
+        <v>4.527487544692121e-05</v>
       </c>
       <c r="EE11" t="n">
-        <v>1.092091588361654e-05</v>
+        <v>4.711743895313703e-05</v>
       </c>
       <c r="EF11" t="n">
-        <v>4.727040504803881e-06</v>
+        <v>1.284775134990923e-05</v>
       </c>
       <c r="EG11" t="n">
-        <v>3.444521644269116e-05</v>
+        <v>2.659583697095513e-05</v>
       </c>
       <c r="EH11" t="n">
-        <v>1.854832044045907e-05</v>
+        <v>8.499033356201835e-06</v>
       </c>
       <c r="EI11" t="n">
-        <v>3.126998763036681e-06</v>
+        <v>6.408608896890655e-07</v>
       </c>
       <c r="EJ11" t="n">
-        <v>6.916718120919541e-06</v>
+        <v>2.094639239658136e-05</v>
       </c>
       <c r="EK11" t="n">
-        <v>2.59461157838814e-05</v>
+        <v>1.621082810743246e-05</v>
       </c>
       <c r="EL11" t="n">
-        <v>2.274397229484748e-05</v>
+        <v>1.207418608828448e-05</v>
       </c>
       <c r="EM11" t="n">
-        <v>1.532803025838803e-06</v>
+        <v>1.514990617579315e-05</v>
       </c>
       <c r="EN11" t="n">
-        <v>8.90470346348593e-08</v>
+        <v>2.115993538609473e-06</v>
       </c>
       <c r="EO11" t="n">
-        <v>9.511758435110096e-06</v>
+        <v>2.326008325326256e-05</v>
       </c>
       <c r="EP11" t="n">
-        <v>2.437999319226947e-05</v>
+        <v>2.07577868422959e-05</v>
       </c>
       <c r="EQ11" t="n">
-        <v>1.737396814860404e-05</v>
+        <v>7.728120181127451e-06</v>
       </c>
       <c r="ER11" t="n">
-        <v>2.598113860585727e-05</v>
+        <v>3.258066135458648e-05</v>
       </c>
       <c r="ES11" t="n">
-        <v>1.788621739251539e-05</v>
+        <v>3.425309841986746e-05</v>
       </c>
       <c r="ET11" t="n">
-        <v>1.208157391374698e-05</v>
+        <v>5.151350251253461e-06</v>
       </c>
       <c r="EU11" t="n">
-        <v>9.263707397622056e-06</v>
+        <v>1.195576260215603e-07</v>
       </c>
       <c r="EV11" t="n">
-        <v>3.891275628120638e-05</v>
+        <v>1.550197885080706e-05</v>
       </c>
       <c r="EW11" t="n">
-        <v>7.209373052319279e-06</v>
+        <v>4.645650915335864e-05</v>
       </c>
       <c r="EX11" t="n">
-        <v>5.010367658542236e-06</v>
+        <v>6.993341230554506e-07</v>
       </c>
       <c r="EY11" t="n">
-        <v>3.589814514270984e-05</v>
+        <v>8.168627391569316e-05</v>
       </c>
       <c r="EZ11" t="n">
-        <v>1.131070894189179e-05</v>
+        <v>1.794114359654486e-05</v>
       </c>
       <c r="FA11" t="n">
-        <v>2.176365524064749e-05</v>
+        <v>2.363963722018525e-05</v>
       </c>
       <c r="FB11" t="n">
-        <v>1.515979693067493e-05</v>
+        <v>6.910690899530891e-06</v>
       </c>
       <c r="FC11" t="n">
-        <v>3.32421222992707e-05</v>
+        <v>5.096986569697037e-05</v>
       </c>
       <c r="FD11" t="n">
-        <v>1.79680973815266e-05</v>
+        <v>3.717009803949622e-06</v>
       </c>
       <c r="FE11" t="n">
-        <v>7.834201824152842e-06</v>
+        <v>1.87451751116896e-05</v>
       </c>
       <c r="FF11" t="n">
-        <v>1.587172846484464e-05</v>
+        <v>9.771095392352436e-06</v>
       </c>
       <c r="FG11" t="n">
-        <v>1.346184853900922e-05</v>
+        <v>8.790021638560575e-06</v>
       </c>
       <c r="FH11" t="n">
-        <v>8.101430466922466e-06</v>
+        <v>4.897755206911825e-05</v>
       </c>
       <c r="FI11" t="n">
-        <v>9.526492249278817e-06</v>
+        <v>2.409393346169963e-05</v>
       </c>
       <c r="FJ11" t="n">
-        <v>5.441217945190147e-05</v>
+        <v>2.753931403276511e-05</v>
       </c>
       <c r="FK11" t="n">
-        <v>9.365734513266943e-06</v>
+        <v>4.428437023307197e-06</v>
       </c>
       <c r="FL11" t="n">
-        <v>3.253395698266104e-05</v>
+        <v>3.723936242749915e-05</v>
       </c>
       <c r="FM11" t="n">
-        <v>2.479418981238268e-06</v>
+        <v>1.05909366538981e-05</v>
       </c>
       <c r="FN11" t="n">
-        <v>1.737143247737549e-05</v>
+        <v>6.444940663641319e-05</v>
       </c>
       <c r="FO11" t="n">
-        <v>8.702660124981776e-06</v>
+        <v>5.42144407518208e-05</v>
       </c>
       <c r="FP11" t="n">
-        <v>1.03655793282087e-06</v>
+        <v>2.180475894419942e-05</v>
       </c>
       <c r="FQ11" t="n">
-        <v>5.785340545116924e-05</v>
+        <v>6.484598270617425e-05</v>
       </c>
       <c r="FR11" t="n">
-        <v>1.731737575028092e-05</v>
+        <v>5.005062848795205e-05</v>
       </c>
       <c r="FS11" t="n">
-        <v>5.157475243322551e-05</v>
+        <v>3.020440999534912e-07</v>
       </c>
       <c r="FT11" t="n">
-        <v>2.304580084455665e-05</v>
+        <v>1.025855726766167e-05</v>
       </c>
       <c r="FU11" t="n">
-        <v>3.713229307322763e-05</v>
+        <v>2.991870496771298e-05</v>
       </c>
       <c r="FV11" t="n">
-        <v>9.288962246500887e-06</v>
+        <v>4.460623313207179e-05</v>
       </c>
       <c r="FW11" t="n">
-        <v>4.605115918820957e-06</v>
+        <v>5.276298179524019e-05</v>
       </c>
       <c r="FX11" t="n">
-        <v>1.28500432765577e-05</v>
+        <v>4.693813025369309e-05</v>
       </c>
       <c r="FY11" t="n">
-        <v>4.934909520670772e-05</v>
+        <v>2.371971640968695e-05</v>
       </c>
       <c r="FZ11" t="n">
-        <v>5.451547622215003e-06</v>
+        <v>1.257449548575096e-05</v>
       </c>
       <c r="GA11" t="n">
-        <v>1.452314336347627e-05</v>
+        <v>5.86111236771103e-05</v>
       </c>
       <c r="GB11" t="n">
-        <v>1.790244709809485e-06</v>
+        <v>5.496867743204348e-07</v>
       </c>
       <c r="GC11" t="n">
-        <v>2.868660521926358e-05</v>
+        <v>7.723210728727281e-05</v>
       </c>
       <c r="GD11" t="n">
-        <v>3.52717652276624e-05</v>
+        <v>4.278012056602165e-05</v>
       </c>
       <c r="GE11" t="n">
-        <v>9.680589573690668e-05</v>
+        <v>2.425042112008668e-05</v>
       </c>
       <c r="GF11" t="n">
-        <v>2.140519427484833e-06</v>
+        <v>1.540974335512146e-05</v>
       </c>
       <c r="GG11" t="n">
-        <v>2.172952918044757e-05</v>
+        <v>1.604655699338764e-05</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>8.851793245412409e-05</v>
+        <v>0.001146208611316979</v>
       </c>
       <c r="B12" t="n">
-        <v>0.002023112261667848</v>
+        <v>0.04004538059234619</v>
       </c>
       <c r="C12" t="n">
-        <v>0.000124317390145734</v>
+        <v>0.02042381465435028</v>
       </c>
       <c r="D12" t="n">
-        <v>0.001058741938322783</v>
+        <v>0.01131251454353333</v>
       </c>
       <c r="E12" t="n">
-        <v>0.001237376360222697</v>
+        <v>0.003409671364352107</v>
       </c>
       <c r="F12" t="n">
-        <v>0.000787760189268738</v>
+        <v>0.02144585177302361</v>
       </c>
       <c r="G12" t="n">
-        <v>0.0003025557089131325</v>
+        <v>0.0006834217347204685</v>
       </c>
       <c r="H12" t="n">
-        <v>2.441815013298765e-05</v>
+        <v>0.0003809317131526768</v>
       </c>
       <c r="I12" t="n">
-        <v>0.0002158983843401074</v>
+        <v>0.01393758412450552</v>
       </c>
       <c r="J12" t="n">
-        <v>3.058527363464236e-05</v>
+        <v>0.002049499191343784</v>
       </c>
       <c r="K12" t="n">
-        <v>0.001691185287199914</v>
+        <v>0.04259848594665527</v>
       </c>
       <c r="L12" t="n">
-        <v>0.0001633921201573685</v>
+        <v>0.02496886253356934</v>
       </c>
       <c r="M12" t="n">
-        <v>0.0002328296832274646</v>
+        <v>0.01891091838479042</v>
       </c>
       <c r="N12" t="n">
-        <v>0.0008064024732448161</v>
+        <v>0.002640092745423317</v>
       </c>
       <c r="O12" t="n">
-        <v>0.0004626454028766602</v>
+        <v>0.01311876345425844</v>
       </c>
       <c r="P12" t="n">
-        <v>0.0005704559735022485</v>
+        <v>0.001695340499281883</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.0003637755871750414</v>
+        <v>0.007150540128350258</v>
       </c>
       <c r="R12" t="n">
-        <v>7.176625513238832e-05</v>
+        <v>0.008867355063557625</v>
       </c>
       <c r="S12" t="n">
-        <v>5.113893712405115e-05</v>
+        <v>0.003418980166316032</v>
       </c>
       <c r="T12" t="n">
-        <v>0.0001054455060511827</v>
+        <v>0.00676227081567049</v>
       </c>
       <c r="U12" t="n">
-        <v>1.697782863629982e-05</v>
+        <v>0.01034898031502962</v>
       </c>
       <c r="V12" t="n">
-        <v>0.0003336518711876124</v>
+        <v>0.0004741201119031757</v>
       </c>
       <c r="W12" t="n">
-        <v>5.953882009634981e-07</v>
+        <v>0.001905860379338264</v>
       </c>
       <c r="X12" t="n">
-        <v>0.0001595807116245851</v>
+        <v>0.01100296806544065</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.0002458253584336489</v>
+        <v>0.001759763574227691</v>
       </c>
       <c r="Z12" t="n">
-        <v>0.000106243351183366</v>
+        <v>0.0004480956413317472</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.0002913595526479185</v>
+        <v>0.006101422011852264</v>
       </c>
       <c r="AB12" t="n">
-        <v>5.396018968895078e-05</v>
+        <v>0.003771432675421238</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.081680941046216e-05</v>
+        <v>0.005925072357058525</v>
       </c>
       <c r="AD12" t="n">
-        <v>0.0002383929386269301</v>
+        <v>0.0008899817476049066</v>
       </c>
       <c r="AE12" t="n">
-        <v>0.0004465369565878063</v>
+        <v>0.01402177941054106</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.0002372492017457262</v>
+        <v>0.0136293563991785</v>
       </c>
       <c r="AG12" t="n">
-        <v>0.0002042418200289831</v>
+        <v>0.002984666964039207</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.694441016297787e-05</v>
+        <v>0.004640840925276279</v>
       </c>
       <c r="AI12" t="n">
-        <v>0.0003505935601424426</v>
+        <v>0.002574703888967633</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0.0002171149535570294</v>
+        <v>0.005424290895462036</v>
       </c>
       <c r="AK12" t="n">
-        <v>0.0001004216464934871</v>
+        <v>0.0008054006029851735</v>
       </c>
       <c r="AL12" t="n">
-        <v>0.0003426907060202211</v>
+        <v>0.007733161561191082</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.0001094039471354336</v>
+        <v>0.007198232691735029</v>
       </c>
       <c r="AN12" t="n">
-        <v>4.854981307289563e-05</v>
+        <v>0.00565354572609067</v>
       </c>
       <c r="AO12" t="n">
-        <v>1.665994750510436e-05</v>
+        <v>0.01583751477301121</v>
       </c>
       <c r="AP12" t="n">
-        <v>0.000244864058913663</v>
+        <v>0.007207273505628109</v>
       </c>
       <c r="AQ12" t="n">
-        <v>6.389144255081192e-05</v>
+        <v>0.003496623132377863</v>
       </c>
       <c r="AR12" t="n">
-        <v>0.0001984361006179824</v>
+        <v>0.0007271289359778166</v>
       </c>
       <c r="AS12" t="n">
-        <v>0.0001807198277674615</v>
+        <v>0.0009041515295393765</v>
       </c>
       <c r="AT12" t="n">
-        <v>0.0002818388747982681</v>
+        <v>0.001242289901711047</v>
       </c>
       <c r="AU12" t="n">
-        <v>0.00105719524435699</v>
+        <v>0.02911025285720825</v>
       </c>
       <c r="AV12" t="n">
-        <v>8.209384759538807e-06</v>
+        <v>0.003244397230446339</v>
       </c>
       <c r="AW12" t="n">
-        <v>0.0009880943689495325</v>
+        <v>0.012147206813097</v>
       </c>
       <c r="AX12" t="n">
-        <v>0.0008341582724824548</v>
+        <v>0.001480159116908908</v>
       </c>
       <c r="AY12" t="n">
-        <v>0.0004823039344046265</v>
+        <v>0.007843509316444397</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0.0003755313227884471</v>
+        <v>0.0005363819655030966</v>
       </c>
       <c r="BA12" t="n">
-        <v>0.0001675768144195899</v>
+        <v>0.0007569470908492804</v>
       </c>
       <c r="BB12" t="n">
-        <v>0.0003868514904752374</v>
+        <v>0.004850124008953571</v>
       </c>
       <c r="BC12" t="n">
-        <v>0.0002073123323498294</v>
+        <v>0.004749380517750978</v>
       </c>
       <c r="BD12" t="n">
-        <v>0.0002962073776870966</v>
+        <v>0.004128864035010338</v>
       </c>
       <c r="BE12" t="n">
-        <v>0.0002674198476597667</v>
+        <v>0.01145871169865131</v>
       </c>
       <c r="BF12" t="n">
-        <v>8.426637214142829e-05</v>
+        <v>0.005748019553720951</v>
       </c>
       <c r="BG12" t="n">
-        <v>0.0006820362177677453</v>
+        <v>0.003009159583598375</v>
       </c>
       <c r="BH12" t="n">
-        <v>0.0002710165863391012</v>
+        <v>0.01427867449820042</v>
       </c>
       <c r="BI12" t="n">
-        <v>6.198891060194001e-05</v>
+        <v>0.002728150226175785</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.0004262124130036682</v>
+        <v>0.003353636479005218</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.0001950269361259416</v>
+        <v>0.007482642307877541</v>
       </c>
       <c r="BL12" t="n">
-        <v>8.25935130706057e-05</v>
+        <v>0.002054629381746054</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.0001793535775505006</v>
+        <v>0.005034828558564186</v>
       </c>
       <c r="BN12" t="n">
-        <v>0.0001585024583619088</v>
+        <v>0.004773910623043776</v>
       </c>
       <c r="BO12" t="n">
-        <v>4.556044586934149e-05</v>
+        <v>0.007429879158735275</v>
       </c>
       <c r="BP12" t="n">
-        <v>0.0004958437057211995</v>
+        <v>0.002722110832110047</v>
       </c>
       <c r="BQ12" t="n">
-        <v>0.0001348278892692178</v>
+        <v>0.0002526489552110434</v>
       </c>
       <c r="BR12" t="n">
-        <v>2.606377165648155e-05</v>
+        <v>0.003168279305100441</v>
       </c>
       <c r="BS12" t="n">
-        <v>0.000321641331538558</v>
+        <v>0.002859186846762896</v>
       </c>
       <c r="BT12" t="n">
-        <v>3.907117206836119e-05</v>
+        <v>0.002922711428254843</v>
       </c>
       <c r="BU12" t="n">
-        <v>0.0002604606270324439</v>
+        <v>0.001583275734446943</v>
       </c>
       <c r="BV12" t="n">
-        <v>0.0007387830410152674</v>
+        <v>0.01942707598209381</v>
       </c>
       <c r="BW12" t="n">
-        <v>4.088938294444233e-05</v>
+        <v>0.001450897892937064</v>
       </c>
       <c r="BX12" t="n">
-        <v>0.0003662765375338495</v>
+        <v>0.006478158291429281</v>
       </c>
       <c r="BY12" t="n">
-        <v>0.0003828006447292864</v>
+        <v>0.002444566693156958</v>
       </c>
       <c r="BZ12" t="n">
-        <v>8.905321010388434e-05</v>
+        <v>0.01328148785978556</v>
       </c>
       <c r="CA12" t="n">
-        <v>0.0002087751345243305</v>
+        <v>0.0002783581148833036</v>
       </c>
       <c r="CB12" t="n">
-        <v>5.773087104898877e-05</v>
+        <v>0.000291735865175724</v>
       </c>
       <c r="CC12" t="n">
-        <v>0.0002664797066245228</v>
+        <v>0.007636349648237228</v>
       </c>
       <c r="CD12" t="n">
-        <v>5.22645132150501e-05</v>
+        <v>0.001030981540679932</v>
       </c>
       <c r="CE12" t="n">
-        <v>0.0002027602458838373</v>
+        <v>0.01317261345684528</v>
       </c>
       <c r="CF12" t="n">
-        <v>9.659856732469052e-05</v>
+        <v>0.008529039099812508</v>
       </c>
       <c r="CG12" t="n">
-        <v>0.0002217259025201201</v>
+        <v>0.00518741924315691</v>
       </c>
       <c r="CH12" t="n">
-        <v>6.096911238273606e-05</v>
+        <v>2.848493750207126e-05</v>
       </c>
       <c r="CI12" t="n">
-        <v>0.0001331845851382241</v>
+        <v>0.0001416132436133921</v>
       </c>
       <c r="CJ12" t="n">
-        <v>4.460851414478384e-06</v>
+        <v>0.0007678305264562368</v>
       </c>
       <c r="CK12" t="n">
-        <v>6.999754987191409e-05</v>
+        <v>0.001205675303936005</v>
       </c>
       <c r="CL12" t="n">
-        <v>0.0002129139029420912</v>
+        <v>0.003826464526355267</v>
       </c>
       <c r="CM12" t="n">
-        <v>1.862874887592625e-05</v>
+        <v>0.004798974376171827</v>
       </c>
       <c r="CN12" t="n">
-        <v>0.0002915039949584752</v>
+        <v>0.01064490433782339</v>
       </c>
       <c r="CO12" t="n">
-        <v>8.43620509840548e-05</v>
+        <v>0.004473008681088686</v>
       </c>
       <c r="CP12" t="n">
-        <v>0.0004821795737370849</v>
+        <v>0.01165644451975822</v>
       </c>
       <c r="CQ12" t="n">
-        <v>8.215494744945318e-05</v>
+        <v>0.003843365702778101</v>
       </c>
       <c r="CR12" t="n">
-        <v>0.0004221690469421446</v>
+        <v>0.009884949773550034</v>
       </c>
       <c r="CS12" t="n">
-        <v>0.000552272074855864</v>
+        <v>0.00289154564961791</v>
       </c>
       <c r="CT12" t="n">
-        <v>0.0002619011502247304</v>
+        <v>0.0001739915460348129</v>
       </c>
       <c r="CU12" t="n">
-        <v>9.573502757120878e-05</v>
+        <v>0.005150565877556801</v>
       </c>
       <c r="CV12" t="n">
-        <v>1.937299202836584e-06</v>
+        <v>0.00112474721390754</v>
       </c>
       <c r="CW12" t="n">
-        <v>0.0002473648055456579</v>
+        <v>0.01375034172087908</v>
       </c>
       <c r="CX12" t="n">
-        <v>0.0001302573800785467</v>
+        <v>0.008980890735983849</v>
       </c>
       <c r="CY12" t="n">
-        <v>0.0003052015963476151</v>
+        <v>0.005149636417627335</v>
       </c>
       <c r="CZ12" t="n">
-        <v>0.0001092843231162988</v>
+        <v>0.001481753424741328</v>
       </c>
       <c r="DA12" t="n">
-        <v>0.0002201816969318315</v>
+        <v>0.001743072993122041</v>
       </c>
       <c r="DB12" t="n">
-        <v>7.026336970739067e-05</v>
+        <v>0.0002594356192275882</v>
       </c>
       <c r="DC12" t="n">
-        <v>0.0001011342246783897</v>
+        <v>0.0004613917553797364</v>
       </c>
       <c r="DD12" t="n">
-        <v>0.0001818935415940359</v>
+        <v>0.005044052377343178</v>
       </c>
       <c r="DE12" t="n">
-        <v>9.282289101975039e-05</v>
+        <v>0.005884065292775631</v>
       </c>
       <c r="DF12" t="n">
-        <v>0.0003774634678848088</v>
+        <v>0.01863201521337032</v>
       </c>
       <c r="DG12" t="n">
-        <v>0.0002200860617449507</v>
+        <v>0.01251542754471302</v>
       </c>
       <c r="DH12" t="n">
-        <v>0.001354398322291672</v>
+        <v>0.01065594796091318</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.0009718362125568092</v>
+        <v>0.005344109144061804</v>
       </c>
       <c r="DJ12" t="n">
-        <v>6.743392441421747e-05</v>
+        <v>0.002616670913994312</v>
       </c>
       <c r="DK12" t="n">
-        <v>0.0004874771402683109</v>
+        <v>0.001453385222703218</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.000699876865837723</v>
+        <v>0.009620760567486286</v>
       </c>
       <c r="DM12" t="n">
-        <v>0.0001042717485688627</v>
+        <v>0.008087361231446266</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.0002380973019171506</v>
+        <v>0.001258525182493031</v>
       </c>
       <c r="DO12" t="n">
-        <v>0.0001891873398562893</v>
+        <v>0.004538852255791426</v>
       </c>
       <c r="DP12" t="n">
-        <v>0.0005023335688747466</v>
+        <v>0.00506623275578022</v>
       </c>
       <c r="DQ12" t="n">
-        <v>0.000119866817840375</v>
+        <v>0.002441250253468752</v>
       </c>
       <c r="DR12" t="n">
-        <v>0.0001027449470711872</v>
+        <v>0.004119386896491051</v>
       </c>
       <c r="DS12" t="n">
-        <v>0.0001538310170872137</v>
+        <v>0.007881062105298042</v>
       </c>
       <c r="DT12" t="n">
-        <v>0.0001135014172177762</v>
+        <v>0.0008880752138793468</v>
       </c>
       <c r="DU12" t="n">
-        <v>0.0001510572910774499</v>
+        <v>0.0001013127621263266</v>
       </c>
       <c r="DV12" t="n">
-        <v>0.0002577322593424469</v>
+        <v>0.007514766417443752</v>
       </c>
       <c r="DW12" t="n">
-        <v>0.0001152884433395229</v>
+        <v>0.003729383694007993</v>
       </c>
       <c r="DX12" t="n">
-        <v>3.483884211163968e-05</v>
+        <v>0.007402560207992792</v>
       </c>
       <c r="DY12" t="n">
-        <v>0.0003949866513721645</v>
+        <v>0.006571678910404444</v>
       </c>
       <c r="DZ12" t="n">
-        <v>0.0002315038291271776</v>
+        <v>0.003847970860078931</v>
       </c>
       <c r="EA12" t="n">
-        <v>1.697270636213943e-05</v>
+        <v>0.009647827595472336</v>
       </c>
       <c r="EB12" t="n">
-        <v>0.0001586223079357296</v>
+        <v>0.007480303756892681</v>
       </c>
       <c r="EC12" t="n">
-        <v>7.775693666189909e-05</v>
+        <v>0.0003550848632585257</v>
       </c>
       <c r="ED12" t="n">
-        <v>0.0002323570370208472</v>
+        <v>0.005503323394805193</v>
       </c>
       <c r="EE12" t="n">
-        <v>0.0001479299244238064</v>
+        <v>0.005606187041848898</v>
       </c>
       <c r="EF12" t="n">
-        <v>0.0002036591904470697</v>
+        <v>0.001606122357770801</v>
       </c>
       <c r="EG12" t="n">
-        <v>0.0001427118550054729</v>
+        <v>0.01299998350441456</v>
       </c>
       <c r="EH12" t="n">
-        <v>0.0002239669993286952</v>
+        <v>0.005586283281445503</v>
       </c>
       <c r="EI12" t="n">
-        <v>2.733160727075301e-05</v>
+        <v>0.003472137730568647</v>
       </c>
       <c r="EJ12" t="n">
-        <v>0.0003277658834122121</v>
+        <v>0.0003739791281986982</v>
       </c>
       <c r="EK12" t="n">
-        <v>0.0002619909646455199</v>
+        <v>0.005869455635547638</v>
       </c>
       <c r="EL12" t="n">
-        <v>3.373934305272996e-07</v>
+        <v>0.001232987502589822</v>
       </c>
       <c r="EM12" t="n">
-        <v>1.08624626591336e-05</v>
+        <v>0.001000942895188928</v>
       </c>
       <c r="EN12" t="n">
-        <v>6.990891415625811e-05</v>
+        <v>0.004806666634976864</v>
       </c>
       <c r="EO12" t="n">
-        <v>3.415310857235454e-05</v>
+        <v>0.0001784066116670147</v>
       </c>
       <c r="EP12" t="n">
-        <v>8.72476175572956e-06</v>
+        <v>0.0005609032232314348</v>
       </c>
       <c r="EQ12" t="n">
-        <v>0.0001201421182486229</v>
+        <v>0.004065204877406359</v>
       </c>
       <c r="ER12" t="n">
-        <v>0.0001520471560070291</v>
+        <v>0.001765619497746229</v>
       </c>
       <c r="ES12" t="n">
-        <v>7.760183507343754e-05</v>
+        <v>0.0004722622688859701</v>
       </c>
       <c r="ET12" t="n">
-        <v>0.0003563420032151043</v>
+        <v>0.0001692537916824222</v>
       </c>
       <c r="EU12" t="n">
-        <v>0.0001574520574649796</v>
+        <v>0.00308009865693748</v>
       </c>
       <c r="EV12" t="n">
-        <v>0.0002205854980275035</v>
+        <v>0.001799716148525476</v>
       </c>
       <c r="EW12" t="n">
-        <v>9.468345524510369e-05</v>
+        <v>0.005464470013976097</v>
       </c>
       <c r="EX12" t="n">
-        <v>2.066695014946163e-05</v>
+        <v>0.001498944358900189</v>
       </c>
       <c r="EY12" t="n">
-        <v>0.0002259644534206018</v>
+        <v>0.01444796752184629</v>
       </c>
       <c r="EZ12" t="n">
-        <v>4.820678077521734e-05</v>
+        <v>0.007415310014039278</v>
       </c>
       <c r="FA12" t="n">
-        <v>0.0002542333968449384</v>
+        <v>0.006635788828134537</v>
       </c>
       <c r="FB12" t="n">
-        <v>3.820436177193187e-06</v>
+        <v>0.001571189612150192</v>
       </c>
       <c r="FC12" t="n">
-        <v>0.0001386741059832275</v>
+        <v>0.002575919963419437</v>
       </c>
       <c r="FD12" t="n">
-        <v>5.265138679533266e-05</v>
+        <v>0.0003133367281407118</v>
       </c>
       <c r="FE12" t="n">
-        <v>6.502724863821641e-05</v>
+        <v>0.001339352573268116</v>
       </c>
       <c r="FF12" t="n">
-        <v>0.0002320414932910353</v>
+        <v>0.004715568386018276</v>
       </c>
       <c r="FG12" t="n">
-        <v>6.998135359026492e-05</v>
+        <v>0.000419755291659385</v>
       </c>
       <c r="FH12" t="n">
-        <v>0.0003029096114914864</v>
+        <v>0.01154069881886244</v>
       </c>
       <c r="FI12" t="n">
-        <v>3.507511792122386e-05</v>
+        <v>0.0005264529027044773</v>
       </c>
       <c r="FJ12" t="n">
-        <v>0.0003342957061249763</v>
+        <v>0.004297071602195501</v>
       </c>
       <c r="FK12" t="n">
-        <v>0.0002094650990329683</v>
+        <v>0.009063743986189365</v>
       </c>
       <c r="FL12" t="n">
-        <v>3.555732837412506e-05</v>
+        <v>0.003769171424210072</v>
       </c>
       <c r="FM12" t="n">
-        <v>6.992333510424942e-06</v>
+        <v>0.002297345083206892</v>
       </c>
       <c r="FN12" t="n">
-        <v>0.0002659710880834609</v>
+        <v>0.001297210576012731</v>
       </c>
       <c r="FO12" t="n">
-        <v>7.803125481586903e-05</v>
+        <v>0.008665613830089569</v>
       </c>
       <c r="FP12" t="n">
-        <v>5.362738738767803e-05</v>
+        <v>0.00152491801418364</v>
       </c>
       <c r="FQ12" t="n">
-        <v>0.0004159285745117813</v>
+        <v>0.01433574594557285</v>
       </c>
       <c r="FR12" t="n">
-        <v>4.759881994687021e-05</v>
+        <v>0.01094720233231783</v>
       </c>
       <c r="FS12" t="n">
-        <v>0.0005400276859290898</v>
+        <v>0.01378684677183628</v>
       </c>
       <c r="FT12" t="n">
-        <v>0.0004385832289699465</v>
+        <v>0.0001342273317277431</v>
       </c>
       <c r="FU12" t="n">
-        <v>0.0001441230706404895</v>
+        <v>0.01056727208197117</v>
       </c>
       <c r="FV12" t="n">
-        <v>0.0001180316030513495</v>
+        <v>0.003592680906876922</v>
       </c>
       <c r="FW12" t="n">
-        <v>4.857670865021646e-05</v>
+        <v>0.0007324698381125927</v>
       </c>
       <c r="FX12" t="n">
-        <v>2.49797958531417e-05</v>
+        <v>0.0007427036762237549</v>
       </c>
       <c r="FY12" t="n">
-        <v>0.000100615419796668</v>
+        <v>0.01061617024242878</v>
       </c>
       <c r="FZ12" t="n">
-        <v>1.539440745546017e-06</v>
+        <v>0.01510368939489126</v>
       </c>
       <c r="GA12" t="n">
-        <v>0.0001011327403830364</v>
+        <v>0.01997634023427963</v>
       </c>
       <c r="GB12" t="n">
-        <v>0.0004033126460853964</v>
+        <v>0.003404352813959122</v>
       </c>
       <c r="GC12" t="n">
-        <v>0.0004721357836388052</v>
+        <v>0.002945682965219021</v>
       </c>
       <c r="GD12" t="n">
-        <v>5.487503585754894e-05</v>
+        <v>0.007005093619227409</v>
       </c>
       <c r="GE12" t="n">
-        <v>0.0006084403139539063</v>
+        <v>0.005823361687362194</v>
       </c>
       <c r="GF12" t="n">
-        <v>9.944164048647508e-05</v>
+        <v>0.007515741512179375</v>
       </c>
       <c r="GG12" t="n">
-        <v>1.680705827311613e-05</v>
+        <v>0.004053627140820026</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>0.02308423258364201</v>
+        <v>0.0001379222376272082</v>
       </c>
       <c r="B13" t="n">
-        <v>0.2700941860675812</v>
+        <v>0.00060332688735798</v>
       </c>
       <c r="C13" t="n">
-        <v>0.0121845779940486</v>
+        <v>2.386633786954917e-05</v>
       </c>
       <c r="D13" t="n">
-        <v>0.1400018483400345</v>
+        <v>0.0002245729410788044</v>
       </c>
       <c r="E13" t="n">
-        <v>0.03652042523026466</v>
+        <v>5.665910430252552e-05</v>
       </c>
       <c r="F13" t="n">
-        <v>0.2636938095092773</v>
+        <v>0.0004183195997029543</v>
       </c>
       <c r="G13" t="n">
-        <v>0.004772966727614403</v>
+        <v>8.532208448741585e-05</v>
       </c>
       <c r="H13" t="n">
-        <v>0.09588789939880371</v>
+        <v>6.466812192229554e-05</v>
       </c>
       <c r="I13" t="n">
-        <v>0.03361897543072701</v>
+        <v>2.750852218014188e-05</v>
       </c>
       <c r="J13" t="n">
-        <v>0.05820509791374207</v>
+        <v>5.813430470880121e-05</v>
       </c>
       <c r="K13" t="n">
-        <v>0.2540064752101898</v>
+        <v>0.0007246483583003283</v>
       </c>
       <c r="L13" t="n">
-        <v>0.00303701451048255</v>
+        <v>7.536767225246876e-05</v>
       </c>
       <c r="M13" t="n">
-        <v>0.1028423234820366</v>
+        <v>0.0003814349474851042</v>
       </c>
       <c r="N13" t="n">
-        <v>0.001460518687963486</v>
+        <v>0.0001224307052325457</v>
       </c>
       <c r="O13" t="n">
-        <v>0.2426442503929138</v>
+        <v>0.0004337758291512728</v>
       </c>
       <c r="P13" t="n">
-        <v>0.01864532195031643</v>
+        <v>1.376226464344654e-05</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.04840560629963875</v>
+        <v>8.486683509545401e-05</v>
       </c>
       <c r="R13" t="n">
-        <v>0.009806429035961628</v>
+        <v>7.047014514682814e-05</v>
       </c>
       <c r="S13" t="n">
-        <v>0.01251366175711155</v>
+        <v>3.325661236885935e-05</v>
       </c>
       <c r="T13" t="n">
-        <v>0.01337157469242811</v>
+        <v>9.048234642250463e-05</v>
       </c>
       <c r="U13" t="n">
-        <v>0.02460465952754021</v>
+        <v>1.873733708634973e-05</v>
       </c>
       <c r="V13" t="n">
-        <v>0.04296129196882248</v>
+        <v>4.147693834966049e-05</v>
       </c>
       <c r="W13" t="n">
-        <v>0.07205949723720551</v>
+        <v>3.375276355654933e-05</v>
       </c>
       <c r="X13" t="n">
-        <v>0.01753161661326885</v>
+        <v>7.472515426343307e-05</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.02438260987401009</v>
+        <v>4.785719283972867e-05</v>
       </c>
       <c r="Z13" t="n">
-        <v>0.06725317239761353</v>
+        <v>0.000193166866665706</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.04252458363771439</v>
+        <v>5.251072252576705e-06</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.005329102277755737</v>
+        <v>7.954739703563973e-05</v>
       </c>
       <c r="AC13" t="n">
-        <v>0.01731729507446289</v>
+        <v>5.514948134077713e-05</v>
       </c>
       <c r="AD13" t="n">
-        <v>0.01848237402737141</v>
+        <v>2.650616079336032e-05</v>
       </c>
       <c r="AE13" t="n">
-        <v>0.01523731276392937</v>
+        <v>0.0001455357414670289</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.02967013418674469</v>
+        <v>7.519321661675349e-05</v>
       </c>
       <c r="AG13" t="n">
-        <v>0.02477460727095604</v>
+        <v>0.0001449472911190242</v>
       </c>
       <c r="AH13" t="n">
-        <v>0.01395186129957438</v>
+        <v>6.234004104044288e-07</v>
       </c>
       <c r="AI13" t="n">
-        <v>0.006000030785799026</v>
+        <v>0.0002691161644179374</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0.02479415200650692</v>
+        <v>4.488327977014706e-05</v>
       </c>
       <c r="AK13" t="n">
-        <v>0.02446242980659008</v>
+        <v>0.0001086957345250994</v>
       </c>
       <c r="AL13" t="n">
-        <v>0.04352667927742004</v>
+        <v>6.493673572549596e-05</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.001667232252657413</v>
+        <v>5.82121720071882e-06</v>
       </c>
       <c r="AN13" t="n">
-        <v>0.006943641230463982</v>
+        <v>6.377438694471493e-05</v>
       </c>
       <c r="AO13" t="n">
-        <v>0.001152393873780966</v>
+        <v>1.137665458372794e-05</v>
       </c>
       <c r="AP13" t="n">
-        <v>0.03269098326563835</v>
+        <v>1.580831667524762e-05</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0.002945689484477043</v>
+        <v>4.628689930541441e-05</v>
       </c>
       <c r="AR13" t="n">
-        <v>0.0170839000493288</v>
+        <v>0.0001864376827143133</v>
       </c>
       <c r="AS13" t="n">
-        <v>0.02470722794532776</v>
+        <v>2.672809387149755e-05</v>
       </c>
       <c r="AT13" t="n">
-        <v>0.02915184944868088</v>
+        <v>0.0001250760979019105</v>
       </c>
       <c r="AU13" t="n">
-        <v>0.1975713521242142</v>
+        <v>0.0004507347766775638</v>
       </c>
       <c r="AV13" t="n">
-        <v>0.001950948499143124</v>
+        <v>8.599760622018948e-05</v>
       </c>
       <c r="AW13" t="n">
-        <v>0.05770295858383179</v>
+        <v>0.0001190951152238995</v>
       </c>
       <c r="AX13" t="n">
-        <v>0.02765282057225704</v>
+        <v>0.0002676100993994623</v>
       </c>
       <c r="AY13" t="n">
-        <v>0.1364703774452209</v>
+        <v>0.0002266863157274202</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0.01165301818400621</v>
+        <v>1.267196239496116e-05</v>
       </c>
       <c r="BA13" t="n">
-        <v>0.02164324559271336</v>
+        <v>2.15978088817792e-05</v>
       </c>
       <c r="BB13" t="n">
-        <v>0.0653376579284668</v>
+        <v>6.117662996985018e-05</v>
       </c>
       <c r="BC13" t="n">
-        <v>0.02452132478356361</v>
+        <v>7.299918797798455e-05</v>
       </c>
       <c r="BD13" t="n">
-        <v>0.0472516342997551</v>
+        <v>8.508354949299246e-05</v>
       </c>
       <c r="BE13" t="n">
-        <v>0.06001319363713264</v>
+        <v>1.384667848469689e-05</v>
       </c>
       <c r="BF13" t="n">
-        <v>0.009381678886711597</v>
+        <v>0.000150211009895429</v>
       </c>
       <c r="BG13" t="n">
-        <v>0.05216707661747932</v>
+        <v>9.513106488157064e-05</v>
       </c>
       <c r="BH13" t="n">
-        <v>0.08037464320659637</v>
+        <v>9.948742808774114e-05</v>
       </c>
       <c r="BI13" t="n">
-        <v>0.01857436820864677</v>
+        <v>3.327930244267918e-05</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.01689907163381577</v>
+        <v>0.0001095314437407069</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.001865943893790245</v>
+        <v>6.083115295041353e-05</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.001097093801945448</v>
+        <v>3.787861351156607e-05</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.07127029448747635</v>
+        <v>8.217164577217773e-06</v>
       </c>
       <c r="BN13" t="n">
-        <v>0.01000308804214001</v>
+        <v>4.475213427213021e-05</v>
       </c>
       <c r="BO13" t="n">
-        <v>0.02312815375626087</v>
+        <v>9.329060412710533e-05</v>
       </c>
       <c r="BP13" t="n">
-        <v>0.006425327155739069</v>
+        <v>6.112373375799507e-05</v>
       </c>
       <c r="BQ13" t="n">
-        <v>0.00216773385182023</v>
+        <v>2.496818706276827e-05</v>
       </c>
       <c r="BR13" t="n">
-        <v>0.01239768415689468</v>
+        <v>0.0001634231593925506</v>
       </c>
       <c r="BS13" t="n">
-        <v>0.00272298650816083</v>
+        <v>2.066748129436746e-05</v>
       </c>
       <c r="BT13" t="n">
-        <v>0.004344434011727571</v>
+        <v>0.0001061266957549378</v>
       </c>
       <c r="BU13" t="n">
-        <v>0.01975430175662041</v>
+        <v>5.948857142357156e-05</v>
       </c>
       <c r="BV13" t="n">
-        <v>0.1018017828464508</v>
+        <v>0.0002492911298759282</v>
       </c>
       <c r="BW13" t="n">
-        <v>0.0128833893686533</v>
+        <v>5.385172698879614e-06</v>
       </c>
       <c r="BX13" t="n">
-        <v>0.05302686616778374</v>
+        <v>9.010566282086074e-05</v>
       </c>
       <c r="BY13" t="n">
-        <v>0.02663053944706917</v>
+        <v>7.596390787512064e-06</v>
       </c>
       <c r="BZ13" t="n">
-        <v>0.05129071325063705</v>
+        <v>0.0001514065079391003</v>
       </c>
       <c r="CA13" t="n">
-        <v>0.01684296317398548</v>
+        <v>5.649985541822389e-05</v>
       </c>
       <c r="CB13" t="n">
-        <v>0.0006298068910837173</v>
+        <v>3.679845394799486e-05</v>
       </c>
       <c r="CC13" t="n">
-        <v>0.04623309522867203</v>
+        <v>6.286385178100318e-05</v>
       </c>
       <c r="CD13" t="n">
-        <v>0.004180599004030228</v>
+        <v>2.518339897505939e-06</v>
       </c>
       <c r="CE13" t="n">
-        <v>0.03300882875919342</v>
+        <v>0.0001712415687507018</v>
       </c>
       <c r="CF13" t="n">
-        <v>0.0277280043810606</v>
+        <v>5.362235970096663e-05</v>
       </c>
       <c r="CG13" t="n">
-        <v>0.02199049666523933</v>
+        <v>6.68250722810626e-05</v>
       </c>
       <c r="CH13" t="n">
-        <v>0.003947626799345016</v>
+        <v>3.641784132923931e-06</v>
       </c>
       <c r="CI13" t="n">
-        <v>0.04461454972624779</v>
+        <v>0.0001124971167882904</v>
       </c>
       <c r="CJ13" t="n">
-        <v>0.01749347895383835</v>
+        <v>3.280120290583e-05</v>
       </c>
       <c r="CK13" t="n">
-        <v>0.01310320012271404</v>
+        <v>2.101906648022123e-05</v>
       </c>
       <c r="CL13" t="n">
-        <v>0.02309484034776688</v>
+        <v>4.904096203972585e-05</v>
       </c>
       <c r="CM13" t="n">
-        <v>0.05126170441508293</v>
+        <v>2.490686347300652e-05</v>
       </c>
       <c r="CN13" t="n">
-        <v>0.005598020739853382</v>
+        <v>0.0001243765582330525</v>
       </c>
       <c r="CO13" t="n">
-        <v>0.006117299664765596</v>
+        <v>0.0001451606367481872</v>
       </c>
       <c r="CP13" t="n">
-        <v>0.01507003419101238</v>
+        <v>0.0001890704588731751</v>
       </c>
       <c r="CQ13" t="n">
-        <v>0.01949442736804485</v>
+        <v>3.120230758213438e-05</v>
       </c>
       <c r="CR13" t="n">
-        <v>0.003078053239732981</v>
+        <v>9.869636414805427e-05</v>
       </c>
       <c r="CS13" t="n">
-        <v>0.05300744995474815</v>
+        <v>1.534580587758683e-05</v>
       </c>
       <c r="CT13" t="n">
-        <v>0.05403919517993927</v>
+        <v>0.0001457267353544012</v>
       </c>
       <c r="CU13" t="n">
-        <v>0.005935311317443848</v>
+        <v>5.162079833098687e-05</v>
       </c>
       <c r="CV13" t="n">
-        <v>0.002167431637644768</v>
+        <v>3.56194723281078e-05</v>
       </c>
       <c r="CW13" t="n">
-        <v>0.02796841599047184</v>
+        <v>0.0001706971816020086</v>
       </c>
       <c r="CX13" t="n">
-        <v>0.02205833047628403</v>
+        <v>5.19216300745029e-05</v>
       </c>
       <c r="CY13" t="n">
-        <v>0.03464195877313614</v>
+        <v>9.095513087231666e-05</v>
       </c>
       <c r="CZ13" t="n">
-        <v>0.005702638067305088</v>
+        <v>9.542392945149913e-06</v>
       </c>
       <c r="DA13" t="n">
-        <v>0.04850707203149796</v>
+        <v>0.0001289973297389224</v>
       </c>
       <c r="DB13" t="n">
-        <v>0.01737946271896362</v>
+        <v>8.475824870401993e-06</v>
       </c>
       <c r="DC13" t="n">
-        <v>0.02640135586261749</v>
+        <v>2.865522583306301e-05</v>
       </c>
       <c r="DD13" t="n">
-        <v>0.008576655760407448</v>
+        <v>4.213574720779434e-05</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.005576861556619406</v>
+        <v>4.155690839979798e-05</v>
       </c>
       <c r="DF13" t="n">
-        <v>0.009329527616500854</v>
+        <v>0.0001706390321487561</v>
       </c>
       <c r="DG13" t="n">
-        <v>0.008913579396903515</v>
+        <v>3.108791133854538e-06</v>
       </c>
       <c r="DH13" t="n">
-        <v>0.1084200292825699</v>
+        <v>2.103563565469813e-05</v>
       </c>
       <c r="DI13" t="n">
-        <v>0.03606671094894409</v>
+        <v>0.0002405786653980613</v>
       </c>
       <c r="DJ13" t="n">
-        <v>0.002494313754141331</v>
+        <v>0.0001304246834479272</v>
       </c>
       <c r="DK13" t="n">
-        <v>0.005248419940471649</v>
+        <v>7.863876817282289e-05</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.03802705556154251</v>
+        <v>3.175515303155407e-06</v>
       </c>
       <c r="DM13" t="n">
-        <v>0.01558523345738649</v>
+        <v>2.187007339671254e-07</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.005589612759649754</v>
+        <v>3.75410781998653e-05</v>
       </c>
       <c r="DO13" t="n">
-        <v>0.007432531099766493</v>
+        <v>0.0001042774820234627</v>
       </c>
       <c r="DP13" t="n">
-        <v>0.01535838469862938</v>
+        <v>5.361764124245383e-05</v>
       </c>
       <c r="DQ13" t="n">
-        <v>0.002569898962974548</v>
+        <v>8.243765478255227e-05</v>
       </c>
       <c r="DR13" t="n">
-        <v>0.01032143458724022</v>
+        <v>4.309947689762339e-05</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.004753006622195244</v>
+        <v>4.314210673328489e-05</v>
       </c>
       <c r="DT13" t="n">
-        <v>0.02424870431423187</v>
+        <v>7.904272933956236e-05</v>
       </c>
       <c r="DU13" t="n">
-        <v>0.0107392119243741</v>
+        <v>0.000167968450114131</v>
       </c>
       <c r="DV13" t="n">
-        <v>0.03175603970885277</v>
+        <v>6.320500688161701e-05</v>
       </c>
       <c r="DW13" t="n">
-        <v>0.002269883640110493</v>
+        <v>3.931413448299281e-05</v>
       </c>
       <c r="DX13" t="n">
-        <v>0.02471088618040085</v>
+        <v>8.240250281232875e-06</v>
       </c>
       <c r="DY13" t="n">
-        <v>0.02203634567558765</v>
+        <v>6.83101243339479e-05</v>
       </c>
       <c r="DZ13" t="n">
-        <v>0.002790269441902637</v>
+        <v>8.871954923961312e-05</v>
       </c>
       <c r="EA13" t="n">
-        <v>0.0009887428022921085</v>
+        <v>0.0001355179265374318</v>
       </c>
       <c r="EB13" t="n">
-        <v>0.01825403608381748</v>
+        <v>2.874599158531055e-05</v>
       </c>
       <c r="EC13" t="n">
-        <v>0.002931427676230669</v>
+        <v>6.502319592982531e-05</v>
       </c>
       <c r="ED13" t="n">
-        <v>0.01158789545297623</v>
+        <v>8.445711864624172e-05</v>
       </c>
       <c r="EE13" t="n">
-        <v>0.0023620689753443</v>
+        <v>9.713500912766904e-05</v>
       </c>
       <c r="EF13" t="n">
-        <v>0.01429750118404627</v>
+        <v>8.257808985945303e-06</v>
       </c>
       <c r="EG13" t="n">
-        <v>0.03707843646407127</v>
+        <v>7.280324643943459e-05</v>
       </c>
       <c r="EH13" t="n">
-        <v>0.01671922020614147</v>
+        <v>1.393225829815492e-06</v>
       </c>
       <c r="EI13" t="n">
-        <v>0.007259863428771496</v>
+        <v>1.371270627714694e-06</v>
       </c>
       <c r="EJ13" t="n">
-        <v>0.002123698126524687</v>
+        <v>1.435308149666525e-05</v>
       </c>
       <c r="EK13" t="n">
-        <v>0.04727816581726074</v>
+        <v>3.115346044069156e-05</v>
       </c>
       <c r="EL13" t="n">
-        <v>0.01379426103085279</v>
+        <v>1.928487108671106e-05</v>
       </c>
       <c r="EM13" t="n">
-        <v>0.006734445225447416</v>
+        <v>1.246563169843284e-05</v>
       </c>
       <c r="EN13" t="n">
-        <v>0.01293251849710941</v>
+        <v>2.480787770764437e-05</v>
       </c>
       <c r="EO13" t="n">
-        <v>0.005293264053761959</v>
+        <v>2.611778108985163e-05</v>
       </c>
       <c r="EP13" t="n">
-        <v>0.01254746876657009</v>
+        <v>6.192229920998216e-05</v>
       </c>
       <c r="EQ13" t="n">
-        <v>0.01478577218949795</v>
+        <v>8.711525879334658e-05</v>
       </c>
       <c r="ER13" t="n">
-        <v>0.0212175901979208</v>
+        <v>7.656376692466438e-05</v>
       </c>
       <c r="ES13" t="n">
-        <v>0.009346412494778633</v>
+        <v>7.212260970845819e-05</v>
       </c>
       <c r="ET13" t="n">
-        <v>0.04084492847323418</v>
+        <v>9.845624299487099e-05</v>
       </c>
       <c r="EU13" t="n">
-        <v>0.031680628657341</v>
+        <v>2.897000013035722e-05</v>
       </c>
       <c r="EV13" t="n">
-        <v>0.07610173523426056</v>
+        <v>6.618309998884797e-05</v>
       </c>
       <c r="EW13" t="n">
-        <v>0.01037327572703362</v>
+        <v>6.306174327619374e-05</v>
       </c>
       <c r="EX13" t="n">
-        <v>0.002322782995179296</v>
+        <v>2.325326386198867e-05</v>
       </c>
       <c r="EY13" t="n">
-        <v>0.02568789012730122</v>
+        <v>0.0001945614203577861</v>
       </c>
       <c r="EZ13" t="n">
-        <v>0.01824776083230972</v>
+        <v>4.161739707342349e-05</v>
       </c>
       <c r="FA13" t="n">
-        <v>0.03007044643163681</v>
+        <v>0.0001102497626561671</v>
       </c>
       <c r="FB13" t="n">
-        <v>0.001091984333470464</v>
+        <v>4.156550130574033e-05</v>
       </c>
       <c r="FC13" t="n">
-        <v>0.0403733029961586</v>
+        <v>9.76937371888198e-05</v>
       </c>
       <c r="FD13" t="n">
-        <v>0.02913432754576206</v>
+        <v>2.757054244284518e-05</v>
       </c>
       <c r="FE13" t="n">
-        <v>0.01410173624753952</v>
+        <v>2.503965515643358e-05</v>
       </c>
       <c r="FF13" t="n">
-        <v>0.02204821072518826</v>
+        <v>2.014311940001789e-05</v>
       </c>
       <c r="FG13" t="n">
-        <v>0.01217825710773468</v>
+        <v>3.408066913834773e-05</v>
       </c>
       <c r="FH13" t="n">
-        <v>0.0006711384048685431</v>
+        <v>0.0002240671310573816</v>
       </c>
       <c r="FI13" t="n">
-        <v>0.009708542376756668</v>
+        <v>0.0001017417016555555</v>
       </c>
       <c r="FJ13" t="n">
-        <v>0.04318524897098541</v>
+        <v>0.0001756510027917102</v>
       </c>
       <c r="FK13" t="n">
-        <v>0.01101253926753998</v>
+        <v>0.0001276210095966235</v>
       </c>
       <c r="FL13" t="n">
-        <v>0.02679337002336979</v>
+        <v>0.0001539119111839682</v>
       </c>
       <c r="FM13" t="n">
-        <v>0.008857926353812218</v>
+        <v>1.320474530075444e-05</v>
       </c>
       <c r="FN13" t="n">
-        <v>0.02129599824547768</v>
+        <v>9.878941636998206e-05</v>
       </c>
       <c r="FO13" t="n">
-        <v>0.01910114102065563</v>
+        <v>8.907033770810813e-05</v>
       </c>
       <c r="FP13" t="n">
-        <v>0.01442377828061581</v>
+        <v>3.210777140338905e-05</v>
       </c>
       <c r="FQ13" t="n">
-        <v>0.05279998481273651</v>
+        <v>6.393679359462112e-05</v>
       </c>
       <c r="FR13" t="n">
-        <v>0.03885854780673981</v>
+        <v>9.310065797762945e-05</v>
       </c>
       <c r="FS13" t="n">
-        <v>0.02426140382885933</v>
+        <v>0.0001375442370772362</v>
       </c>
       <c r="FT13" t="n">
-        <v>0.01370736956596375</v>
+        <v>0.0001021385687636212</v>
       </c>
       <c r="FU13" t="n">
-        <v>0.008922290056943893</v>
+        <v>6.593899161089212e-05</v>
       </c>
       <c r="FV13" t="n">
-        <v>0.02142512053251266</v>
+        <v>5.370668441173621e-05</v>
       </c>
       <c r="FW13" t="n">
-        <v>0.003675260348245502</v>
+        <v>4.600562897394411e-05</v>
       </c>
       <c r="FX13" t="n">
-        <v>0.01859917491674423</v>
+        <v>1.418718602508307e-05</v>
       </c>
       <c r="FY13" t="n">
-        <v>0.04650051146745682</v>
+        <v>0.0001490455470047891</v>
       </c>
       <c r="FZ13" t="n">
-        <v>0.01996774598956108</v>
+        <v>3.463673056103289e-05</v>
       </c>
       <c r="GA13" t="n">
-        <v>0.03209981322288513</v>
+        <v>0.0002752907166723162</v>
       </c>
       <c r="GB13" t="n">
-        <v>0.01183719653636217</v>
+        <v>1.038084519677795e-05</v>
       </c>
       <c r="GC13" t="n">
-        <v>0.02790356427431107</v>
+        <v>0.0002713850990403444</v>
       </c>
       <c r="GD13" t="n">
-        <v>0.01698098331689835</v>
+        <v>0.0001446290261810645</v>
       </c>
       <c r="GE13" t="n">
-        <v>0.1272857487201691</v>
+        <v>3.438871135585941e-05</v>
       </c>
       <c r="GF13" t="n">
-        <v>0.001055099070072174</v>
+        <v>3.097085209446959e-05</v>
       </c>
       <c r="GG13" t="n">
-        <v>0.005722253583371639</v>
+        <v>3.402948277653195e-05</v>
       </c>
     </row>
     <row r="14">
@@ -8965,1140 +8965,1140 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>0.0001625073055038229</v>
+        <v>2.030251522455728e-10</v>
       </c>
       <c r="B16" t="n">
-        <v>0.003670740406960249</v>
+        <v>3.950492910576031e-08</v>
       </c>
       <c r="C16" t="n">
-        <v>6.533721898449585e-05</v>
+        <v>3.046680063789609e-08</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0009331564069725573</v>
+        <v>9.303640524649381e-09</v>
       </c>
       <c r="E16" t="n">
-        <v>0.001097588567063212</v>
+        <v>7.124146828019207e-10</v>
       </c>
       <c r="F16" t="n">
-        <v>0.001307672588154674</v>
+        <v>1.943373639790025e-08</v>
       </c>
       <c r="G16" t="n">
-        <v>0.0004255551612004638</v>
+        <v>7.302858762159303e-09</v>
       </c>
       <c r="H16" t="n">
-        <v>0.0005912304040975869</v>
+        <v>2.739471050006159e-08</v>
       </c>
       <c r="I16" t="n">
-        <v>0.00065939238993451</v>
+        <v>2.764710593794462e-08</v>
       </c>
       <c r="J16" t="n">
-        <v>0.0002234159910585731</v>
+        <v>1.713171826622784e-09</v>
       </c>
       <c r="K16" t="n">
-        <v>0.003435318591073155</v>
+        <v>4.346865267734756e-08</v>
       </c>
       <c r="L16" t="n">
-        <v>7.02252727933228e-05</v>
+        <v>3.473166998446686e-08</v>
       </c>
       <c r="M16" t="n">
-        <v>0.0004990622983314097</v>
+        <v>1.130852567143847e-08</v>
       </c>
       <c r="N16" t="n">
-        <v>0.0002625968481879681</v>
+        <v>1.333903743017117e-08</v>
       </c>
       <c r="O16" t="n">
-        <v>0.001154388766735792</v>
+        <v>1.513963887589398e-08</v>
       </c>
       <c r="P16" t="n">
-        <v>0.0002413186739431694</v>
+        <v>5.129834335093619e-09</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.0001780540042091161</v>
+        <v>1.411878702839431e-08</v>
       </c>
       <c r="R16" t="n">
-        <v>0.000681525852996856</v>
+        <v>3.386895652823796e-09</v>
       </c>
       <c r="S16" t="n">
-        <v>0.000188314777915366</v>
+        <v>1.559517492921714e-08</v>
       </c>
       <c r="T16" t="n">
-        <v>0.00041594059439376</v>
+        <v>2.698130252554165e-08</v>
       </c>
       <c r="U16" t="n">
-        <v>2.658635457919445e-05</v>
+        <v>8.700066445044286e-09</v>
       </c>
       <c r="V16" t="n">
-        <v>0.0002292959106853232</v>
+        <v>1.439983776663212e-08</v>
       </c>
       <c r="W16" t="n">
-        <v>0.0003594657173380256</v>
+        <v>5.157219540308233e-09</v>
       </c>
       <c r="X16" t="n">
-        <v>0.0001808006782084703</v>
+        <v>5.194793484264437e-10</v>
       </c>
       <c r="Y16" t="n">
-        <v>6.908408249728382e-05</v>
+        <v>1.976443897433455e-09</v>
       </c>
       <c r="Z16" t="n">
-        <v>0.000536738836672157</v>
+        <v>1.009973527033026e-08</v>
       </c>
       <c r="AA16" t="n">
-        <v>0.0002643791376613081</v>
+        <v>1.779901559473274e-08</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.0002589089854154736</v>
+        <v>2.550426358993718e-08</v>
       </c>
       <c r="AC16" t="n">
-        <v>0.0001823353377403691</v>
+        <v>5.74426284316587e-09</v>
       </c>
       <c r="AD16" t="n">
-        <v>0.0001477868936490268</v>
+        <v>2.033282697766481e-08</v>
       </c>
       <c r="AE16" t="n">
-        <v>0.0001958820794243366</v>
+        <v>9.136059908598781e-09</v>
       </c>
       <c r="AF16" t="n">
-        <v>3.366581950103864e-05</v>
+        <v>3.386417368744787e-09</v>
       </c>
       <c r="AG16" t="n">
-        <v>6.626610411331058e-05</v>
+        <v>1.540501948227302e-08</v>
       </c>
       <c r="AH16" t="n">
-        <v>7.015810115262866e-05</v>
+        <v>8.951936969481267e-09</v>
       </c>
       <c r="AI16" t="n">
-        <v>2.627723733894527e-05</v>
+        <v>2.399347565074095e-08</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0.000165001314599067</v>
+        <v>2.7566601445983e-08</v>
       </c>
       <c r="AK16" t="n">
-        <v>0.0005129930796101689</v>
+        <v>1.486855438770363e-08</v>
       </c>
       <c r="AL16" t="n">
-        <v>0.0004245954041834921</v>
+        <v>2.090404116472655e-08</v>
       </c>
       <c r="AM16" t="n">
-        <v>0.0001317017304245383</v>
+        <v>2.408064858627768e-08</v>
       </c>
       <c r="AN16" t="n">
-        <v>0.00026314752176404</v>
+        <v>2.128249354527156e-09</v>
       </c>
       <c r="AO16" t="n">
-        <v>0.000236154068261385</v>
+        <v>8.489512204334915e-09</v>
       </c>
       <c r="AP16" t="n">
-        <v>0.0003279149241279811</v>
+        <v>9.373423814906801e-09</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0.0002231803664471954</v>
+        <v>4.882160453689721e-09</v>
       </c>
       <c r="AR16" t="n">
-        <v>8.97034551599063e-05</v>
+        <v>3.765283640433381e-09</v>
       </c>
       <c r="AS16" t="n">
-        <v>0.0002602206950541586</v>
+        <v>4.844596279696134e-09</v>
       </c>
       <c r="AT16" t="n">
-        <v>0.0002756398171186447</v>
+        <v>1.851344855197112e-08</v>
       </c>
       <c r="AU16" t="n">
-        <v>0.002395435236394405</v>
+        <v>2.205485749584568e-08</v>
       </c>
       <c r="AV16" t="n">
-        <v>0.0004316969425417483</v>
+        <v>1.149877881800876e-08</v>
       </c>
       <c r="AW16" t="n">
-        <v>7.445483788615093e-05</v>
+        <v>1.947604744145792e-09</v>
       </c>
       <c r="AX16" t="n">
-        <v>8.692317351233214e-05</v>
+        <v>2.436651769244236e-08</v>
       </c>
       <c r="AY16" t="n">
-        <v>0.0003603432851377875</v>
+        <v>1.266818983047813e-09</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0.0006580305634997785</v>
+        <v>3.67835584214049e-09</v>
       </c>
       <c r="BA16" t="n">
-        <v>0.000418921816162765</v>
+        <v>3.467373721477429e-09</v>
       </c>
       <c r="BB16" t="n">
-        <v>0.0002177967253373936</v>
+        <v>1.269310523355216e-08</v>
       </c>
       <c r="BC16" t="n">
-        <v>0.0001899121562018991</v>
+        <v>4.434961908827972e-08</v>
       </c>
       <c r="BD16" t="n">
-        <v>0.0005346187390387058</v>
+        <v>6.028759713672116e-08</v>
       </c>
       <c r="BE16" t="n">
-        <v>0.0005369714926928282</v>
+        <v>1.375388780644471e-08</v>
       </c>
       <c r="BF16" t="n">
-        <v>9.533456614008173e-05</v>
+        <v>1.116099213049893e-08</v>
       </c>
       <c r="BG16" t="n">
-        <v>0.0009622533107176423</v>
+        <v>4.531333885893218e-08</v>
       </c>
       <c r="BH16" t="n">
-        <v>0.000657912518363446</v>
+        <v>1.481341493914101e-09</v>
       </c>
       <c r="BI16" t="n">
-        <v>0.0001465335371904075</v>
+        <v>1.115594727707503e-08</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0.0003492776013445109</v>
+        <v>3.351025412712261e-08</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.0005166225600987673</v>
+        <v>7.22811819287017e-08</v>
       </c>
       <c r="BL16" t="n">
-        <v>0.0001288246130570769</v>
+        <v>6.377255612477484e-09</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.0004360439488664269</v>
+        <v>1.140568173241263e-08</v>
       </c>
       <c r="BN16" t="n">
-        <v>9.339325333712623e-05</v>
+        <v>1.172163610618782e-08</v>
       </c>
       <c r="BO16" t="n">
-        <v>9.29082598304376e-05</v>
+        <v>5.946507730669737e-10</v>
       </c>
       <c r="BP16" t="n">
-        <v>8.740630437387154e-05</v>
+        <v>4.941675513236987e-09</v>
       </c>
       <c r="BQ16" t="n">
-        <v>0.0001695942773949355</v>
+        <v>8.480824043033408e-09</v>
       </c>
       <c r="BR16" t="n">
-        <v>0.0002502007118891925</v>
+        <v>1.050726083917652e-08</v>
       </c>
       <c r="BS16" t="n">
-        <v>5.276987212710083e-05</v>
+        <v>1.416623707228837e-08</v>
       </c>
       <c r="BT16" t="n">
-        <v>0.0001371926628053188</v>
+        <v>1.077951772288088e-08</v>
       </c>
       <c r="BU16" t="n">
-        <v>3.089000529143959e-05</v>
+        <v>2.501766438456343e-08</v>
       </c>
       <c r="BV16" t="n">
-        <v>0.001302944030612707</v>
+        <v>2.152306421976391e-08</v>
       </c>
       <c r="BW16" t="n">
-        <v>0.0001800228492356837</v>
+        <v>5.000477365513234e-09</v>
       </c>
       <c r="BX16" t="n">
-        <v>0.0002044078282779083</v>
+        <v>2.597047465968672e-09</v>
       </c>
       <c r="BY16" t="n">
-        <v>0.0001010378473438323</v>
+        <v>3.395038694620212e-09</v>
       </c>
       <c r="BZ16" t="n">
-        <v>0.0001814131246646866</v>
+        <v>3.571891893372481e-09</v>
       </c>
       <c r="CA16" t="n">
-        <v>0.0001317189598921686</v>
+        <v>2.879022797941388e-09</v>
       </c>
       <c r="CB16" t="n">
-        <v>7.511259173043072e-05</v>
+        <v>1.852229036813924e-09</v>
       </c>
       <c r="CC16" t="n">
-        <v>7.095192995620891e-05</v>
+        <v>5.765140365099342e-09</v>
       </c>
       <c r="CD16" t="n">
-        <v>0.0001724522007862106</v>
+        <v>3.087699873560723e-09</v>
       </c>
       <c r="CE16" t="n">
-        <v>0.000619681435637176</v>
+        <v>1.258426918226974e-09</v>
       </c>
       <c r="CF16" t="n">
-        <v>0.0001032346626743674</v>
+        <v>4.240699347235477e-09</v>
       </c>
       <c r="CG16" t="n">
-        <v>0.0001043530501192436</v>
+        <v>3.609515797364793e-09</v>
       </c>
       <c r="CH16" t="n">
-        <v>0.0001148991723312065</v>
+        <v>3.280193894283912e-09</v>
       </c>
       <c r="CI16" t="n">
-        <v>0.0001485629036324099</v>
+        <v>7.616643316055161e-09</v>
       </c>
       <c r="CJ16" t="n">
-        <v>0.0002266421215608716</v>
+        <v>4.063967828926707e-09</v>
       </c>
       <c r="CK16" t="n">
-        <v>7.059287599986419e-05</v>
+        <v>3.055255159978287e-09</v>
       </c>
       <c r="CL16" t="n">
-        <v>0.0001690173521637917</v>
+        <v>2.242160235255142e-09</v>
       </c>
       <c r="CM16" t="n">
-        <v>0.0008805063553154469</v>
+        <v>1.143378014489826e-08</v>
       </c>
       <c r="CN16" t="n">
-        <v>0.0001358927838737145</v>
+        <v>1.02522728084864e-08</v>
       </c>
       <c r="CO16" t="n">
-        <v>0.0001872565189842135</v>
+        <v>2.497306894611029e-08</v>
       </c>
       <c r="CP16" t="n">
-        <v>0.001095279818400741</v>
+        <v>2.493849571294504e-08</v>
       </c>
       <c r="CQ16" t="n">
-        <v>0.0005429125158116221</v>
+        <v>3.552477068069493e-08</v>
       </c>
       <c r="CR16" t="n">
-        <v>0.0007014228613115847</v>
+        <v>9.302812742362221e-09</v>
       </c>
       <c r="CS16" t="n">
-        <v>0.0006165137747302651</v>
+        <v>2.561841405679388e-09</v>
       </c>
       <c r="CT16" t="n">
-        <v>0.0003684494295157492</v>
+        <v>7.609652463713701e-09</v>
       </c>
       <c r="CU16" t="n">
-        <v>0.0003251582093071193</v>
+        <v>2.42979183440184e-08</v>
       </c>
       <c r="CV16" t="n">
-        <v>0.0001656257372815162</v>
+        <v>2.057261028198809e-09</v>
       </c>
       <c r="CW16" t="n">
-        <v>0.0005676117725670338</v>
+        <v>6.115013828633664e-09</v>
       </c>
       <c r="CX16" t="n">
-        <v>9.615143062546849e-05</v>
+        <v>3.389895031347123e-09</v>
       </c>
       <c r="CY16" t="n">
-        <v>0.0002930252230726182</v>
+        <v>3.420055127989485e-09</v>
       </c>
       <c r="CZ16" t="n">
-        <v>0.0001352988183498383</v>
+        <v>3.661965397583344e-09</v>
       </c>
       <c r="DA16" t="n">
-        <v>7.947250560391694e-05</v>
+        <v>5.698228999762023e-09</v>
       </c>
       <c r="DB16" t="n">
-        <v>0.0002206504868809134</v>
+        <v>1.975438479462355e-09</v>
       </c>
       <c r="DC16" t="n">
-        <v>0.0001799060119083151</v>
+        <v>3.230793410580191e-10</v>
       </c>
       <c r="DD16" t="n">
-        <v>0.0001723882887745276</v>
+        <v>4.096753603022307e-09</v>
       </c>
       <c r="DE16" t="n">
-        <v>0.0002806545817293227</v>
+        <v>8.900656212063041e-09</v>
       </c>
       <c r="DF16" t="n">
-        <v>0.000551530160009861</v>
+        <v>3.965097050695476e-08</v>
       </c>
       <c r="DG16" t="n">
-        <v>0.0001470568822696805</v>
+        <v>4.137658038416703e-08</v>
       </c>
       <c r="DH16" t="n">
-        <v>0.0005524563021026552</v>
+        <v>8.282388108682426e-09</v>
       </c>
       <c r="DI16" t="n">
-        <v>0.001231647795066237</v>
+        <v>1.33569599825023e-08</v>
       </c>
       <c r="DJ16" t="n">
-        <v>0.001186374807730317</v>
+        <v>1.384858716590998e-08</v>
       </c>
       <c r="DK16" t="n">
-        <v>0.0001345831406069919</v>
+        <v>1.610623812098311e-08</v>
       </c>
       <c r="DL16" t="n">
-        <v>0.0002396773343207315</v>
+        <v>3.274387649909727e-09</v>
       </c>
       <c r="DM16" t="n">
-        <v>0.0008612981182523072</v>
+        <v>5.06603337058209e-09</v>
       </c>
       <c r="DN16" t="n">
-        <v>0.0002336816105525941</v>
+        <v>3.077517618521597e-08</v>
       </c>
       <c r="DO16" t="n">
-        <v>0.0001059314017766155</v>
+        <v>3.074674026493085e-08</v>
       </c>
       <c r="DP16" t="n">
-        <v>0.0002681733458302915</v>
+        <v>1.286779038878194e-08</v>
       </c>
       <c r="DQ16" t="n">
-        <v>0.0004239326517563313</v>
+        <v>8.330169443127033e-09</v>
       </c>
       <c r="DR16" t="n">
-        <v>0.0001678353291936219</v>
+        <v>1.506101199311161e-08</v>
       </c>
       <c r="DS16" t="n">
-        <v>0.0004054759338032454</v>
+        <v>2.119612485529387e-09</v>
       </c>
       <c r="DT16" t="n">
-        <v>0.0003566736704669893</v>
+        <v>1.046543829374968e-08</v>
       </c>
       <c r="DU16" t="n">
-        <v>0.000307325943140313</v>
+        <v>1.172905150781389e-08</v>
       </c>
       <c r="DV16" t="n">
-        <v>0.0002277263847645372</v>
+        <v>4.123501096131577e-09</v>
       </c>
       <c r="DW16" t="n">
-        <v>8.48897616378963e-05</v>
+        <v>1.205712951701798e-08</v>
       </c>
       <c r="DX16" t="n">
-        <v>0.0004221591807436198</v>
+        <v>2.625244022169682e-09</v>
       </c>
       <c r="DY16" t="n">
-        <v>0.0001742387830745429</v>
+        <v>2.853150604664734e-09</v>
       </c>
       <c r="DZ16" t="n">
-        <v>0.0004962297971360385</v>
+        <v>5.481942899621117e-09</v>
       </c>
       <c r="EA16" t="n">
-        <v>0.0003069161321036518</v>
+        <v>4.493176319897429e-08</v>
       </c>
       <c r="EB16" t="n">
-        <v>0.0001505095133325085</v>
+        <v>1.590006348806128e-08</v>
       </c>
       <c r="EC16" t="n">
-        <v>7.643689605174586e-05</v>
+        <v>2.518347841373725e-08</v>
       </c>
       <c r="ED16" t="n">
-        <v>0.0003267455904278904</v>
+        <v>2.636901363928246e-09</v>
       </c>
       <c r="EE16" t="n">
-        <v>0.0007616282673552632</v>
+        <v>1.092618795439648e-08</v>
       </c>
       <c r="EF16" t="n">
-        <v>0.0005612136446870863</v>
+        <v>4.12322309628621e-09</v>
       </c>
       <c r="EG16" t="n">
-        <v>0.0008951883064582944</v>
+        <v>9.146780222124562e-09</v>
       </c>
       <c r="EH16" t="n">
-        <v>6.432541704270989e-05</v>
+        <v>2.198322857083213e-09</v>
       </c>
       <c r="EI16" t="n">
-        <v>0.0001813791604945436</v>
+        <v>7.482812591774746e-09</v>
       </c>
       <c r="EJ16" t="n">
-        <v>9.435112588107586e-05</v>
+        <v>8.518672878210509e-09</v>
       </c>
       <c r="EK16" t="n">
-        <v>0.0003271212626714259</v>
+        <v>1.214474920629982e-08</v>
       </c>
       <c r="EL16" t="n">
-        <v>0.0003212945302948356</v>
+        <v>5.059634489157361e-09</v>
       </c>
       <c r="EM16" t="n">
-        <v>0.0001746903581079096</v>
+        <v>4.89309437412544e-09</v>
       </c>
       <c r="EN16" t="n">
-        <v>5.940150003880262e-05</v>
+        <v>1.3412427612991e-08</v>
       </c>
       <c r="EO16" t="n">
-        <v>0.0002581137814559042</v>
+        <v>1.592377607551043e-08</v>
       </c>
       <c r="EP16" t="n">
-        <v>0.0003381170681677759</v>
+        <v>1.111801317676964e-08</v>
       </c>
       <c r="EQ16" t="n">
-        <v>8.285448711831123e-05</v>
+        <v>8.394271944212051e-09</v>
       </c>
       <c r="ER16" t="n">
-        <v>0.000418306648498401</v>
+        <v>8.386033201190912e-09</v>
       </c>
       <c r="ES16" t="n">
-        <v>0.0002797093475237489</v>
+        <v>5.662646351822787e-09</v>
       </c>
       <c r="ET16" t="n">
-        <v>4.762167372973636e-05</v>
+        <v>2.762393425115306e-09</v>
       </c>
       <c r="EU16" t="n">
-        <v>0.0005885777645744383</v>
+        <v>5.459663388052149e-09</v>
       </c>
       <c r="EV16" t="n">
-        <v>0.0004540204245131463</v>
+        <v>1.30800845710155e-08</v>
       </c>
       <c r="EW16" t="n">
-        <v>0.0001851621636888012</v>
+        <v>7.279845615215663e-09</v>
       </c>
       <c r="EX16" t="n">
-        <v>0.000229274810408242</v>
+        <v>2.30703056658399e-09</v>
       </c>
       <c r="EY16" t="n">
-        <v>0.0005826235865242779</v>
+        <v>7.940622381852336e-09</v>
       </c>
       <c r="EZ16" t="n">
-        <v>3.88164771720767e-05</v>
+        <v>1.866501175840085e-09</v>
       </c>
       <c r="FA16" t="n">
-        <v>1.325404082308523e-05</v>
+        <v>1.433976493103728e-09</v>
       </c>
       <c r="FB16" t="n">
-        <v>0.000108859094325453</v>
+        <v>4.976866696537741e-10</v>
       </c>
       <c r="FC16" t="n">
-        <v>0.0001204452273668721</v>
+        <v>8.476191304396252e-09</v>
       </c>
       <c r="FD16" t="n">
-        <v>0.0003317566006444395</v>
+        <v>7.64401075770138e-09</v>
       </c>
       <c r="FE16" t="n">
-        <v>0.0001440963242202997</v>
+        <v>5.808615810565243e-09</v>
       </c>
       <c r="FF16" t="n">
-        <v>0.0002812842139974236</v>
+        <v>6.000974384079427e-09</v>
       </c>
       <c r="FG16" t="n">
-        <v>0.0001144496854976751</v>
+        <v>1.735445565032023e-09</v>
       </c>
       <c r="FH16" t="n">
-        <v>0.0002643500629346818</v>
+        <v>7.75365904814862e-09</v>
       </c>
       <c r="FI16" t="n">
-        <v>0.0003253495669923723</v>
+        <v>2.763906081781897e-08</v>
       </c>
       <c r="FJ16" t="n">
-        <v>0.0005794989410787821</v>
+        <v>1.122195847358398e-08</v>
       </c>
       <c r="FK16" t="n">
-        <v>0.0002302719076396897</v>
+        <v>2.870169879543027e-08</v>
       </c>
       <c r="FL16" t="n">
-        <v>6.936895078979433e-05</v>
+        <v>1.016916773011189e-08</v>
       </c>
       <c r="FM16" t="n">
-        <v>0.0001722056185826659</v>
+        <v>1.373377078728311e-09</v>
       </c>
       <c r="FN16" t="n">
-        <v>0.0001363222399959341</v>
+        <v>2.676056531925042e-08</v>
       </c>
       <c r="FO16" t="n">
-        <v>0.0002502445131540298</v>
+        <v>1.69878866529416e-08</v>
       </c>
       <c r="FP16" t="n">
-        <v>0.0006497618742287159</v>
+        <v>3.459157582597072e-08</v>
       </c>
       <c r="FQ16" t="n">
-        <v>0.0002649548696354032</v>
+        <v>3.135189530212301e-08</v>
       </c>
       <c r="FR16" t="n">
-        <v>0.0003005223697982728</v>
+        <v>3.094334388720199e-08</v>
       </c>
       <c r="FS16" t="n">
-        <v>0.000502966227941215</v>
+        <v>6.289870668751973e-08</v>
       </c>
       <c r="FT16" t="n">
-        <v>9.294912160839885e-05</v>
+        <v>6.899752769129464e-09</v>
       </c>
       <c r="FU16" t="n">
-        <v>0.0002811792655847967</v>
+        <v>1.902777047035897e-09</v>
       </c>
       <c r="FV16" t="n">
-        <v>0.0001041432988131419</v>
+        <v>7.005019675432322e-09</v>
       </c>
       <c r="FW16" t="n">
-        <v>2.798574132611975e-05</v>
+        <v>3.680978366560339e-08</v>
       </c>
       <c r="FX16" t="n">
-        <v>0.0002305346424691379</v>
+        <v>6.239942340613425e-09</v>
       </c>
       <c r="FY16" t="n">
-        <v>0.000729277147911489</v>
+        <v>1.159303675279943e-08</v>
       </c>
       <c r="FZ16" t="n">
-        <v>0.0001017888644128107</v>
+        <v>2.085360506498546e-08</v>
       </c>
       <c r="GA16" t="n">
-        <v>0.0001959515066118911</v>
+        <v>1.850755637633483e-08</v>
       </c>
       <c r="GB16" t="n">
-        <v>1.62962078320561e-05</v>
+        <v>2.005306143360031e-08</v>
       </c>
       <c r="GC16" t="n">
-        <v>0.000156287889694795</v>
+        <v>1.329558241280893e-08</v>
       </c>
       <c r="GD16" t="n">
-        <v>0.0003006122133228928</v>
+        <v>1.648277425658762e-08</v>
       </c>
       <c r="GE16" t="n">
-        <v>8.680026076035574e-05</v>
+        <v>1.542491290251746e-08</v>
       </c>
       <c r="GF16" t="n">
-        <v>0.0002097943070111796</v>
+        <v>4.034950151776684e-09</v>
       </c>
       <c r="GG16" t="n">
-        <v>0.0002751450520008802</v>
+        <v>3.066126463835417e-09</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>1.180318832397461</v>
+        <v>0.5848846435546875</v>
       </c>
       <c r="B17" t="n">
-        <v>0.2624476253986359</v>
+        <v>0.07003936171531677</v>
       </c>
       <c r="C17" t="n">
-        <v>0.03602723777294159</v>
+        <v>1.371728539466858</v>
       </c>
       <c r="D17" t="n">
-        <v>0.2170795798301697</v>
+        <v>0.5881034731864929</v>
       </c>
       <c r="E17" t="n">
-        <v>0.1146289333701134</v>
+        <v>0.619350790977478</v>
       </c>
       <c r="F17" t="n">
-        <v>0.824756920337677</v>
+        <v>1.483222246170044</v>
       </c>
       <c r="G17" t="n">
-        <v>0.2843971848487854</v>
+        <v>0.2449263781309128</v>
       </c>
       <c r="H17" t="n">
-        <v>0.2468066364526749</v>
+        <v>0.7028997540473938</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1478591710329056</v>
+        <v>0.651999831199646</v>
       </c>
       <c r="J17" t="n">
-        <v>0.8320124745368958</v>
+        <v>0.5539077520370483</v>
       </c>
       <c r="K17" t="n">
-        <v>0.2442663460969925</v>
+        <v>0.2859893143177032</v>
       </c>
       <c r="L17" t="n">
-        <v>0.08131936937570572</v>
+        <v>1.813968658447266</v>
       </c>
       <c r="M17" t="n">
-        <v>0.1893030107021332</v>
+        <v>0.2350879311561584</v>
       </c>
       <c r="N17" t="n">
-        <v>0.1216944605112076</v>
+        <v>1.163515090942383</v>
       </c>
       <c r="O17" t="n">
-        <v>0.7159577012062073</v>
+        <v>2.460204839706421</v>
       </c>
       <c r="P17" t="n">
-        <v>0.517544150352478</v>
+        <v>0.2104295790195465</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.345853716135025</v>
+        <v>0.5330830216407776</v>
       </c>
       <c r="R17" t="n">
-        <v>0.05499375611543655</v>
+        <v>1.027936577796936</v>
       </c>
       <c r="S17" t="n">
-        <v>0.122728168964386</v>
+        <v>0.1049882024526596</v>
       </c>
       <c r="T17" t="n">
-        <v>0.301302045583725</v>
+        <v>0.4458854794502258</v>
       </c>
       <c r="U17" t="n">
-        <v>0.08859209716320038</v>
+        <v>0.5477308034896851</v>
       </c>
       <c r="V17" t="n">
-        <v>0.1868656277656555</v>
+        <v>0.002783045172691345</v>
       </c>
       <c r="W17" t="n">
-        <v>0.4058549702167511</v>
+        <v>0.204473152756691</v>
       </c>
       <c r="X17" t="n">
-        <v>0.1560489535331726</v>
+        <v>0.1213886588811874</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.210093691945076</v>
+        <v>0.4285227060317993</v>
       </c>
       <c r="Z17" t="n">
-        <v>0.1270359307527542</v>
+        <v>0.1756923645734787</v>
       </c>
       <c r="AA17" t="n">
-        <v>0.01843433082103729</v>
+        <v>0.1334753036499023</v>
       </c>
       <c r="AB17" t="n">
-        <v>0.2663926184177399</v>
+        <v>0.2844670414924622</v>
       </c>
       <c r="AC17" t="n">
-        <v>0.1188983246684074</v>
+        <v>0.06491955369710922</v>
       </c>
       <c r="AD17" t="n">
-        <v>0.149054080247879</v>
+        <v>0.4080002307891846</v>
       </c>
       <c r="AE17" t="n">
-        <v>0.0740465372800827</v>
+        <v>0.1097308173775673</v>
       </c>
       <c r="AF17" t="n">
-        <v>0.1120143160223961</v>
+        <v>0.125984251499176</v>
       </c>
       <c r="AG17" t="n">
-        <v>0.1418112367391586</v>
+        <v>0.5366302132606506</v>
       </c>
       <c r="AH17" t="n">
-        <v>0.05035024881362915</v>
+        <v>0.2583291232585907</v>
       </c>
       <c r="AI17" t="n">
-        <v>0.05687310546636581</v>
+        <v>0.1343338936567307</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0.03541107103228569</v>
+        <v>0.6521579027175903</v>
       </c>
       <c r="AK17" t="n">
-        <v>0.2485543936491013</v>
+        <v>0.1930579245090485</v>
       </c>
       <c r="AL17" t="n">
-        <v>0.1174021139740944</v>
+        <v>0.05275344848632812</v>
       </c>
       <c r="AM17" t="n">
-        <v>0.1018578112125397</v>
+        <v>0.2655395567417145</v>
       </c>
       <c r="AN17" t="n">
-        <v>0.18299899995327</v>
+        <v>0.4317006468772888</v>
       </c>
       <c r="AO17" t="n">
-        <v>0.03424657136201859</v>
+        <v>0.7594559788703918</v>
       </c>
       <c r="AP17" t="n">
-        <v>0.05385412648320198</v>
+        <v>0.07194268703460693</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0.03006621822714806</v>
+        <v>0.1531426310539246</v>
       </c>
       <c r="AR17" t="n">
-        <v>0.141258493065834</v>
+        <v>0.1867043524980545</v>
       </c>
       <c r="AS17" t="n">
-        <v>0.01079247612506151</v>
+        <v>0.03339933976531029</v>
       </c>
       <c r="AT17" t="n">
-        <v>0.7277436852455139</v>
+        <v>0.08120882511138916</v>
       </c>
       <c r="AU17" t="n">
-        <v>0.2824447453022003</v>
+        <v>0.8813360929489136</v>
       </c>
       <c r="AV17" t="n">
-        <v>0.1099474802613258</v>
+        <v>0.7129140496253967</v>
       </c>
       <c r="AW17" t="n">
-        <v>0.1571962535381317</v>
+        <v>0.1728441119194031</v>
       </c>
       <c r="AX17" t="n">
-        <v>0.5958960652351379</v>
+        <v>0.4892546236515045</v>
       </c>
       <c r="AY17" t="n">
-        <v>0.6714555621147156</v>
+        <v>1.582449555397034</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0.05543580651283264</v>
+        <v>0.468798041343689</v>
       </c>
       <c r="BA17" t="n">
-        <v>0.353589653968811</v>
+        <v>0.3306079208850861</v>
       </c>
       <c r="BB17" t="n">
-        <v>0.1189827397465706</v>
+        <v>0.1486810296773911</v>
       </c>
       <c r="BC17" t="n">
-        <v>0.2096754014492035</v>
+        <v>0.307512104511261</v>
       </c>
       <c r="BD17" t="n">
-        <v>0.4472244381904602</v>
+        <v>0.4695419073104858</v>
       </c>
       <c r="BE17" t="n">
-        <v>0.1104241758584976</v>
+        <v>0.2256154716014862</v>
       </c>
       <c r="BF17" t="n">
-        <v>0.165772870182991</v>
+        <v>0.09923109412193298</v>
       </c>
       <c r="BG17" t="n">
-        <v>0.05268099904060364</v>
+        <v>1.17997670173645</v>
       </c>
       <c r="BH17" t="n">
-        <v>0.03570632264018059</v>
+        <v>0.768659770488739</v>
       </c>
       <c r="BI17" t="n">
-        <v>0.3716038465499878</v>
+        <v>0.0421411320567131</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.1683153361082077</v>
+        <v>0.1908360570669174</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.04659848660230637</v>
+        <v>0.2998316884040833</v>
       </c>
       <c r="BL17" t="n">
-        <v>0.02140155807137489</v>
+        <v>0.5671635866165161</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.2061213105916977</v>
+        <v>0.2433558851480484</v>
       </c>
       <c r="BN17" t="n">
-        <v>0.05190711468458176</v>
+        <v>0.8958279490470886</v>
       </c>
       <c r="BO17" t="n">
-        <v>0.2324418872594833</v>
+        <v>0.006030023097991943</v>
       </c>
       <c r="BP17" t="n">
-        <v>0.1896874457597733</v>
+        <v>0.06480519473552704</v>
       </c>
       <c r="BQ17" t="n">
-        <v>0.1815392524003983</v>
+        <v>0.1017649248242378</v>
       </c>
       <c r="BR17" t="n">
-        <v>0.1858390867710114</v>
+        <v>0.1734987199306488</v>
       </c>
       <c r="BS17" t="n">
-        <v>0.1701963841915131</v>
+        <v>0.1747335642576218</v>
       </c>
       <c r="BT17" t="n">
-        <v>0.1692915707826614</v>
+        <v>0.2440392822027206</v>
       </c>
       <c r="BU17" t="n">
-        <v>0.3561715483665466</v>
+        <v>0.07315399497747421</v>
       </c>
       <c r="BV17" t="n">
-        <v>0.2577700614929199</v>
+        <v>0.1201103627681732</v>
       </c>
       <c r="BW17" t="n">
-        <v>0.105206161737442</v>
+        <v>0.6262916922569275</v>
       </c>
       <c r="BX17" t="n">
-        <v>0.1410582214593887</v>
+        <v>0.6708921194076538</v>
       </c>
       <c r="BY17" t="n">
-        <v>0.387031614780426</v>
+        <v>0.1901224702596664</v>
       </c>
       <c r="BZ17" t="n">
-        <v>0.4585424661636353</v>
+        <v>0.7034153342247009</v>
       </c>
       <c r="CA17" t="n">
-        <v>0.05101502686738968</v>
+        <v>0.3462085425853729</v>
       </c>
       <c r="CB17" t="n">
-        <v>0.2427727282047272</v>
+        <v>0.1112069487571716</v>
       </c>
       <c r="CC17" t="n">
-        <v>0.0170366894453764</v>
+        <v>0.07022160291671753</v>
       </c>
       <c r="CD17" t="n">
-        <v>0.2071567475795746</v>
+        <v>0.07287240028381348</v>
       </c>
       <c r="CE17" t="n">
-        <v>0.2340685129165649</v>
+        <v>0.05601990222930908</v>
       </c>
       <c r="CF17" t="n">
-        <v>0.009120514616370201</v>
+        <v>0.5408768057823181</v>
       </c>
       <c r="CG17" t="n">
-        <v>0.0006161481142044067</v>
+        <v>0.1264802813529968</v>
       </c>
       <c r="CH17" t="n">
-        <v>0.08329862356185913</v>
+        <v>0.1124960035085678</v>
       </c>
       <c r="CI17" t="n">
-        <v>0.1400411128997803</v>
+        <v>0.1481123417615891</v>
       </c>
       <c r="CJ17" t="n">
-        <v>0.02694472298026085</v>
+        <v>0.1375765800476074</v>
       </c>
       <c r="CK17" t="n">
-        <v>0.2237138301134109</v>
+        <v>0.08195298910140991</v>
       </c>
       <c r="CL17" t="n">
-        <v>0.0202200785279274</v>
+        <v>0.08892946690320969</v>
       </c>
       <c r="CM17" t="n">
-        <v>0.03247847408056259</v>
+        <v>0.1525468230247498</v>
       </c>
       <c r="CN17" t="n">
-        <v>0.06939671188592911</v>
+        <v>0.09991998225450516</v>
       </c>
       <c r="CO17" t="n">
-        <v>0.004537966102361679</v>
+        <v>0.2370522916316986</v>
       </c>
       <c r="CP17" t="n">
-        <v>0.006920285522937775</v>
+        <v>0.1604753881692886</v>
       </c>
       <c r="CQ17" t="n">
-        <v>0.625977098941803</v>
+        <v>0.292252391576767</v>
       </c>
       <c r="CR17" t="n">
-        <v>0.1016014590859413</v>
+        <v>0.5923437476158142</v>
       </c>
       <c r="CS17" t="n">
-        <v>0.08734869211912155</v>
+        <v>0.461259514093399</v>
       </c>
       <c r="CT17" t="n">
-        <v>0.04722239077091217</v>
+        <v>0.1652331799268723</v>
       </c>
       <c r="CU17" t="n">
-        <v>0.02921108342707157</v>
+        <v>0.03871528059244156</v>
       </c>
       <c r="CV17" t="n">
-        <v>0.1915698796510696</v>
+        <v>0.1025032475590706</v>
       </c>
       <c r="CW17" t="n">
-        <v>0.2226179391145706</v>
+        <v>0.1166781410574913</v>
       </c>
       <c r="CX17" t="n">
-        <v>0.01289805956184864</v>
+        <v>0.5053735375404358</v>
       </c>
       <c r="CY17" t="n">
-        <v>0.02510286867618561</v>
+        <v>0.1047535911202431</v>
       </c>
       <c r="CZ17" t="n">
-        <v>0.07357688993215561</v>
+        <v>0.3172684907913208</v>
       </c>
       <c r="DA17" t="n">
-        <v>0.1475271880626678</v>
+        <v>0.3495361804962158</v>
       </c>
       <c r="DB17" t="n">
-        <v>6.191432476043701e-06</v>
+        <v>0.144146203994751</v>
       </c>
       <c r="DC17" t="n">
-        <v>0.2236250042915344</v>
+        <v>0.0201024953275919</v>
       </c>
       <c r="DD17" t="n">
-        <v>0.03981001675128937</v>
+        <v>0.0994885042309761</v>
       </c>
       <c r="DE17" t="n">
-        <v>0.08251099288463593</v>
+        <v>0.1424831300973892</v>
       </c>
       <c r="DF17" t="n">
-        <v>0.109473742544651</v>
+        <v>0.1321528553962708</v>
       </c>
       <c r="DG17" t="n">
-        <v>0.04461254179477692</v>
+        <v>0.6422188878059387</v>
       </c>
       <c r="DH17" t="n">
-        <v>0.1613059341907501</v>
+        <v>0.2733647227287292</v>
       </c>
       <c r="DI17" t="n">
-        <v>0.3635796308517456</v>
+        <v>0.1941564381122589</v>
       </c>
       <c r="DJ17" t="n">
-        <v>0.002030434086918831</v>
+        <v>0.262524276971817</v>
       </c>
       <c r="DK17" t="n">
-        <v>0.07045847177505493</v>
+        <v>0.432799905538559</v>
       </c>
       <c r="DL17" t="n">
-        <v>0.2261217683553696</v>
+        <v>0.2326010167598724</v>
       </c>
       <c r="DM17" t="n">
-        <v>0.1083736270666122</v>
+        <v>0.5219295620918274</v>
       </c>
       <c r="DN17" t="n">
-        <v>0.1072840914130211</v>
+        <v>0.02204790152609348</v>
       </c>
       <c r="DO17" t="n">
-        <v>0.008241094648838043</v>
+        <v>0.1793106496334076</v>
       </c>
       <c r="DP17" t="n">
-        <v>0.1055444628000259</v>
+        <v>0.6419658064842224</v>
       </c>
       <c r="DQ17" t="n">
-        <v>0.0298868790268898</v>
+        <v>0.07922375947237015</v>
       </c>
       <c r="DR17" t="n">
-        <v>0.04442330077290535</v>
+        <v>0.3435224592685699</v>
       </c>
       <c r="DS17" t="n">
-        <v>0.1124017238616943</v>
+        <v>0.4133778810501099</v>
       </c>
       <c r="DT17" t="n">
-        <v>0.1855147331953049</v>
+        <v>0.2228248417377472</v>
       </c>
       <c r="DU17" t="n">
-        <v>0.4045686423778534</v>
+        <v>0.2385864108800888</v>
       </c>
       <c r="DV17" t="n">
-        <v>0.04623319208621979</v>
+        <v>0.4878709316253662</v>
       </c>
       <c r="DW17" t="n">
-        <v>0.01469737198203802</v>
+        <v>0.1388528794050217</v>
       </c>
       <c r="DX17" t="n">
-        <v>0.1713905185461044</v>
+        <v>0.515184223651886</v>
       </c>
       <c r="DY17" t="n">
-        <v>0.02710531279444695</v>
+        <v>0.6427204608917236</v>
       </c>
       <c r="DZ17" t="n">
-        <v>0.03964009135961533</v>
+        <v>0.7106972336769104</v>
       </c>
       <c r="EA17" t="n">
-        <v>0.02378075942397118</v>
+        <v>0.2253076732158661</v>
       </c>
       <c r="EB17" t="n">
-        <v>0.3302265703678131</v>
+        <v>0.5810720920562744</v>
       </c>
       <c r="EC17" t="n">
-        <v>0.02017518505454063</v>
+        <v>0.1263360679149628</v>
       </c>
       <c r="ED17" t="n">
-        <v>0.02929426357150078</v>
+        <v>0.2373557835817337</v>
       </c>
       <c r="EE17" t="n">
-        <v>0.125989094376564</v>
+        <v>0.1232561841607094</v>
       </c>
       <c r="EF17" t="n">
-        <v>0.1558857858181</v>
+        <v>0.1578329056501389</v>
       </c>
       <c r="EG17" t="n">
-        <v>0.165084645152092</v>
+        <v>0.1415406912565231</v>
       </c>
       <c r="EH17" t="n">
-        <v>0.02859915792942047</v>
+        <v>0.4527249932289124</v>
       </c>
       <c r="EI17" t="n">
-        <v>0.07607606053352356</v>
+        <v>0.004408175125718117</v>
       </c>
       <c r="EJ17" t="n">
-        <v>0.01644260250031948</v>
+        <v>0.4152713418006897</v>
       </c>
       <c r="EK17" t="n">
-        <v>0.02583561837673187</v>
+        <v>0.1092369481921196</v>
       </c>
       <c r="EL17" t="n">
-        <v>0.009257040917873383</v>
+        <v>0.01152574829757214</v>
       </c>
       <c r="EM17" t="n">
-        <v>0.03606799617409706</v>
+        <v>0.02155927568674088</v>
       </c>
       <c r="EN17" t="n">
-        <v>0.04177474975585938</v>
+        <v>0.1175269111990929</v>
       </c>
       <c r="EO17" t="n">
-        <v>0.07893306761980057</v>
+        <v>0.008628770709037781</v>
       </c>
       <c r="EP17" t="n">
-        <v>0.2749474346637726</v>
+        <v>0.1995585560798645</v>
       </c>
       <c r="EQ17" t="n">
-        <v>0.06947876513004303</v>
+        <v>0.1935864388942719</v>
       </c>
       <c r="ER17" t="n">
-        <v>0.1030310243368149</v>
+        <v>0.03053360432386398</v>
       </c>
       <c r="ES17" t="n">
-        <v>0.3104412257671356</v>
+        <v>0.1627426445484161</v>
       </c>
       <c r="ET17" t="n">
-        <v>0.1382138133049011</v>
+        <v>0.2902105152606964</v>
       </c>
       <c r="EU17" t="n">
-        <v>0.1710902601480484</v>
+        <v>0.1830323338508606</v>
       </c>
       <c r="EV17" t="n">
-        <v>0.1514442712068558</v>
+        <v>0.1612802296876907</v>
       </c>
       <c r="EW17" t="n">
-        <v>0.1365577876567841</v>
+        <v>0.2081024944782257</v>
       </c>
       <c r="EX17" t="n">
-        <v>0.154307559132576</v>
+        <v>0.03870616853237152</v>
       </c>
       <c r="EY17" t="n">
-        <v>0.1827547401189804</v>
+        <v>0.01948732882738113</v>
       </c>
       <c r="EZ17" t="n">
-        <v>0.006807371973991394</v>
+        <v>0.3967071175575256</v>
       </c>
       <c r="FA17" t="n">
-        <v>0.04828403517603874</v>
+        <v>0.144148975610733</v>
       </c>
       <c r="FB17" t="n">
-        <v>0.07718504220247269</v>
+        <v>0.1222541630268097</v>
       </c>
       <c r="FC17" t="n">
-        <v>0.1069734692573547</v>
+        <v>0.3370934426784515</v>
       </c>
       <c r="FD17" t="n">
-        <v>0.05345487222075462</v>
+        <v>0.1998439729213715</v>
       </c>
       <c r="FE17" t="n">
-        <v>0.2686589062213898</v>
+        <v>0.08246991038322449</v>
       </c>
       <c r="FF17" t="n">
-        <v>0.03132621571421623</v>
+        <v>0.06257987767457962</v>
       </c>
       <c r="FG17" t="n">
-        <v>0.1046399474143982</v>
+        <v>0.2375799864530563</v>
       </c>
       <c r="FH17" t="n">
-        <v>0.07016362249851227</v>
+        <v>0.3680876195430756</v>
       </c>
       <c r="FI17" t="n">
-        <v>0.0588342659175396</v>
+        <v>0.6143237352371216</v>
       </c>
       <c r="FJ17" t="n">
-        <v>0.01723785698413849</v>
+        <v>0.2994651794433594</v>
       </c>
       <c r="FK17" t="n">
-        <v>0.09701593965291977</v>
+        <v>0.04778685420751572</v>
       </c>
       <c r="FL17" t="n">
-        <v>0.01401578821241856</v>
+        <v>0.4175926744937897</v>
       </c>
       <c r="FM17" t="n">
-        <v>0.06058432534337044</v>
+        <v>0.2781196236610413</v>
       </c>
       <c r="FN17" t="n">
-        <v>0.01227173767983913</v>
+        <v>0.4359074234962463</v>
       </c>
       <c r="FO17" t="n">
-        <v>0.02701780572533607</v>
+        <v>0.4850861430168152</v>
       </c>
       <c r="FP17" t="n">
-        <v>0.2454353868961334</v>
+        <v>0.2713158130645752</v>
       </c>
       <c r="FQ17" t="n">
-        <v>0.1534387916326523</v>
+        <v>0.3373424410820007</v>
       </c>
       <c r="FR17" t="n">
-        <v>0.1370709389448166</v>
+        <v>0.7695785760879517</v>
       </c>
       <c r="FS17" t="n">
-        <v>0.09993056952953339</v>
+        <v>0.1202555298805237</v>
       </c>
       <c r="FT17" t="n">
-        <v>0.234009325504303</v>
+        <v>0.6619278192520142</v>
       </c>
       <c r="FU17" t="n">
-        <v>0.3053976893424988</v>
+        <v>0.4138425290584564</v>
       </c>
       <c r="FV17" t="n">
-        <v>0.1054039597511292</v>
+        <v>0.1008172035217285</v>
       </c>
       <c r="FW17" t="n">
-        <v>0.02449970506131649</v>
+        <v>0.3672768473625183</v>
       </c>
       <c r="FX17" t="n">
-        <v>0.005827286280691624</v>
+        <v>0.9430080056190491</v>
       </c>
       <c r="FY17" t="n">
-        <v>0.1003322303295135</v>
+        <v>0.3014031946659088</v>
       </c>
       <c r="FZ17" t="n">
-        <v>0.02141768299043179</v>
+        <v>0.7141110897064209</v>
       </c>
       <c r="GA17" t="n">
-        <v>0.06822192668914795</v>
+        <v>0.4742826819419861</v>
       </c>
       <c r="GB17" t="n">
-        <v>0.05670862272381783</v>
+        <v>0.02296196669340134</v>
       </c>
       <c r="GC17" t="n">
-        <v>0.1061685085296631</v>
+        <v>0.09068579971790314</v>
       </c>
       <c r="GD17" t="n">
-        <v>0.07953757047653198</v>
+        <v>0.1115282252430916</v>
       </c>
       <c r="GE17" t="n">
-        <v>0.07594138383865356</v>
+        <v>0.3244221210479736</v>
       </c>
       <c r="GF17" t="n">
-        <v>0.130971685051918</v>
+        <v>0.5502086281776428</v>
       </c>
       <c r="GG17" t="n">
-        <v>0.04311869293451309</v>
+        <v>0.2385734170675278</v>
       </c>
     </row>
   </sheetData>
